--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -12043,6 +12043,534 @@
       <c r="J7" s="171" t="inlineStr">
         <is>
           <t>Pass 1: MTP vs test suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-01</t>
+        </is>
+      </c>
+      <c r="B8" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C8" s="171" t="inlineStr">
+        <is>
+          <t>Audio attachments on visits with server-side transcription + translation (AudioAttachment.transcript/translation; audio_attachment/&lt;pk&gt;/transcribe endpoint)</t>
+        </is>
+      </c>
+      <c r="D8" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E8" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (WVV covers image carousel only, not audio/transcription). Src: opportunity AudioAttachment + AudioAttachmentTranscribe</t>
+        </is>
+      </c>
+      <c r="F8" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H8" s="171" t="inlineStr"/>
+      <c r="I8" s="171" t="inlineStr"/>
+      <c r="J8" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-02</t>
+        </is>
+      </c>
+      <c r="B9" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C9" s="171" t="inlineStr">
+        <is>
+          <t>Granular verification-flag types configured per opportunity: gps, duplicate, location-radius, form-submission time window (start/end), catchment_areas, duration</t>
+        </is>
+      </c>
+      <c r="D9" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E9" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs OD_7 (generic 'verification flags'). Each flag type not a case. Src: OpportunityVerificationFlags model</t>
+        </is>
+      </c>
+      <c r="F9" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H9" s="171" t="inlineStr"/>
+      <c r="I9" s="171" t="inlineStr"/>
+      <c r="J9" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-03</t>
+        </is>
+      </c>
+      <c r="B10" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C10" s="171" t="inlineStr">
+        <is>
+          <t>Catchment-area based verification: import/export catchment areas (CSV) and flag visits outside the area (CatchmentArea model, import/export_catchment_area)</t>
+        </is>
+      </c>
+      <c r="D10" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E10" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: opportunity CatchmentArea + import_catchment_area/export_catchment_area</t>
+        </is>
+      </c>
+      <c r="F10" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H10" s="171" t="inlineStr"/>
+      <c r="I10" s="171" t="inlineStr"/>
+      <c r="J10" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-04</t>
+        </is>
+      </c>
+      <c r="B11" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C11" s="171" t="inlineStr">
+        <is>
+          <t>Form-JSON validation rules (question path == value) and per-deliver-unit flag rules (check_attachments, duration) as configurable verification checks</t>
+        </is>
+      </c>
+      <c r="D11" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E11" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: FormJsonValidationRules + DeliverUnitFlagRules + delete_form_json_rule</t>
+        </is>
+      </c>
+      <c r="F11" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H11" s="171" t="inlineStr"/>
+      <c r="I11" s="171" t="inlineStr"/>
+      <c r="J11" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-05</t>
+        </is>
+      </c>
+      <c r="B12" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C12" s="171" t="inlineStr">
+        <is>
+          <t>auto_approve_payments opportunity setting (distinct from auto_approve_visits) - payments auto-approved without manual step</t>
+        </is>
+      </c>
+      <c r="D12" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E12" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (visit auto-approve covered, payment auto-approve not). Src: Opportunity.auto_approve_payments</t>
+        </is>
+      </c>
+      <c r="F12" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H12" s="171" t="inlineStr"/>
+      <c r="I12" s="171" t="inlineStr"/>
+      <c r="J12" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-06</t>
+        </is>
+      </c>
+      <c r="B13" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C13" s="171" t="inlineStr">
+        <is>
+          <t>automatic_visit_verification opportunity flag (system auto-verifies visits against rules, distinct from NM manual approve)</t>
+        </is>
+      </c>
+      <c r="D13" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E13" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs MTP. Src: Opportunity.automatic_visit_verification</t>
+        </is>
+      </c>
+      <c r="F13" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H13" s="171" t="inlineStr"/>
+      <c r="I13" s="171" t="inlineStr"/>
+      <c r="J13" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-07</t>
+        </is>
+      </c>
+      <c r="B14" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity List page</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="inlineStr">
+        <is>
+          <t>Archived opportunities: an opportunity can be archived (distinct from active/ended); archived-state handling in lists/filters</t>
+        </is>
+      </c>
+      <c r="D14" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E14" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (OLP filters cover Test/Live/Active/Ended, not Archived). Src: Opportunity.archived / is_active</t>
+        </is>
+      </c>
+      <c r="F14" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G14" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H14" s="171" t="inlineStr"/>
+      <c r="I14" s="171" t="inlineStr"/>
+      <c r="J14" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-08</t>
+        </is>
+      </c>
+      <c r="B15" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C15" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity finalize step: an opportunity must be 'setup complete' (payment units + budget + dates) and finalized before going live (OpportunityFinalize / is_setup_complete)</t>
+        </is>
+      </c>
+      <c r="D15" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E15" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (creation covered, finalize/setup-complete gate not). Src: OpportunityFinalize view / Opportunity.is_setup_complete</t>
+        </is>
+      </c>
+      <c r="F15" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G15" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H15" s="171" t="inlineStr"/>
+      <c r="I15" s="171" t="inlineStr"/>
+      <c r="J15" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-09</t>
+        </is>
+      </c>
+      <c r="B16" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C16" s="171" t="inlineStr">
+        <is>
+          <t>Invite SMS delivery status tracking: UserInvite status includes sms_delivered / sms_not_delivered (Twilio delivery callback), plus not_found / invited / accepted</t>
+        </is>
+      </c>
+      <c r="D16" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E16" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Connect_worker (pending/accepted/not-found). SMS delivered-vs-not not covered. Src: UserInviteStatus</t>
+        </is>
+      </c>
+      <c r="F16" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G16" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H16" s="171" t="inlineStr"/>
+      <c r="I16" s="171" t="inlineStr"/>
+      <c r="J16" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-10</t>
+        </is>
+      </c>
+      <c r="B17" s="171" t="inlineStr">
+        <is>
+          <t>Invoices List page</t>
+        </is>
+      </c>
+      <c r="C17" s="171" t="inlineStr">
+        <is>
+          <t>Organization-level payments to Network Manager orgs (Payment.organization) - distinct from worker payments; incl. payment_method/payment_operator</t>
+        </is>
+      </c>
+      <c r="D17" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E17" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (payment processing covers worker payments only). Src: Payment.organization / payment_method</t>
+        </is>
+      </c>
+      <c r="F17" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H17" s="171" t="inlineStr"/>
+      <c r="I17" s="171" t="inlineStr"/>
+      <c r="J17" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-11</t>
+        </is>
+      </c>
+      <c r="B18" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity dashboard</t>
+        </is>
+      </c>
+      <c r="C18" s="171" t="inlineStr">
+        <is>
+          <t>Sync deliver units from the HQ app (sync_deliver_units) - refresh deliver-unit definitions from CommCare</t>
+        </is>
+      </c>
+      <c r="D18" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E18" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: sync_deliver_units view</t>
+        </is>
+      </c>
+      <c r="F18" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G18" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H18" s="171" t="inlineStr"/>
+      <c r="I18" s="171" t="inlineStr"/>
+      <c r="J18" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-12</t>
+        </is>
+      </c>
+      <c r="B19" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C19" s="171" t="inlineStr">
+        <is>
+          <t>Labs/experiments framework (LabsRecord) attached to user/org/opportunity/program - may gate experimental behaviour; confirm if user-facing or internal</t>
+        </is>
+      </c>
+      <c r="D19" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E19" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (possibly internal - reviewer/product to confirm scope). Src: LabsRecord model</t>
+        </is>
+      </c>
+      <c r="F19" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H19" s="171" t="inlineStr"/>
+      <c r="I19" s="171" t="inlineStr"/>
+      <c r="J19" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -12571,6 +12571,446 @@
       <c r="J19" s="171" t="inlineStr">
         <is>
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-13</t>
+        </is>
+      </c>
+      <c r="B20" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C20" s="171" t="inlineStr">
+        <is>
+          <t>Validation: Learn app and Deliver app cannot be the same app (error on both fields)</t>
+        </is>
+      </c>
+      <c r="D20" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E20" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: OpportunityInitForm.clean</t>
+        </is>
+      </c>
+      <c r="F20" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G20" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H20" s="171" t="inlineStr"/>
+      <c r="I20" s="171" t="inlineStr"/>
+      <c r="J20" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-14</t>
+        </is>
+      </c>
+      <c r="B21" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C21" s="171" t="inlineStr">
+        <is>
+          <t>Certain opportunity fields become non-editable once Connect Workers have joined ('cannot be edited after Connect Workers have joined')</t>
+        </is>
+      </c>
+      <c r="D21" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E21" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: OpportunityInitUpdateForm.clean (_disabled_fields)</t>
+        </is>
+      </c>
+      <c r="F21" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G21" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H21" s="171" t="inlineStr"/>
+      <c r="I21" s="171" t="inlineStr"/>
+      <c r="J21" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-15</t>
+        </is>
+      </c>
+      <c r="B22" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C22" s="171" t="inlineStr">
+        <is>
+          <t>Managed-opp finalize validations: end-date not in past, start-date today-or-later, start&lt;end, both within the program's date window, and total budget (summed across the program's opps) must not exceed program budget</t>
+        </is>
+      </c>
+      <c r="D22" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E22" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Opp_create_21 (budget page). Program-budget cap + program-date bounds + date rules not cases. Src: OpportunityFinalizeForm.clean</t>
+        </is>
+      </c>
+      <c r="F22" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G22" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H22" s="171" t="inlineStr"/>
+      <c r="I22" s="171" t="inlineStr"/>
+      <c r="J22" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-16</t>
+        </is>
+      </c>
+      <c r="B23" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="171" t="inlineStr">
+        <is>
+          <t>Add-budget (new workers) rules: PM-only for managed opps; 'users' and 'total budget' can't both be set conflictingly; total budget can't be below already-claimed budget; can't exceed program budget</t>
+        </is>
+      </c>
+      <c r="D23" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E23" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs OD_17. PM-gate + program-cap + not-below-claimed not covered. Src: AddBudgetNewUsersForm.clean</t>
+        </is>
+      </c>
+      <c r="F23" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G23" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H23" s="171" t="inlineStr"/>
+      <c r="I23" s="171" t="inlineStr"/>
+      <c r="J23" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-17</t>
+        </is>
+      </c>
+      <c r="B24" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="171" t="inlineStr">
+        <is>
+          <t>Add-budget (existing workers) rules: increase can't exceed opportunity remaining budget; must specify visits OR end date; adjustment type required with visits; end date not in past</t>
+        </is>
+      </c>
+      <c r="D24" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E24" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs OD_10-14 (OD_14 decrease-below-completed covered). Budget-exceed + required-field rules not covered. Src: AddBudgetExistingUsersForm.clean</t>
+        </is>
+      </c>
+      <c r="F24" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G24" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H24" s="171" t="inlineStr"/>
+      <c r="I24" s="171" t="inlineStr"/>
+      <c r="J24" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-18</t>
+        </is>
+      </c>
+      <c r="B25" s="171" t="inlineStr">
+        <is>
+          <t>Invoices List page</t>
+        </is>
+      </c>
+      <c r="C25" s="171" t="inlineStr">
+        <is>
+          <t>Invoice number must be unique (reused number rejected) and is auto-generated when left blank</t>
+        </is>
+      </c>
+      <c r="D25" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E25" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: AutomatedPaymentInvoiceForm.clean_invoice_number</t>
+        </is>
+      </c>
+      <c r="F25" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G25" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H25" s="171" t="inlineStr"/>
+      <c r="I25" s="171" t="inlineStr"/>
+      <c r="J25" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-19</t>
+        </is>
+      </c>
+      <c r="B26" s="171" t="inlineStr">
+        <is>
+          <t>Invoices List page</t>
+        </is>
+      </c>
+      <c r="C26" s="171" t="inlineStr">
+        <is>
+          <t>Custom invoice requires an available exchange rate for the chosen date (error if none) and converts via USD toggle (amount &lt;-&gt; amount_usd)</t>
+        </is>
+      </c>
+      <c r="D26" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E26" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Invoice_04/06. 'Exchange rate not available' error + toggle conversion not covered. Src: AutomatedPaymentInvoiceForm.clean</t>
+        </is>
+      </c>
+      <c r="F26" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G26" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H26" s="171" t="inlineStr"/>
+      <c r="I26" s="171" t="inlineStr"/>
+      <c r="J26" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-20</t>
+        </is>
+      </c>
+      <c r="B27" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C27" s="171" t="inlineStr">
+        <is>
+          <t>Payment unit start/end date validation: end date cannot be earlier than start date</t>
+        </is>
+      </c>
+      <c r="D27" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E27" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: PaymentUnitForm.clean</t>
+        </is>
+      </c>
+      <c r="F27" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G27" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H27" s="171" t="inlineStr"/>
+      <c r="I27" s="171" t="inlineStr"/>
+      <c r="J27" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-21</t>
+        </is>
+      </c>
+      <c r="B28" s="171" t="inlineStr">
+        <is>
+          <t>Re-Learn Task</t>
+        </is>
+      </c>
+      <c r="C28" s="171" t="inlineStr">
+        <is>
+          <t>Adding a task type with a duplicate task-unit ID (already exists for the deliver app) is rejected</t>
+        </is>
+      </c>
+      <c r="D28" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E28" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: AddTaskTypeForm.clean</t>
+        </is>
+      </c>
+      <c r="F28" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G28" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H28" s="171" t="inlineStr"/>
+      <c r="I28" s="171" t="inlineStr"/>
+      <c r="J28" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-22</t>
+        </is>
+      </c>
+      <c r="B29" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="C29" s="171" t="inlineStr">
+        <is>
+          <t>Multi-stage opportunity lifecycle: Init -&gt; InitUpdate -&gt; Finalize, each PM-gated for managed opportunities (role checks + stage transitions)</t>
+        </is>
+      </c>
+      <c r="D29" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E29" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs MTP (creation treated as one flow). Stage/role gating not covered. Src: OpportunityInit/InitUpdate/OpportunityFinalize views</t>
+        </is>
+      </c>
+      <c r="F29" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G29" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H29" s="171" t="inlineStr"/>
+      <c r="I29" s="171" t="inlineStr"/>
+      <c r="J29" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -13011,6 +13011,182 @@
       <c r="J29" s="171" t="inlineStr">
         <is>
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-23</t>
+        </is>
+      </c>
+      <c r="B30" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C30" s="171" t="inlineStr">
+        <is>
+          <t>Deliver-tab has Has-Duplicates and Deliveries-with-Pending-Review filters, AND both are hidden when the opportunity has automatic_visit_verification enabled (conditional filter set)</t>
+        </is>
+      </c>
+      <c r="D30" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E30" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Delivery_tab_10-16 (last-active/flags/overlimit). Duplicates + review-pending + conditional hiding missing. Src: DeliverFilterSet</t>
+        </is>
+      </c>
+      <c r="F30" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G30" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H30" s="171" t="inlineStr"/>
+      <c r="I30" s="171" t="inlineStr"/>
+      <c r="J30" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 3: opportunity filters + visit_import + helpers</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-24</t>
+        </is>
+      </c>
+      <c r="B31" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C31" s="171" t="inlineStr">
+        <is>
+          <t>Bulk visit-status import (PM review CSV): per-row status must be a valid VisitValidationStatus, rejection requires a reason, justification required for certain agree/disagree changes, and invalid rows are reported individually</t>
+        </is>
+      </c>
+      <c r="D31" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E31" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs WVV_25-27. Per-row validation + justification-required not covered. Src: bulk_update_visit_status / get_data_by_visit_id</t>
+        </is>
+      </c>
+      <c r="F31" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G31" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H31" s="171" t="inlineStr"/>
+      <c r="I31" s="171" t="inlineStr"/>
+      <c r="J31" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 3: opportunity filters + visit_import + helpers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-25</t>
+        </is>
+      </c>
+      <c r="B32" s="171" t="inlineStr">
+        <is>
+          <t>Invoices List page</t>
+        </is>
+      </c>
+      <c r="C32" s="171" t="inlineStr">
+        <is>
+          <t>Bulk payment import (CSV): currency must match the opportunity currency, an exchange rate is required/looked up, and invalid rows are reported per-row</t>
+        </is>
+      </c>
+      <c r="D32" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E32" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (payment_import). Src: bulk_update_payments</t>
+        </is>
+      </c>
+      <c r="F32" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G32" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H32" s="171" t="inlineStr"/>
+      <c r="I32" s="171" t="inlineStr"/>
+      <c r="J32" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 3: opportunity filters + visit_import + helpers</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-26</t>
+        </is>
+      </c>
+      <c r="B33" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C33" s="171" t="inlineStr">
+        <is>
+          <t>Bulk completed-work status import (CSV): status validation, rejection reason handling, per-row error reporting, triggers payment-accrued recalculation</t>
+        </is>
+      </c>
+      <c r="D33" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E33" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: bulk_update_completed_work_status</t>
+        </is>
+      </c>
+      <c r="F33" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G33" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H33" s="171" t="inlineStr"/>
+      <c r="I33" s="171" t="inlineStr"/>
+      <c r="J33" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 3: opportunity filters + visit_import + helpers</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -13187,6 +13187,226 @@
       <c r="J33" s="171" t="inlineStr">
         <is>
           <t>Web batch 3: opportunity filters + visit_import + helpers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-27</t>
+        </is>
+      </c>
+      <c r="B34" s="171" t="inlineStr">
+        <is>
+          <t>Programs List page</t>
+        </is>
+      </c>
+      <c r="C34" s="171" t="inlineStr">
+        <is>
+          <t>Program application lifecycle includes REJECTED (PM rejects an application) and DECLINED (NM declines an invite) states, in addition to invited/applied/accepted</t>
+        </is>
+      </c>
+      <c r="D34" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E34" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs PLP_02/06/07/16 (invite/apply/accept). Reject + decline paths not covered. Src: program manage_application / apply_or_decline_application</t>
+        </is>
+      </c>
+      <c r="F34" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G34" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H34" s="171" t="inlineStr"/>
+      <c r="I34" s="171" t="inlineStr"/>
+      <c r="J34" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 4: program + organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-28</t>
+        </is>
+      </c>
+      <c r="B35" s="171" t="inlineStr">
+        <is>
+          <t>Programs List page</t>
+        </is>
+      </c>
+      <c r="C35" s="171" t="inlineStr">
+        <is>
+          <t>Organization membership roles (Admin vs Member) and the program-manager-org flag gate access across the web app (e.g. only PM-admins can create programs/invite)</t>
+        </is>
+      </c>
+      <c r="D35" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E35" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (no org-role/permission cases). Src: UserOrganizationMembership.Role / is_program_manager</t>
+        </is>
+      </c>
+      <c r="F35" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G35" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H35" s="171" t="inlineStr"/>
+      <c r="I35" s="171" t="inlineStr"/>
+      <c r="J35" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 4: program + organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-29</t>
+        </is>
+      </c>
+      <c r="B36" s="171" t="inlineStr">
+        <is>
+          <t>Programs List page</t>
+        </is>
+      </c>
+      <c r="C36" s="171" t="inlineStr">
+        <is>
+          <t>Program invite emails: an email is sent when an org is invited to a program, and a notification email to the PM when an org applies</t>
+        </is>
+      </c>
+      <c r="D36" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E36" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: send_program_invite_email / send_program_invite_applied_email</t>
+        </is>
+      </c>
+      <c r="F36" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G36" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H36" s="171" t="inlineStr"/>
+      <c r="I36" s="171" t="inlineStr"/>
+      <c r="J36" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 4: program + organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-30</t>
+        </is>
+      </c>
+      <c r="B37" s="171" t="inlineStr">
+        <is>
+          <t>Programs List page</t>
+        </is>
+      </c>
+      <c r="C37" s="171" t="inlineStr">
+        <is>
+          <t>Role-specific home dashboards: Program Manager vs Network Manager orgs see different landing content/metrics (program_manager_home vs network_manager_home)</t>
+        </is>
+      </c>
+      <c r="D37" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E37" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs PLP_03. Per-role dashboard differences not covered. Src: program_home / program_manager_home / network_manager_home</t>
+        </is>
+      </c>
+      <c r="F37" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G37" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H37" s="171" t="inlineStr"/>
+      <c r="I37" s="171" t="inlineStr"/>
+      <c r="J37" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 4: program + organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="171" t="inlineStr">
+        <is>
+          <t>GAP-MISC-07</t>
+        </is>
+      </c>
+      <c r="B38" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C38" s="171" t="inlineStr">
+        <is>
+          <t>Possible dead/broken code: UserOrganizationMembership.is_viewer() checks self.Role.VIEWER, but Role only defines ADMIN and MEMBER - calling is_viewer() would raise AttributeError. Confirm whether a VIEWER role is intended or the method is dead.</t>
+        </is>
+      </c>
+      <c r="D38" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E38" s="171" t="inlineStr">
+        <is>
+          <t>Code hygiene finding in web pass. Src: organization/models.py UserOrganizationMembership</t>
+        </is>
+      </c>
+      <c r="F38" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G38" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H38" s="171" t="inlineStr"/>
+      <c r="I38" s="171" t="inlineStr"/>
+      <c r="J38" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 4: program + organization</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -13407,6 +13407,138 @@
       <c r="J38" s="171" t="inlineStr">
         <is>
           <t>Web batch 4: program + organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-31</t>
+        </is>
+      </c>
+      <c r="B39" s="171" t="inlineStr">
+        <is>
+          <t>Microplanning</t>
+        </is>
+      </c>
+      <c r="C39" s="171" t="inlineStr">
+        <is>
+          <t>Work-area file import: upload work areas (WorkAreaImport) with async import-status polling - the ingestion step that precedes clustering/assignment</t>
+        </is>
+      </c>
+      <c r="D39" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E39" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (MP cases assume areas already uploaded). Src: microplanning WorkAreaImport / import_status</t>
+        </is>
+      </c>
+      <c r="F39" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G39" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H39" s="171" t="inlineStr"/>
+      <c r="I39" s="171" t="inlineStr"/>
+      <c r="J39" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 5: microplanning</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-32</t>
+        </is>
+      </c>
+      <c r="B40" s="171" t="inlineStr">
+        <is>
+          <t>Microplanning</t>
+        </is>
+      </c>
+      <c r="C40" s="171" t="inlineStr">
+        <is>
+          <t>Automatic work-area status transitions driven by visits: NOT_VISITED -&gt; VISITED on first approved visit, -&gt; EXPECTED_VISIT_REACHED when approved visit count hits the expected count</t>
+        </is>
+      </c>
+      <c r="D40" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E40" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs MP_07/08 (statuses listed, transitions not). Src: WorkArea.update_status</t>
+        </is>
+      </c>
+      <c r="F40" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G40" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H40" s="171" t="inlineStr"/>
+      <c r="I40" s="171" t="inlineStr"/>
+      <c r="J40" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 5: microplanning</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-33</t>
+        </is>
+      </c>
+      <c r="B41" s="171" t="inlineStr">
+        <is>
+          <t>Microplanning</t>
+        </is>
+      </c>
+      <c r="C41" s="171" t="inlineStr">
+        <is>
+          <t>Clustering and import run as async jobs with status polling (cluster_work_areas + clustering_status; import + import_status) - UI must poll for completion</t>
+        </is>
+      </c>
+      <c r="D41" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E41" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs MP_02. Async/polling behaviour not covered. Src: cluster_work_areas / clustering_status</t>
+        </is>
+      </c>
+      <c r="F41" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G41" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H41" s="171" t="inlineStr"/>
+      <c r="I41" s="171" t="inlineStr"/>
+      <c r="J41" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 5: microplanning</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -13539,6 +13539,270 @@
       <c r="J41" s="171" t="inlineStr">
         <is>
           <t>Web batch 5: microplanning</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-34</t>
+        </is>
+      </c>
+      <c r="B42" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C42" s="171" t="inlineStr">
+        <is>
+          <t>SMS status callback (Twilio) endpoint updates invite delivery status to sms_delivered / sms_not_delivered on the UserInvite</t>
+        </is>
+      </c>
+      <c r="D42" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E42" s="171" t="inlineStr">
+        <is>
+          <t>Backs SRC-W-09; callback endpoint itself untested. Src: users SMSStatusCallbackView</t>
+        </is>
+      </c>
+      <c r="F42" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G42" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H42" s="171" t="inlineStr"/>
+      <c r="I42" s="171" t="inlineStr"/>
+      <c r="J42" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-35</t>
+        </is>
+      </c>
+      <c r="B43" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity List page</t>
+        </is>
+      </c>
+      <c r="C43" s="171" t="inlineStr">
+        <is>
+          <t>Web accept-invite / invite-redirect link flow (opening an opportunity invite URL lands on accept view / redirects into the opportunity)</t>
+        </is>
+      </c>
+      <c r="D43" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E43" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (invite acceptance treated as mobile-only). Src: AcceptInviteView / InviteRedirectView</t>
+        </is>
+      </c>
+      <c r="F43" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G43" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H43" s="171" t="inlineStr"/>
+      <c r="I43" s="171" t="inlineStr"/>
+      <c r="J43" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-36</t>
+        </is>
+      </c>
+      <c r="B44" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C44" s="171" t="inlineStr">
+        <is>
+          <t>Web feature-flag administration: enable/disable feature flags and waffle switches from the web (feature_flags / toggle_switch / update_flag)</t>
+        </is>
+      </c>
+      <c r="D44" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E44" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP. Src: flags/views.py</t>
+        </is>
+      </c>
+      <c r="F44" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G44" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H44" s="171" t="inlineStr"/>
+      <c r="I44" s="171" t="inlineStr"/>
+      <c r="J44" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-37</t>
+        </is>
+      </c>
+      <c r="B45" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity dashboard</t>
+        </is>
+      </c>
+      <c r="C45" s="171" t="inlineStr">
+        <is>
+          <t>Audit reports workflow (feature-flag-gated): list audit reports, view detail, act on per-entry tasks, complete a report, export - beyond the single Audit-opportunity button</t>
+        </is>
+      </c>
+      <c r="D45" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E45" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs OD_2 (audit button only). Full audit workflow untested. Src: audit/views.py</t>
+        </is>
+      </c>
+      <c r="F45" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G45" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H45" s="171" t="inlineStr"/>
+      <c r="I45" s="171" t="inlineStr"/>
+      <c r="J45" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-38</t>
+        </is>
+      </c>
+      <c r="B46" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C46" s="171" t="inlineStr">
+        <is>
+          <t>Reporting module: Delivery Stats / KPI reports and Invoice reports with filters + CSV/XLSX export (org-level analytics)</t>
+        </is>
+      </c>
+      <c r="D46" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E46" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (no reports/KPI cases). Src: reports/views.py DeliveryStatsReportView / InvoiceReportView</t>
+        </is>
+      </c>
+      <c r="F46" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G46" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H46" s="171" t="inlineStr"/>
+      <c r="I46" s="171" t="inlineStr"/>
+      <c r="J46" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-39</t>
+        </is>
+      </c>
+      <c r="B47" s="171" t="inlineStr">
+        <is>
+          <t>App Credentials</t>
+        </is>
+      </c>
+      <c r="C47" s="171" t="inlineStr">
+        <is>
+          <t>UserCredential issuance with Learn/Delivery credential levels + types + issued_on + computed titles (drives credential-gated opportunity access)</t>
+        </is>
+      </c>
+      <c r="D47" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E47" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Credentials_1-3 + Worker History. Level/type issuance model not covered. Src: users/models UserCredential</t>
+        </is>
+      </c>
+      <c r="F47" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G47" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H47" s="171" t="inlineStr"/>
+      <c r="I47" s="171" t="inlineStr"/>
+      <c r="J47" s="171" t="inlineStr">
+        <is>
+          <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -11728,6 +11728,7 @@
     <col width="12" customWidth="1" style="148" min="8" max="8"/>
     <col width="40" customWidth="1" style="148" min="9" max="9"/>
     <col width="28" customWidth="1" style="148" min="10" max="10"/>
+    <col width="46" customWidth="1" style="148" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11781,6 +11782,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="K1" s="170" t="inlineStr">
+        <is>
+          <t>Eng Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="171" t="inlineStr">
@@ -11825,6 +11831,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="K2" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="171" t="inlineStr">
@@ -11869,6 +11880,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="K3" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="171" t="inlineStr">
@@ -11913,6 +11929,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="K4" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="171" t="inlineStr">
@@ -11957,6 +11978,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="K5" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="171" t="inlineStr">
@@ -12001,6 +12027,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="K6" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="171" t="inlineStr">
@@ -12045,6 +12076,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="K7" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="171" t="inlineStr">
@@ -12089,6 +12125,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K8" s="171" t="inlineStr">
+        <is>
+          <t>Partial (some eng coverage; confirm with eng)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="171" t="inlineStr">
@@ -12133,6 +12174,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K9" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="171" t="inlineStr">
@@ -12177,6 +12223,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K10" s="171" t="inlineStr">
+        <is>
+          <t>Partial (some eng coverage; confirm with eng)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="171" t="inlineStr">
@@ -12221,6 +12272,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K11" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="171" t="inlineStr">
@@ -12265,6 +12321,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K12" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="171" t="inlineStr">
@@ -12309,6 +12370,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K13" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="171" t="inlineStr">
@@ -12353,6 +12419,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K14" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="171" t="inlineStr">
@@ -12397,6 +12468,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K15" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="171" t="inlineStr">
@@ -12441,6 +12517,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K16" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="171" t="inlineStr">
@@ -12485,6 +12566,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K17" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="171" t="inlineStr">
@@ -12529,6 +12615,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K18" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="171" t="inlineStr">
@@ -12573,6 +12664,11 @@
           <t>Web pass 4/5 batch 1: commcare-connect opportunity spine (urls+models)</t>
         </is>
       </c>
+      <c r="K19" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="171" t="inlineStr">
@@ -12617,6 +12713,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K20" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="171" t="inlineStr">
@@ -12661,6 +12762,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K21" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="171" t="inlineStr">
@@ -12705,6 +12811,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K22" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="171" t="inlineStr">
@@ -12749,6 +12860,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K23" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="171" t="inlineStr">
@@ -12793,6 +12909,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K24" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="171" t="inlineStr">
@@ -12837,6 +12958,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K25" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="171" t="inlineStr">
@@ -12881,6 +13007,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K26" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="171" t="inlineStr">
@@ -12925,6 +13056,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K27" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="171" t="inlineStr">
@@ -12969,6 +13105,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K28" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="171" t="inlineStr">
@@ -13013,6 +13154,11 @@
           <t>Web batch 2: commcare-connect opportunity views + forms</t>
         </is>
       </c>
+      <c r="K29" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="171" t="inlineStr">
@@ -13057,6 +13203,11 @@
           <t>Web batch 3: opportunity filters + visit_import + helpers</t>
         </is>
       </c>
+      <c r="K30" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="171" t="inlineStr">
@@ -13101,6 +13252,11 @@
           <t>Web batch 3: opportunity filters + visit_import + helpers</t>
         </is>
       </c>
+      <c r="K31" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="171" t="inlineStr">
@@ -13145,6 +13301,11 @@
           <t>Web batch 3: opportunity filters + visit_import + helpers</t>
         </is>
       </c>
+      <c r="K32" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="171" t="inlineStr">
@@ -13189,6 +13350,11 @@
           <t>Web batch 3: opportunity filters + visit_import + helpers</t>
         </is>
       </c>
+      <c r="K33" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="171" t="inlineStr">
@@ -13233,6 +13399,11 @@
           <t>Web batch 4: program + organization</t>
         </is>
       </c>
+      <c r="K34" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="171" t="inlineStr">
@@ -13277,6 +13448,11 @@
           <t>Web batch 4: program + organization</t>
         </is>
       </c>
+      <c r="K35" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="171" t="inlineStr">
@@ -13321,6 +13497,11 @@
           <t>Web batch 4: program + organization</t>
         </is>
       </c>
+      <c r="K36" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="171" t="inlineStr">
@@ -13365,6 +13546,11 @@
           <t>Web batch 4: program + organization</t>
         </is>
       </c>
+      <c r="K37" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="171" t="inlineStr">
@@ -13409,6 +13595,11 @@
           <t>Web batch 4: program + organization</t>
         </is>
       </c>
+      <c r="K38" s="171" t="inlineStr">
+        <is>
+          <t>N/A (hygiene/discrepancy/automation note)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="171" t="inlineStr">
@@ -13453,6 +13644,11 @@
           <t>Web batch 5: microplanning</t>
         </is>
       </c>
+      <c r="K39" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="171" t="inlineStr">
@@ -13497,6 +13693,11 @@
           <t>Web batch 5: microplanning</t>
         </is>
       </c>
+      <c r="K40" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="171" t="inlineStr">
@@ -13541,6 +13742,11 @@
           <t>Web batch 5: microplanning</t>
         </is>
       </c>
+      <c r="K41" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="171" t="inlineStr">
@@ -13585,6 +13791,11 @@
           <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
         </is>
       </c>
+      <c r="K42" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="171" t="inlineStr">
@@ -13629,6 +13840,11 @@
           <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
         </is>
       </c>
+      <c r="K43" s="171" t="inlineStr">
+        <is>
+          <t>Partial (some eng coverage; confirm with eng)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="171" t="inlineStr">
@@ -13673,6 +13889,11 @@
           <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
         </is>
       </c>
+      <c r="K44" s="171" t="inlineStr">
+        <is>
+          <t>Partial (some eng coverage; confirm with eng)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="171" t="inlineStr">
@@ -13717,6 +13938,11 @@
           <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
         </is>
       </c>
+      <c r="K45" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="171" t="inlineStr">
@@ -13761,6 +13987,11 @@
           <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
         </is>
       </c>
+      <c r="K46" s="171" t="inlineStr">
+        <is>
+          <t>Partial (some eng coverage; confirm with eng)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="171" t="inlineStr">
@@ -13803,6 +14034,11 @@
       <c r="J47" s="171" t="inlineStr">
         <is>
           <t>Web batch 6: users + commcarehq + audit + reports + flags</t>
+        </is>
+      </c>
+      <c r="K47" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -11715,7 +11715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -14039,6 +14039,251 @@
       <c r="K47" s="171" t="inlineStr">
         <is>
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="171" t="inlineStr">
+        <is>
+          <t>GAP-UTC-W-01</t>
+        </is>
+      </c>
+      <c r="B48" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C48" s="171" t="inlineStr">
+        <is>
+          <t>users/oauth2_validator.py - the custom OAuth2 validator (token/scope issuance to mobile clients) has no unit test; security-sensitive auth path</t>
+        </is>
+      </c>
+      <c r="D48" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E48" s="171" t="inlineStr">
+        <is>
+          <t>Unit-test coverage gap (web). Src: users/oauth2_validator.py</t>
+        </is>
+      </c>
+      <c r="F48" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G48" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H48" s="171" t="inlineStr"/>
+      <c r="I48" s="171" t="inlineStr"/>
+      <c r="J48" s="171" t="inlineStr">
+        <is>
+          <t>Web: unit-test-coverage gaps (Shubham dimension)</t>
+        </is>
+      </c>
+      <c r="K48" s="171" t="inlineStr">
+        <is>
+          <t>Eng GAP (no unit test) - dev deliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="171" t="inlineStr">
+        <is>
+          <t>GAP-UTC-W-02</t>
+        </is>
+      </c>
+      <c r="B49" s="171" t="inlineStr">
+        <is>
+          <t>App Credentials</t>
+        </is>
+      </c>
+      <c r="C49" s="171" t="inlineStr">
+        <is>
+          <t>commcarehq/views.py - get_domains / get_application (HQ API-key-driven domain+app fetch) views untested (only the connect_id_client has test_api)</t>
+        </is>
+      </c>
+      <c r="D49" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E49" s="171" t="inlineStr">
+        <is>
+          <t>Unit-test coverage gap (web). Src: commcarehq/views.py</t>
+        </is>
+      </c>
+      <c r="F49" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G49" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H49" s="171" t="inlineStr"/>
+      <c r="I49" s="171" t="inlineStr"/>
+      <c r="J49" s="171" t="inlineStr">
+        <is>
+          <t>Web: unit-test-coverage gaps (Shubham dimension)</t>
+        </is>
+      </c>
+      <c r="K49" s="171" t="inlineStr">
+        <is>
+          <t>Eng GAP (no unit test) - dev deliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="171" t="inlineStr">
+        <is>
+          <t>GAP-UTC-W-03</t>
+        </is>
+      </c>
+      <c r="B50" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C50" s="171" t="inlineStr">
+        <is>
+          <t>flags admin layer untested: flags/views.py (feature_flags/toggle_switch/update_flag), decorators.py, utils.py (only test_flag_models + test_context_processors exist)</t>
+        </is>
+      </c>
+      <c r="D50" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E50" s="171" t="inlineStr">
+        <is>
+          <t>Unit-test coverage gap (web). Src: flags/views.py, decorators.py, utils.py</t>
+        </is>
+      </c>
+      <c r="F50" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G50" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H50" s="171" t="inlineStr"/>
+      <c r="I50" s="171" t="inlineStr"/>
+      <c r="J50" s="171" t="inlineStr">
+        <is>
+          <t>Web: unit-test-coverage gaps (Shubham dimension)</t>
+        </is>
+      </c>
+      <c r="K50" s="171" t="inlineStr">
+        <is>
+          <t>Eng GAP (no unit test) - dev deliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="171" t="inlineStr">
+        <is>
+          <t>GAP-UTC-W-04</t>
+        </is>
+      </c>
+      <c r="B51" s="171" t="inlineStr">
+        <is>
+          <t>Microplanning</t>
+        </is>
+      </c>
+      <c r="C51" s="171" t="inlineStr">
+        <is>
+          <t>microplanning/forms.py - microplanning form validation untested (views/models/serializers/clustering are tested)</t>
+        </is>
+      </c>
+      <c r="D51" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E51" s="171" t="inlineStr">
+        <is>
+          <t>Unit-test coverage gap (web). Src: microplanning/forms.py</t>
+        </is>
+      </c>
+      <c r="F51" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G51" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H51" s="171" t="inlineStr"/>
+      <c r="I51" s="171" t="inlineStr"/>
+      <c r="J51" s="171" t="inlineStr">
+        <is>
+          <t>Web: unit-test-coverage gaps (Shubham dimension)</t>
+        </is>
+      </c>
+      <c r="K51" s="171" t="inlineStr">
+        <is>
+          <t>Eng GAP (no unit test) - dev deliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="171" t="inlineStr">
+        <is>
+          <t>GAP-UTC-W-05</t>
+        </is>
+      </c>
+      <c r="B52" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C52" s="171" t="inlineStr">
+        <is>
+          <t>users/signals.py - user signal handlers untested</t>
+        </is>
+      </c>
+      <c r="D52" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E52" s="171" t="inlineStr">
+        <is>
+          <t>Unit-test coverage gap (web). Src: users/signals.py</t>
+        </is>
+      </c>
+      <c r="F52" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G52" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H52" s="171" t="inlineStr"/>
+      <c r="I52" s="171" t="inlineStr"/>
+      <c r="J52" s="171" t="inlineStr">
+        <is>
+          <t>Web: unit-test-coverage gaps (Shubham dimension)</t>
+        </is>
+      </c>
+      <c r="K52" s="171" t="inlineStr">
+        <is>
+          <t>Eng GAP (no unit test) - dev deliverable</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -4,24 +4,25 @@
   <workbookPr/>
   <sheets>
     <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name=" Test Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Login page" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Programs List page" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Opportunity creation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Opportunity List page" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Opportunity dashboard" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Connect workers page" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Visit verification page" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Invoices List page" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Connect Messaging" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Delivery Reminder Mails" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="App Credentials" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Re-Learn Task" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Microplanning" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Test Tracker Horizontal" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet name="Automation Status" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Gap Analysis" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Automation Coverage" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name=" Test Tracker" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Login page" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Programs List page" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Opportunity creation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Opportunity List page" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Opportunity dashboard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Connect workers page" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Visit verification page" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Invoices List page" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Connect Messaging" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Delivery Reminder Mails" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="App Credentials" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Re-Learn Task" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Microplanning" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Test Tracker Horizontal" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet name="Automation Status" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Gap Analysis" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Automation Coverage" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -884,6 +885,8 @@
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1517,6 +1520,1411 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="18.25" customWidth="1" style="148" min="1" max="1"/>
+    <col width="47" customWidth="1" style="148" min="2" max="2"/>
+    <col width="45.13" customWidth="1" style="148" min="3" max="3"/>
+    <col width="49.38" customWidth="1" style="148" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="166" t="inlineStr">
+        <is>
+          <t>Network Manager</t>
+        </is>
+      </c>
+      <c r="B1" s="153" t="n"/>
+      <c r="C1" s="153" t="n"/>
+      <c r="D1" s="153" t="n"/>
+      <c r="E1" s="153" t="n"/>
+      <c r="F1" s="153" t="n"/>
+      <c r="G1" s="154" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="148">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="54" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C2" s="54" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D2" s="55" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="E2" s="54" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="F2" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA Ticket </t>
+        </is>
+      </c>
+      <c r="G2" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comments </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_1</t>
+        </is>
+      </c>
+      <c r="B3" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm user lands on the Worker Visit Verification Page when they select a worker from the workers list page </t>
+        </is>
+      </c>
+      <c r="C3" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on the connect worker
+6. User lands on the worker visits verification page
+</t>
+        </is>
+      </c>
+      <c r="D3" s="73" t="inlineStr">
+        <is>
+          <t>- User should be able to land on the Worker Visit Verification page when they select any worker form the list 
+- They should be able to review different type of visits under diff tabs that have been submitted on a given day
+- The list should contain the following columns 
+i) Completion Time , Date
+ii) Entity Name
+iii) deliver unit
+iv) payment unit
+v) Last Activity
+vi) Status</t>
+        </is>
+      </c>
+      <c r="E3" s="66" t="n"/>
+      <c r="F3" s="73" t="n"/>
+      <c r="G3" s="73" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_2</t>
+        </is>
+      </c>
+      <c r="B4" s="73" t="inlineStr">
+        <is>
+          <t>User should also view the worker's to date performance at the top of the page</t>
+        </is>
+      </c>
+      <c r="C4" s="73" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to worker visit verification page</t>
+        </is>
+      </c>
+      <c r="D4" s="73" t="inlineStr">
+        <is>
+          <t>- User should be able to view the workers performance at the top of the page and should see the following information 
+(i) Total Visits: Payment units completed so far
+(ii) Pending Tasks
+(iii) Rejected Visits
+(iv) Accrued amount
+(v) Paid Amount</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="n"/>
+      <c r="F4" s="73" t="n"/>
+      <c r="G4" s="73" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_3</t>
+        </is>
+      </c>
+      <c r="B5" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm on selecting an image a pop-up should open with a carousel view </t>
+        </is>
+      </c>
+      <c r="C5" s="73" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to worker visit verification page
+3. Select any visit
+4. Click on the image under visit details</t>
+        </is>
+      </c>
+      <c r="D5" s="73" t="inlineStr">
+        <is>
+          <t>- User should be able to see the images in a carousel view when an image is selected</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="n"/>
+      <c r="F5" s="73" t="n"/>
+      <c r="G5" s="73" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_4</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm user is able to suspend users from an opportunity </t>
+        </is>
+      </c>
+      <c r="C6" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on the connect worker
+6. User lands on the worker visits verification page
+7. Click on user name &gt;&gt; User details with suspend button pop up is displayed
+8. Click on suspend button</t>
+        </is>
+      </c>
+      <c r="D6" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User should be able to suspend any worker from the opportunity by clicking the name of the user on the worker verification screen page </t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="n"/>
+      <c r="F6" s="73" t="n"/>
+      <c r="G6" s="73" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_5</t>
+        </is>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
+          <t>Verify user is able to see two tabs: 
+Visits and Tasks</t>
+        </is>
+      </c>
+      <c r="C7" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to worker visit verification page</t>
+        </is>
+      </c>
+      <c r="D7" s="80" t="inlineStr">
+        <is>
+          <t>- Visit details are shown in visits tab
+- Task details are shown in tasks tab</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="n"/>
+      <c r="F7" s="73" t="n"/>
+      <c r="G7" s="73" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_6</t>
+        </is>
+      </c>
+      <c r="B8" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify submitted visit is auto approved </t>
+        </is>
+      </c>
+      <c r="C8" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Invite a worker from an Opp
+3. Submit few forms from mobile
+4. Navigate to visit verification page</t>
+        </is>
+      </c>
+      <c r="D8" s="80" t="inlineStr">
+        <is>
+          <t>- Submitted visit should get auto approved
+- Visit status should be approved</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="n"/>
+      <c r="F8" s="73" t="n"/>
+      <c r="G8" s="73" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_7</t>
+        </is>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Verify submitted visiit is auto rejected when doesn't satisfy the configured verification rules</t>
+        </is>
+      </c>
+      <c r="C9" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. For an opportunity configure verification rules
+3. Submit the vists from mobile which doesn't satisfy the configured rules
+4. Navigate to visit verification page</t>
+        </is>
+      </c>
+      <c r="D9" s="80" t="inlineStr">
+        <is>
+          <t>- Visits that doesn't satisfy the configured verification rules are auto rejected</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="n"/>
+      <c r="F9" s="73" t="n"/>
+      <c r="G9" s="73" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_8</t>
+        </is>
+      </c>
+      <c r="B10" s="80" t="inlineStr">
+        <is>
+          <t>Verify submitted visit is auto rejected when suspended user make a visit</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to visit verification page &gt;&gt; Click on worker name &gt;&gt; Suspend the user
+3. Submit few forms from mobile using user in step2
+4. Observe the status of submitted visits in step3</t>
+        </is>
+      </c>
+      <c r="D10" s="80" t="inlineStr">
+        <is>
+          <t>- Visits that are submitted by suspended user are auto rejected</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="n"/>
+      <c r="F10" s="73" t="n"/>
+      <c r="G10" s="73" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_9</t>
+        </is>
+      </c>
+      <c r="B11" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify user is able to see the visit details upon clicking on the visit </t>
+        </is>
+      </c>
+      <c r="C11" s="73" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to worker visit verification page
+3. Select any visit</t>
+        </is>
+      </c>
+      <c r="D11" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Following details are shown for visit details:
+Payment unit, Entity id, Entity name
+Verification Parameters
+Map
+</t>
+        </is>
+      </c>
+      <c r="E11" s="66" t="n"/>
+      <c r="F11" s="73" t="n"/>
+      <c r="G11" s="73" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_10</t>
+        </is>
+      </c>
+      <c r="B12" s="104" t="inlineStr">
+        <is>
+          <t>Verify Over Limit status is marked correctly when visits exceeding the configured daily limit are submitted on the same day.</t>
+        </is>
+      </c>
+      <c r="C12" s="104" t="inlineStr">
+        <is>
+          <t>1. login to CCC web UI
+2. Invite connect worker
+3. Complete the daily limit visits in mobile
+4. Again submit the visits exceeding the daily visit limit</t>
+        </is>
+      </c>
+      <c r="D12" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- visits submitted exceeding the daily visit limit should marked as over limit </t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="n"/>
+      <c r="F12" s="73" t="n"/>
+      <c r="G12" s="73" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_11</t>
+        </is>
+      </c>
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>Verify only the first N visits (up to the daily limit) remain valid and any additional visits are flagged as Over Limit.</t>
+        </is>
+      </c>
+      <c r="C13" s="104" t="inlineStr">
+        <is>
+          <t>1. login to CCC web UI
+2. Invite connect worker
+3. Complete the daily limit visits in mobile
+4. Again submit the visits exceeding the daily visit limit</t>
+        </is>
+      </c>
+      <c r="D13" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- visits submitted exceeding the daily visit limit should marked as over limit </t>
+        </is>
+      </c>
+      <c r="E13" s="66" t="n"/>
+      <c r="F13" s="73" t="n"/>
+      <c r="G13" s="73" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_12</t>
+        </is>
+      </c>
+      <c r="B14" s="104" t="inlineStr">
+        <is>
+          <t>Verify Over Limit status is marked correctly when visits exceeding the configured total/max visit limit are submitted.</t>
+        </is>
+      </c>
+      <c r="C14" s="104" t="inlineStr">
+        <is>
+          <t>1. login to CCC web UI
+2. Invite connect worker
+3. Complete the total max limit visits in mobile
+4. Again submit the visits exceeding the daily visit limit</t>
+        </is>
+      </c>
+      <c r="D14" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- visits submitted exceeding the total max limit should marked as over limit </t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="73" t="n"/>
+      <c r="G14" s="73" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_13</t>
+        </is>
+      </c>
+      <c r="B15" s="104" t="inlineStr">
+        <is>
+          <t>Verify only the first N visits (up to the total visit limit) remain valid and any additional visits are flagged as Over Limit.</t>
+        </is>
+      </c>
+      <c r="C15" s="104" t="inlineStr">
+        <is>
+          <t>1. login to CCC web UI
+2. Invite connect worker
+3. Complete the total max limit visits in mobile
+4. Again submit the visits exceeding the daily visit limit</t>
+        </is>
+      </c>
+      <c r="D15" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- visits submitted exceeding the total max limit should marked as over limit </t>
+        </is>
+      </c>
+      <c r="E15" s="66" t="n"/>
+      <c r="F15" s="73" t="n"/>
+      <c r="G15" s="73" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_14</t>
+        </is>
+      </c>
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>Verify no additional visits are accepted when multiple submissions are processed concurrently after the daily limit has been reached.</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Create an opportunity with a configured daily visit limit.
+3. Invite multiple Connect workers or prepare multiple visit submissions from the same worker.
+4. Submit visits until the daily limit is reached.
+5. Immediately submit multiple additional visits concurrently (for example, back-to-back submissions from a single device, multiple devices, or queued submissions syncing together).
+6. Navigate to the Worker Visit Verification page.</t>
+        </is>
+      </c>
+      <c r="D16" s="104" t="inlineStr">
+        <is>
+          <t>- Visits submitted before the daily limit is marked as approved
+- visits submitted after the daily limit is marked as overlimit</t>
+        </is>
+      </c>
+      <c r="E16" s="66" t="n"/>
+      <c r="F16" s="73" t="n"/>
+      <c r="G16" s="73" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_15</t>
+        </is>
+      </c>
+      <c r="B17" s="104" t="inlineStr">
+        <is>
+          <t>Verify no additional visits are accepted when multiple submissions are processed concurrently after the total visit limit has been reached.</t>
+        </is>
+      </c>
+      <c r="C17" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Create an opportunity with a configured total/max visit limit.
+3. Invite Connect workers.
+4. Submit visits until the total visit limit is reached.
+5. Immediately submit multiple additional visits concurrently (multiple devices, rapid submissions, or queued sync submissions).
+6. Navigate to the Worker Visit Verification page.</t>
+        </is>
+      </c>
+      <c r="D17" s="104" t="inlineStr">
+        <is>
+          <t>- Visits submitted before the total max limit is marked as approved
+- visits submitted after the total max limit is marked as overlimit</t>
+        </is>
+      </c>
+      <c r="E17" s="66" t="n"/>
+      <c r="F17" s="73" t="n"/>
+      <c r="G17" s="73" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_16</t>
+        </is>
+      </c>
+      <c r="B18" s="104" t="inlineStr">
+        <is>
+          <t>Verify visits exceeding the daily limit are displayed with an Over Limit status on the Visit Verification screen.</t>
+        </is>
+      </c>
+      <c r="C18" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Configure a daily visit limit for the opportunity.
+3. Invite Connect workers.
+4. Submit visits exceeding the configured daily visit limit.
+5. Open the Worker Visit Verification page.
+6. Locate visits marked as Over Limit.
+7. Hover over the visit count indicator.</t>
+        </is>
+      </c>
+      <c r="D18" s="104" t="inlineStr">
+        <is>
+          <t>- when mouse hover on the count of visits overlimit count should be displayed</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="n"/>
+      <c r="F18" s="73" t="n"/>
+      <c r="G18" s="73" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_17</t>
+        </is>
+      </c>
+      <c r="B19" s="104" t="inlineStr">
+        <is>
+          <t>Verify visits exceeding the total visit limit are displayed with an Over Limit status on the Visit Verification screen.</t>
+        </is>
+      </c>
+      <c r="C19" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Configure a total/max visit limit for the opportunity.
+3. Invite Connect workers.
+4. Submit visits exceeding the configured total visit limit.
+5. Open the Worker Visit Verification page.
+6. Locate visits marked as Over Limit.
+7. Hover over the visit count indicator.</t>
+        </is>
+      </c>
+      <c r="D19" s="104" t="inlineStr">
+        <is>
+          <t>- when mouse hover on the count of visits overlimit count should be displayed</t>
+        </is>
+      </c>
+      <c r="E19" s="66" t="n"/>
+      <c r="F19" s="73" t="n"/>
+      <c r="G19" s="73" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_18</t>
+        </is>
+      </c>
+      <c r="B20" s="104" t="inlineStr">
+        <is>
+          <t>Verify the count of valid visits and Over Limit visits displayed on the Visit Verification screen is accurate after concurrent submissions.</t>
+        </is>
+      </c>
+      <c r="C20" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Configure daily and total visit limits.
+3. Invite Connect workers.
+4. Submit multiple visits concurrently after the configured limit has been reached.
+5. Open the Worker Visit Verification page.
+6. Verify the visit summary counts.
+7. Hover over the count indicators if applicable.</t>
+        </is>
+      </c>
+      <c r="D20" s="104" t="inlineStr">
+        <is>
+          <t>- when mouse hover on the count of visits overlimit count should be displayed</t>
+        </is>
+      </c>
+      <c r="E20" s="66" t="n"/>
+      <c r="F20" s="73" t="n"/>
+      <c r="G20" s="73" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_19</t>
+        </is>
+      </c>
+      <c r="B21" s="104" t="inlineStr">
+        <is>
+          <t>Verify visits submitted through queued/offline sync are correctly evaluated against the daily limit when multiple submissions are processed together.</t>
+        </is>
+      </c>
+      <c r="C21" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Configure a daily visit limit.
+3. Invite a Connect worker.
+4. Put the mobile device in offline mode.
+5. Submit multiple visits while offline, including submissions exceeding the daily limit.
+6. Restore network connectivity and allow all queued visits to sync together.
+7. Open the Worker Visit Verification page.</t>
+        </is>
+      </c>
+      <c r="D21" s="104" t="inlineStr">
+        <is>
+          <t>- Visit that are in daily limit marked as approved
+- Visits that exceeds daily limit are marked as over limit</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="n"/>
+      <c r="F21" s="73" t="n"/>
+      <c r="G21" s="73" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_20</t>
+        </is>
+      </c>
+      <c r="B22" s="104" t="inlineStr">
+        <is>
+          <t>Verify visits submitted through queued/offline sync are correctly evaluated against the total visit limit when multiple submissions are processed together.</t>
+        </is>
+      </c>
+      <c r="C22" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI.
+2. Configure a total/max visit limit.
+3. Invite a Connect worker.
+4. Put the mobile device in offline mode.
+5. Submit multiple visits while offline, including submissions exceeding the total visit limit.
+6. Restore network connectivity and allow all queued visits to sync together.
+7. Open the Worker Visit Verification page.</t>
+        </is>
+      </c>
+      <c r="D22" s="104" t="inlineStr">
+        <is>
+          <t>- Visit that are in total/max limit marked as approved
+- Visits that exceeds total/max limit are marked as over limit</t>
+        </is>
+      </c>
+      <c r="E22" s="66" t="n"/>
+      <c r="F22" s="73" t="n"/>
+      <c r="G22" s="73" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_21</t>
+        </is>
+      </c>
+      <c r="B23" s="104" t="inlineStr">
+        <is>
+          <t>Verify trial visit submission</t>
+        </is>
+      </c>
+      <c r="C23" s="104" t="inlineStr">
+        <is>
+          <t>1. Submit visits befor the opp start date</t>
+        </is>
+      </c>
+      <c r="D23" s="104" t="inlineStr">
+        <is>
+          <t>- visits submitted before opp start date is marked as trial</t>
+        </is>
+      </c>
+      <c r="E23" s="66" t="n"/>
+      <c r="F23" s="73" t="n"/>
+      <c r="G23" s="73" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_22</t>
+        </is>
+      </c>
+      <c r="B24" s="104" t="inlineStr">
+        <is>
+          <t>Verify post end date submissions</t>
+        </is>
+      </c>
+      <c r="C24" s="104" t="inlineStr">
+        <is>
+          <t>1. Submit the visits after the opp has ended</t>
+        </is>
+      </c>
+      <c r="D24" s="104" t="inlineStr">
+        <is>
+          <t>- visits submitted after opp ended is not updated in web and no progress is gained for an opp</t>
+        </is>
+      </c>
+      <c r="E24" s="66" t="n"/>
+      <c r="F24" s="73" t="n"/>
+      <c r="G24" s="73" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_23</t>
+        </is>
+      </c>
+      <c r="B25" s="104" t="inlineStr">
+        <is>
+          <t>Verify duplicate visits are billable only when visits are approved by NM and agreed by PM</t>
+        </is>
+      </c>
+      <c r="C25" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Invite user for an Opp
+3. Submit duplicate forms
+4. Approve visit by NM user 
+5. Agree visit by PM user
+</t>
+        </is>
+      </c>
+      <c r="D25" s="104" t="inlineStr">
+        <is>
+          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
+        </is>
+      </c>
+      <c r="E25" s="66" t="n"/>
+      <c r="F25" s="73" t="n"/>
+      <c r="G25" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_24</t>
+        </is>
+      </c>
+      <c r="B26" s="104" t="inlineStr">
+        <is>
+          <t>Verify duplicate visits are not billable when PM is not agreed</t>
+        </is>
+      </c>
+      <c r="C26" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Invite user for an Opp
+3. Submit duplicate forms
+4. Approve visit by NM user 
+</t>
+        </is>
+      </c>
+      <c r="D26" s="104" t="inlineStr">
+        <is>
+          <t>- Visits that aren't agreed by Pm are not eligilble for payment</t>
+        </is>
+      </c>
+      <c r="E26" s="66" t="n"/>
+      <c r="F26" s="73" t="n"/>
+      <c r="G26" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_25</t>
+        </is>
+      </c>
+      <c r="B27" s="104" t="inlineStr">
+        <is>
+          <t>Verfiy the visits are billable only when agreed by PM using import bulk</t>
+        </is>
+      </c>
+      <c r="C27" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CC web UI
+2. Invite user for an opp
+3. Submit few duplicate visits
+4. Navigate to connect workers page &gt;&gt; Download the PM review csv export
+5. Make chnages are PM agreed for visits and import
+</t>
+        </is>
+      </c>
+      <c r="D27" s="104" t="inlineStr">
+        <is>
+          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
+        </is>
+      </c>
+      <c r="E27" s="66" t="n"/>
+      <c r="F27" s="73" t="n"/>
+      <c r="G27" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_26</t>
+        </is>
+      </c>
+      <c r="B28" s="104" t="inlineStr">
+        <is>
+          <t>Verfiy the visits are not billable when disagreed by PM using import bulk</t>
+        </is>
+      </c>
+      <c r="C28" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CC web UI
+2. Invite user for an opp
+3. Submit few duplicate visits
+4. Navigate to connect workers page &gt;&gt; Download the PM review csv export
+5. Make chnages are PM disagreed for visits and import
+</t>
+        </is>
+      </c>
+      <c r="D28" s="104" t="inlineStr">
+        <is>
+          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
+        </is>
+      </c>
+      <c r="E28" s="66" t="n"/>
+      <c r="F28" s="73" t="n"/>
+      <c r="G28" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_27</t>
+        </is>
+      </c>
+      <c r="B29" s="104" t="inlineStr">
+        <is>
+          <t>Verify combination of agreed/disgareed for duplicate visits using import</t>
+        </is>
+      </c>
+      <c r="C29" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CC web UI
+2. Invite user for an opp
+3. Submit few duplicate visits
+4. Navigate to connect workers page &gt;&gt; Download the PM review csv export
+5. Make chnages are PM agreed for few visits, disagree some visits and import
+</t>
+        </is>
+      </c>
+      <c r="D29" s="104" t="inlineStr">
+        <is>
+          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
+        </is>
+      </c>
+      <c r="E29" s="66" t="n"/>
+      <c r="F29" s="73" t="n"/>
+      <c r="G29" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_28</t>
+        </is>
+      </c>
+      <c r="B30" s="104" t="inlineStr">
+        <is>
+          <t>Verify the invoice generating should contains only visits that are agreed by PM</t>
+        </is>
+      </c>
+      <c r="C30" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Loin to CCC web UI
+2. Navigate to view invoices page
+3. Click create invoice &gt;&gt; service delivery
+4. Select date </t>
+        </is>
+      </c>
+      <c r="D30" s="104" t="inlineStr">
+        <is>
+          <t>- The visits that are approved by NM and agreed by PM are listed for invoice generation</t>
+        </is>
+      </c>
+      <c r="E30" s="66" t="n"/>
+      <c r="F30" s="73" t="n"/>
+      <c r="G30" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_29</t>
+        </is>
+      </c>
+      <c r="B31" s="104" t="inlineStr">
+        <is>
+          <t>Verify payment is accrued only when all required visits and atleast one optional visit (if any) are agreed by PM</t>
+        </is>
+      </c>
+      <c r="C31" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Submit all required visits
+3. Submit atleast one optioanl visit
+4. Approve by NM and agree by PM</t>
+        </is>
+      </c>
+      <c r="D31" s="104" t="inlineStr">
+        <is>
+          <t>- payment should be accrued only when all req visits and atleast one optional visit is agreed by PM</t>
+        </is>
+      </c>
+      <c r="E31" s="66" t="n"/>
+      <c r="F31" s="73" t="n"/>
+      <c r="G31" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_30</t>
+        </is>
+      </c>
+      <c r="B32" s="104" t="inlineStr">
+        <is>
+          <t>Verify payment is not accrued when all required visits and atleast one optional visit (if any) are agreed by PM</t>
+        </is>
+      </c>
+      <c r="C32" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Submit all required visits
+3. Submit atleast one optioanl visit
+4. Approve by NM 
+5. Don't agree all visits by PM</t>
+        </is>
+      </c>
+      <c r="D32" s="104" t="inlineStr">
+        <is>
+          <t>- payment should not be accrued</t>
+        </is>
+      </c>
+      <c r="E32" s="66" t="n"/>
+      <c r="F32" s="73" t="n"/>
+      <c r="G32" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_31</t>
+        </is>
+      </c>
+      <c r="B33" s="86" t="inlineStr">
+        <is>
+          <t>Verfiy user is able to reject the visits (NM user)</t>
+        </is>
+      </c>
+      <c r="C33" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to visit verification page
+3. Click on visit details &gt;&gt; Click on reject</t>
+        </is>
+      </c>
+      <c r="D33" s="104" t="inlineStr">
+        <is>
+          <t>- Status should get update to rejected</t>
+        </is>
+      </c>
+      <c r="E33" s="66" t="n"/>
+      <c r="F33" s="87" t="n"/>
+      <c r="G33" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_32</t>
+        </is>
+      </c>
+      <c r="B34" s="86" t="inlineStr">
+        <is>
+          <t>Verify user is able to approve the visits (NM user)</t>
+        </is>
+      </c>
+      <c r="C34" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to visit verification page
+3. Click on visit details &gt;&gt; Click on approve</t>
+        </is>
+      </c>
+      <c r="D34" s="104" t="inlineStr">
+        <is>
+          <t>- Status should get update to approved</t>
+        </is>
+      </c>
+      <c r="E34" s="66" t="n"/>
+      <c r="F34" s="87" t="n"/>
+      <c r="G34" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_33</t>
+        </is>
+      </c>
+      <c r="B35" s="86" t="inlineStr">
+        <is>
+          <t>Verify user is able to agree the visits (PM user)</t>
+        </is>
+      </c>
+      <c r="C35" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to visit verification page
+3. Click on visit details &gt;&gt; Click on agree</t>
+        </is>
+      </c>
+      <c r="D35" s="104" t="inlineStr">
+        <is>
+          <t>- when PM approved visit paymnet amount is accrued</t>
+        </is>
+      </c>
+      <c r="E35" s="66" t="n"/>
+      <c r="F35" s="87" t="n"/>
+      <c r="G35" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_34</t>
+        </is>
+      </c>
+      <c r="B36" s="86" t="inlineStr">
+        <is>
+          <t>Verify user is able to disagree the visits (PM user)</t>
+        </is>
+      </c>
+      <c r="C36" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to visit verification page
+3. Click on visit details &gt;&gt; Click on disagree</t>
+        </is>
+      </c>
+      <c r="D36" s="104" t="inlineStr">
+        <is>
+          <t>- When PM disagreed no paymnet is accrued</t>
+        </is>
+      </c>
+      <c r="E36" s="66" t="n"/>
+      <c r="F36" s="87" t="n"/>
+      <c r="G36" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="85" t="inlineStr">
+        <is>
+          <t>Worker Visit Verification Page_35</t>
+        </is>
+      </c>
+      <c r="B37" s="86" t="inlineStr">
+        <is>
+          <t>Verify user is not able to agree the visit that is disagreed and vice versa</t>
+        </is>
+      </c>
+      <c r="C37" s="104" t="n"/>
+      <c r="D37" s="104" t="n"/>
+      <c r="E37" s="66" t="n"/>
+      <c r="F37" s="87" t="n"/>
+      <c r="G37" s="73" t="inlineStr">
+        <is>
+          <t>This test is for opp created before june 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="166" t="inlineStr">
+        <is>
+          <t>Payment eligibility</t>
+        </is>
+      </c>
+      <c r="B38" s="153" t="n"/>
+      <c r="C38" s="153" t="n"/>
+      <c r="D38" s="153" t="n"/>
+      <c r="E38" s="153" t="n"/>
+      <c r="F38" s="153" t="n"/>
+      <c r="G38" s="154" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_01</t>
+        </is>
+      </c>
+      <c r="B39" s="104" t="inlineStr">
+        <is>
+          <t>Verify user becomes eligible for payment when all required visits are approved</t>
+        </is>
+      </c>
+      <c r="C39" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI. 
+2. Create or select an opportunity with required delivery units configured. 
+3. Invite a PID user to the opportunity. 
+4. Login to the mobile app with the PID user. 
+5. Claim the job and submit forms for all required visits.
+ 6. Approve the visits from the web/admin panel.</t>
+        </is>
+      </c>
+      <c r="D39" s="104" t="inlineStr">
+        <is>
+          <t>User becomes eligible for payment once all required visits are approved.</t>
+        </is>
+      </c>
+      <c r="E39" s="66" t="n"/>
+      <c r="F39" s="73" t="n"/>
+      <c r="G39" s="73" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_02</t>
+        </is>
+      </c>
+      <c r="B40" s="104" t="inlineStr">
+        <is>
+          <t>Verify user is not eligible for payment if any required visit is not approved</t>
+        </is>
+      </c>
+      <c r="C40" s="104" t="inlineStr">
+        <is>
+          <t>1. Login to CCC Web UI. 
+2. Create an opportunity with multiple required visits. 
+3. Invite a PID user. 
+4. Submit all required visits from mobile. 
+5. Approve only some of the required visits and leave at least one pending/rejected.</t>
+        </is>
+      </c>
+      <c r="D40" s="104" t="inlineStr">
+        <is>
+          <t>User should not be eligible for payment if any required visit is not approved.</t>
+        </is>
+      </c>
+      <c r="E40" s="66" t="n"/>
+      <c r="F40" s="73" t="n"/>
+      <c r="G40" s="73" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_03</t>
+        </is>
+      </c>
+      <c r="B41" s="104" t="inlineStr">
+        <is>
+          <t>Verify payment eligibility when all required visits and at least one optional visit are approved</t>
+        </is>
+      </c>
+      <c r="C41" s="104" t="inlineStr">
+        <is>
+          <t>1. Create an opportunity with required and optional delivery units. 
+2. Invite PID user and claim job from mobile. 
+3. Submit required visit forms. 
+4. Submit at least one optional visit form. 
+5. Approve all required visits and one optional visit.</t>
+        </is>
+      </c>
+      <c r="D41" s="104" t="inlineStr">
+        <is>
+          <t>User becomes eligible for payment.</t>
+        </is>
+      </c>
+      <c r="E41" s="66" t="n"/>
+      <c r="F41" s="73" t="n"/>
+      <c r="G41" s="73" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_04</t>
+        </is>
+      </c>
+      <c r="B42" s="104" t="inlineStr">
+        <is>
+          <t>Verify worker is not eligible if optional visits exist but none are approved</t>
+        </is>
+      </c>
+      <c r="C42" s="104" t="inlineStr">
+        <is>
+          <t>1. Create opportunity with required and optional visits. 
+2. Submit all required visits. 
+3. Submit optional visits but do not approve them.
+ 4. Approve only required visits.</t>
+        </is>
+      </c>
+      <c r="D42" s="104" t="inlineStr">
+        <is>
+          <t>User should not be eligible for payment because no optional visit is approved.</t>
+        </is>
+      </c>
+      <c r="E42" s="66" t="n"/>
+      <c r="F42" s="73" t="n"/>
+      <c r="G42" s="73" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_06</t>
+        </is>
+      </c>
+      <c r="B43" s="104" t="inlineStr">
+        <is>
+          <t>Verify auto-approval system correctly marks eligibility</t>
+        </is>
+      </c>
+      <c r="C43" s="104" t="inlineStr">
+        <is>
+          <t>1. Enable auto approval for visits. 
+2. Invite PID user. 
+3. Submit required and optional visits from mobile. 
+4. Allow system to auto approve visits.</t>
+        </is>
+      </c>
+      <c r="D43" s="104" t="inlineStr">
+        <is>
+          <t>System automatically marks user as eligible for payment when conditions are satisfied.</t>
+        </is>
+      </c>
+      <c r="E43" s="66" t="n"/>
+      <c r="F43" s="73" t="n"/>
+      <c r="G43" s="73" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_07</t>
+        </is>
+      </c>
+      <c r="B44" s="104" t="inlineStr">
+        <is>
+          <t>Verify manual approval works with new eligibility logic</t>
+        </is>
+      </c>
+      <c r="C44" s="104" t="inlineStr">
+        <is>
+          <t>1. Create opportunity with required and optional visits. 
+2. Submit visits from mobile. 
+3. Admin manually approves required visits and at least one optional visit.</t>
+        </is>
+      </c>
+      <c r="D44" s="104" t="inlineStr">
+        <is>
+          <t>User becomes eligible for payment after manual approval.</t>
+        </is>
+      </c>
+      <c r="E44" s="66" t="n"/>
+      <c r="F44" s="73" t="n"/>
+      <c r="G44" s="73" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_08</t>
+        </is>
+      </c>
+      <c r="B45" s="104" t="inlineStr">
+        <is>
+          <t>Verify optional visit approved but required visits missing</t>
+        </is>
+      </c>
+      <c r="C45" s="104" t="inlineStr">
+        <is>
+          <t>1. Create opportunity with required and optional visits. 
+2. Submit optional visit first.
+3. Approve optional visit but leave required visits pending.</t>
+        </is>
+      </c>
+      <c r="D45" s="104" t="inlineStr">
+        <is>
+          <t>User should not be eligible for payment until all required visits are approved.</t>
+        </is>
+      </c>
+      <c r="E45" s="66" t="n"/>
+      <c r="F45" s="73" t="n"/>
+      <c r="G45" s="73" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="58" t="inlineStr">
+        <is>
+          <t>Payment eligibility_09</t>
+        </is>
+      </c>
+      <c r="B46" s="104" t="inlineStr">
+        <is>
+          <t>Verify rejected visits do not count toward payment eligibility</t>
+        </is>
+      </c>
+      <c r="C46" s="104" t="inlineStr">
+        <is>
+          <t>1. Submit required visits from mobile. 
+2. Reject one of the required visits from web.</t>
+        </is>
+      </c>
+      <c r="D46" s="104" t="inlineStr">
+        <is>
+          <t>User should not be eligible for payment when a required visit is rejected.</t>
+        </is>
+      </c>
+      <c r="E46" s="66" t="n"/>
+      <c r="F46" s="73" t="n"/>
+      <c r="G46" s="73" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="58" t="n"/>
+      <c r="B47" s="88" t="n"/>
+      <c r="C47" s="88" t="n"/>
+      <c r="D47" s="68" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="89" t="n"/>
+      <c r="G47" s="89" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E3:E37 E39:E47">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="6">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="7">
+      <formula>"Blocking"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E3:E37 E39:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,N/A,Blocking"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
@@ -2729,7 +4137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3123,7 +4531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3428,7 +4836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3587,7 +4995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4771,7 +6179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6865,7 +8273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -11333,7 +12741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12137,13 +13545,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -12157,6 +13565,7 @@
     <col width="40" customWidth="1" style="148" min="9" max="9"/>
     <col width="28" customWidth="1" style="148" min="10" max="10"/>
     <col width="46" customWidth="1" style="148" min="11" max="11"/>
+    <col width="40" customWidth="1" style="148" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12215,6 +13624,11 @@
           <t>Eng Coverage</t>
         </is>
       </c>
+      <c r="L1" s="170" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="171" t="inlineStr">
@@ -12264,6 +13678,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L2" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="171" t="inlineStr">
@@ -12313,6 +13732,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L3" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="171" t="inlineStr">
@@ -12362,6 +13786,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L4" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="171" t="inlineStr">
@@ -12411,6 +13840,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L5" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="171" t="inlineStr">
@@ -12460,6 +13894,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L6" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="171" t="inlineStr">
@@ -12509,6 +13948,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L7" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="171" t="inlineStr">
@@ -12558,6 +14002,11 @@
           <t>Partial (some eng coverage; confirm with eng)</t>
         </is>
       </c>
+      <c r="L8" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="171" t="inlineStr">
@@ -12607,6 +14056,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L9" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="171" t="inlineStr">
@@ -12656,6 +14110,11 @@
           <t>Partial (some eng coverage; confirm with eng)</t>
         </is>
       </c>
+      <c r="L10" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="171" t="inlineStr">
@@ -12705,6 +14164,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L11" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="171" t="inlineStr">
@@ -12754,6 +14218,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L12" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="171" t="inlineStr">
@@ -12803,6 +14272,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L13" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="171" t="inlineStr">
@@ -12852,6 +14326,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L14" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="171" t="inlineStr">
@@ -12901,6 +14380,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L15" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="171" t="inlineStr">
@@ -12950,6 +14434,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L16" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="171" t="inlineStr">
@@ -12999,6 +14488,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L17" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="171" t="inlineStr">
@@ -13048,6 +14542,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L18" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="171" t="inlineStr">
@@ -13097,6 +14596,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L19" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="171" t="inlineStr">
@@ -13146,6 +14650,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L20" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="171" t="inlineStr">
@@ -13195,6 +14704,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L21" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="171" t="inlineStr">
@@ -13244,6 +14758,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L22" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="171" t="inlineStr">
@@ -13293,6 +14812,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L23" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="171" t="inlineStr">
@@ -13342,6 +14866,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L24" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="171" t="inlineStr">
@@ -13391,6 +14920,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L25" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="171" t="inlineStr">
@@ -13440,6 +14974,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L26" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="171" t="inlineStr">
@@ -13489,6 +15028,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L27" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="171" t="inlineStr">
@@ -13538,6 +15082,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L28" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="171" t="inlineStr">
@@ -13587,6 +15136,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L29" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="171" t="inlineStr">
@@ -13636,6 +15190,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L30" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="171" t="inlineStr">
@@ -13685,6 +15244,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L31" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="171" t="inlineStr">
@@ -13734,6 +15298,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L32" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="171" t="inlineStr">
@@ -13783,6 +15352,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L33" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="171" t="inlineStr">
@@ -13832,6 +15406,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L34" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="171" t="inlineStr">
@@ -13881,6 +15460,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L35" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="171" t="inlineStr">
@@ -13930,6 +15514,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L36" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="171" t="inlineStr">
@@ -13979,6 +15568,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L37" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="171" t="inlineStr">
@@ -14028,6 +15622,11 @@
           <t>N/A (hygiene/discrepancy/automation note)</t>
         </is>
       </c>
+      <c r="L38" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="171" t="inlineStr">
@@ -14077,6 +15676,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L39" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="171" t="inlineStr">
@@ -14126,6 +15730,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L40" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="171" t="inlineStr">
@@ -14175,6 +15784,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L41" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="171" t="inlineStr">
@@ -14224,6 +15838,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L42" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="171" t="inlineStr">
@@ -14273,6 +15892,11 @@
           <t>Partial (some eng coverage; confirm with eng)</t>
         </is>
       </c>
+      <c r="L43" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="171" t="inlineStr">
@@ -14322,6 +15946,11 @@
           <t>Partial (some eng coverage; confirm with eng)</t>
         </is>
       </c>
+      <c r="L44" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="171" t="inlineStr">
@@ -14371,6 +16000,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L45" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="171" t="inlineStr">
@@ -14420,6 +16054,11 @@
           <t>Partial (some eng coverage; confirm with eng)</t>
         </is>
       </c>
+      <c r="L46" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="171" t="inlineStr">
@@ -14469,6 +16108,11 @@
           <t>Eng-covered (logic) - QA e2e only if critical journey</t>
         </is>
       </c>
+      <c r="L47" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="171" t="inlineStr">
@@ -14518,6 +16162,11 @@
           <t>Eng GAP (no unit test) - dev deliverable</t>
         </is>
       </c>
+      <c r="L48" s="171" t="inlineStr">
+        <is>
+          <t>Dev: add unit test</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="171" t="inlineStr">
@@ -14567,6 +16216,11 @@
           <t>Eng GAP (no unit test) - dev deliverable</t>
         </is>
       </c>
+      <c r="L49" s="171" t="inlineStr">
+        <is>
+          <t>Dev: add unit test</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="171" t="inlineStr">
@@ -14616,6 +16270,11 @@
           <t>Eng GAP (no unit test) - dev deliverable</t>
         </is>
       </c>
+      <c r="L50" s="171" t="inlineStr">
+        <is>
+          <t>Dev: add unit test</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="171" t="inlineStr">
@@ -14665,6 +16324,11 @@
           <t>Eng GAP (no unit test) - dev deliverable</t>
         </is>
       </c>
+      <c r="L51" s="171" t="inlineStr">
+        <is>
+          <t>Dev: add unit test</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="171" t="inlineStr">
@@ -14712,6 +16376,11 @@
       <c r="K52" s="171" t="inlineStr">
         <is>
           <t>Eng GAP (no unit test) - dev deliverable</t>
+        </is>
+      </c>
+      <c r="L52" s="171" t="inlineStr">
+        <is>
+          <t>Dev: add unit test</t>
         </is>
       </c>
     </row>
@@ -14720,7 +16389,143 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" style="148" min="1" max="1"/>
+    <col width="12" customWidth="1" style="148" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="174" t="inlineStr">
+        <is>
+          <t>Gap Analysis — Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="175" t="inlineStr">
+        <is>
+          <t>OUTPUT 1 — MTP completeness (all functional gaps: add to the MTP)</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which already eng-covered (add to MTP only, do NOT automate)</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP only*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which QA to automate (see Output 2)</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="175" t="inlineStr">
+        <is>
+          <t>OUTPUT 2 — QA automation backlog (functional gaps NOT eng-covered)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   QA-owned (real device/SMS/push - eng cannot cover)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*QA-owned*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Automatable, confirm w/ eng (partial coverage)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*confirm w/ eng*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="175" t="inlineStr">
+        <is>
+          <t>DEV deliverable — unit-test-coverage gaps (eng to add unit tests)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Dev:*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="175" t="inlineStr">
+        <is>
+          <t>CROSS-CUTTING — reconcile plan/code (hygiene/discrepancy)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Reconcile*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="175" t="inlineStr">
+        <is>
+          <t>TOTAL Gap Analysis rows</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>COUNTA('Gap Analysis'!$L$2:$L$1000)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27510,7 +29315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -28541,7 +30346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -28885,7 +30690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -29416,7 +31221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30308,7 +32113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31210,7 +33015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31954,7 +33759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33218,1409 +35023,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G47"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="18.25" customWidth="1" style="148" min="1" max="1"/>
-    <col width="47" customWidth="1" style="148" min="2" max="2"/>
-    <col width="45.13" customWidth="1" style="148" min="3" max="3"/>
-    <col width="49.38" customWidth="1" style="148" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="166" t="inlineStr">
-        <is>
-          <t>Network Manager</t>
-        </is>
-      </c>
-      <c r="B1" s="153" t="n"/>
-      <c r="C1" s="153" t="n"/>
-      <c r="D1" s="153" t="n"/>
-      <c r="E1" s="153" t="n"/>
-      <c r="F1" s="153" t="n"/>
-      <c r="G1" s="154" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="148">
-      <c r="A2" s="54" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="54" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C2" s="54" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D2" s="55" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E2" s="54" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="F2" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QA Ticket </t>
-        </is>
-      </c>
-      <c r="G2" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comments </t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_1</t>
-        </is>
-      </c>
-      <c r="B3" s="73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirm user lands on the Worker Visit Verification Page when they select a worker from the workers list page </t>
-        </is>
-      </c>
-      <c r="C3" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on the connect worker
-6. User lands on the worker visits verification page
-</t>
-        </is>
-      </c>
-      <c r="D3" s="73" t="inlineStr">
-        <is>
-          <t>- User should be able to land on the Worker Visit Verification page when they select any worker form the list 
-- They should be able to review different type of visits under diff tabs that have been submitted on a given day
-- The list should contain the following columns 
-i) Completion Time , Date
-ii) Entity Name
-iii) deliver unit
-iv) payment unit
-v) Last Activity
-vi) Status</t>
-        </is>
-      </c>
-      <c r="E3" s="66" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_2</t>
-        </is>
-      </c>
-      <c r="B4" s="73" t="inlineStr">
-        <is>
-          <t>User should also view the worker's to date performance at the top of the page</t>
-        </is>
-      </c>
-      <c r="C4" s="73" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to worker visit verification page</t>
-        </is>
-      </c>
-      <c r="D4" s="73" t="inlineStr">
-        <is>
-          <t>- User should be able to view the workers performance at the top of the page and should see the following information 
-(i) Total Visits: Payment units completed so far
-(ii) Pending Tasks
-(iii) Rejected Visits
-(iv) Accrued amount
-(v) Paid Amount</t>
-        </is>
-      </c>
-      <c r="E4" s="66" t="n"/>
-      <c r="F4" s="73" t="n"/>
-      <c r="G4" s="73" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_3</t>
-        </is>
-      </c>
-      <c r="B5" s="73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirm on selecting an image a pop-up should open with a carousel view </t>
-        </is>
-      </c>
-      <c r="C5" s="73" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to worker visit verification page
-3. Select any visit
-4. Click on the image under visit details</t>
-        </is>
-      </c>
-      <c r="D5" s="73" t="inlineStr">
-        <is>
-          <t>- User should be able to see the images in a carousel view when an image is selected</t>
-        </is>
-      </c>
-      <c r="E5" s="66" t="n"/>
-      <c r="F5" s="73" t="n"/>
-      <c r="G5" s="73" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_4</t>
-        </is>
-      </c>
-      <c r="B6" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirm user is able to suspend users from an opportunity </t>
-        </is>
-      </c>
-      <c r="C6" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on the connect worker
-6. User lands on the worker visits verification page
-7. Click on user name &gt;&gt; User details with suspend button pop up is displayed
-8. Click on suspend button</t>
-        </is>
-      </c>
-      <c r="D6" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User should be able to suspend any worker from the opportunity by clicking the name of the user on the worker verification screen page </t>
-        </is>
-      </c>
-      <c r="E6" s="66" t="n"/>
-      <c r="F6" s="73" t="n"/>
-      <c r="G6" s="73" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_5</t>
-        </is>
-      </c>
-      <c r="B7" s="80" t="inlineStr">
-        <is>
-          <t>Verify user is able to see two tabs: 
-Visits and Tasks</t>
-        </is>
-      </c>
-      <c r="C7" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to worker visit verification page</t>
-        </is>
-      </c>
-      <c r="D7" s="80" t="inlineStr">
-        <is>
-          <t>- Visit details are shown in visits tab
-- Task details are shown in tasks tab</t>
-        </is>
-      </c>
-      <c r="E7" s="66" t="n"/>
-      <c r="F7" s="73" t="n"/>
-      <c r="G7" s="73" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_6</t>
-        </is>
-      </c>
-      <c r="B8" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify submitted visit is auto approved </t>
-        </is>
-      </c>
-      <c r="C8" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Invite a worker from an Opp
-3. Submit few forms from mobile
-4. Navigate to visit verification page</t>
-        </is>
-      </c>
-      <c r="D8" s="80" t="inlineStr">
-        <is>
-          <t>- Submitted visit should get auto approved
-- Visit status should be approved</t>
-        </is>
-      </c>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="73" t="n"/>
-      <c r="G8" s="73" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_7</t>
-        </is>
-      </c>
-      <c r="B9" s="80" t="inlineStr">
-        <is>
-          <t>Verify submitted visiit is auto rejected when doesn't satisfy the configured verification rules</t>
-        </is>
-      </c>
-      <c r="C9" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. For an opportunity configure verification rules
-3. Submit the vists from mobile which doesn't satisfy the configured rules
-4. Navigate to visit verification page</t>
-        </is>
-      </c>
-      <c r="D9" s="80" t="inlineStr">
-        <is>
-          <t>- Visits that doesn't satisfy the configured verification rules are auto rejected</t>
-        </is>
-      </c>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="73" t="n"/>
-      <c r="G9" s="73" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_8</t>
-        </is>
-      </c>
-      <c r="B10" s="80" t="inlineStr">
-        <is>
-          <t>Verify submitted visit is auto rejected when suspended user make a visit</t>
-        </is>
-      </c>
-      <c r="C10" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to visit verification page &gt;&gt; Click on worker name &gt;&gt; Suspend the user
-3. Submit few forms from mobile using user in step2
-4. Observe the status of submitted visits in step3</t>
-        </is>
-      </c>
-      <c r="D10" s="80" t="inlineStr">
-        <is>
-          <t>- Visits that are submitted by suspended user are auto rejected</t>
-        </is>
-      </c>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="73" t="n"/>
-      <c r="G10" s="73" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_9</t>
-        </is>
-      </c>
-      <c r="B11" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify user is able to see the visit details upon clicking on the visit </t>
-        </is>
-      </c>
-      <c r="C11" s="73" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to worker visit verification page
-3. Select any visit</t>
-        </is>
-      </c>
-      <c r="D11" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- Following details are shown for visit details:
-Payment unit, Entity id, Entity name
-Verification Parameters
-Map
-</t>
-        </is>
-      </c>
-      <c r="E11" s="66" t="n"/>
-      <c r="F11" s="73" t="n"/>
-      <c r="G11" s="73" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_10</t>
-        </is>
-      </c>
-      <c r="B12" s="104" t="inlineStr">
-        <is>
-          <t>Verify Over Limit status is marked correctly when visits exceeding the configured daily limit are submitted on the same day.</t>
-        </is>
-      </c>
-      <c r="C12" s="104" t="inlineStr">
-        <is>
-          <t>1. login to CCC web UI
-2. Invite connect worker
-3. Complete the daily limit visits in mobile
-4. Again submit the visits exceeding the daily visit limit</t>
-        </is>
-      </c>
-      <c r="D12" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- visits submitted exceeding the daily visit limit should marked as over limit </t>
-        </is>
-      </c>
-      <c r="E12" s="66" t="n"/>
-      <c r="F12" s="73" t="n"/>
-      <c r="G12" s="73" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_11</t>
-        </is>
-      </c>
-      <c r="B13" s="104" t="inlineStr">
-        <is>
-          <t>Verify only the first N visits (up to the daily limit) remain valid and any additional visits are flagged as Over Limit.</t>
-        </is>
-      </c>
-      <c r="C13" s="104" t="inlineStr">
-        <is>
-          <t>1. login to CCC web UI
-2. Invite connect worker
-3. Complete the daily limit visits in mobile
-4. Again submit the visits exceeding the daily visit limit</t>
-        </is>
-      </c>
-      <c r="D13" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- visits submitted exceeding the daily visit limit should marked as over limit </t>
-        </is>
-      </c>
-      <c r="E13" s="66" t="n"/>
-      <c r="F13" s="73" t="n"/>
-      <c r="G13" s="73" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_12</t>
-        </is>
-      </c>
-      <c r="B14" s="104" t="inlineStr">
-        <is>
-          <t>Verify Over Limit status is marked correctly when visits exceeding the configured total/max visit limit are submitted.</t>
-        </is>
-      </c>
-      <c r="C14" s="104" t="inlineStr">
-        <is>
-          <t>1. login to CCC web UI
-2. Invite connect worker
-3. Complete the total max limit visits in mobile
-4. Again submit the visits exceeding the daily visit limit</t>
-        </is>
-      </c>
-      <c r="D14" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- visits submitted exceeding the total max limit should marked as over limit </t>
-        </is>
-      </c>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="73" t="n"/>
-      <c r="G14" s="73" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_13</t>
-        </is>
-      </c>
-      <c r="B15" s="104" t="inlineStr">
-        <is>
-          <t>Verify only the first N visits (up to the total visit limit) remain valid and any additional visits are flagged as Over Limit.</t>
-        </is>
-      </c>
-      <c r="C15" s="104" t="inlineStr">
-        <is>
-          <t>1. login to CCC web UI
-2. Invite connect worker
-3. Complete the total max limit visits in mobile
-4. Again submit the visits exceeding the daily visit limit</t>
-        </is>
-      </c>
-      <c r="D15" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- visits submitted exceeding the total max limit should marked as over limit </t>
-        </is>
-      </c>
-      <c r="E15" s="66" t="n"/>
-      <c r="F15" s="73" t="n"/>
-      <c r="G15" s="73" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_14</t>
-        </is>
-      </c>
-      <c r="B16" s="104" t="inlineStr">
-        <is>
-          <t>Verify no additional visits are accepted when multiple submissions are processed concurrently after the daily limit has been reached.</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Create an opportunity with a configured daily visit limit.
-3. Invite multiple Connect workers or prepare multiple visit submissions from the same worker.
-4. Submit visits until the daily limit is reached.
-5. Immediately submit multiple additional visits concurrently (for example, back-to-back submissions from a single device, multiple devices, or queued submissions syncing together).
-6. Navigate to the Worker Visit Verification page.</t>
-        </is>
-      </c>
-      <c r="D16" s="104" t="inlineStr">
-        <is>
-          <t>- Visits submitted before the daily limit is marked as approved
-- visits submitted after the daily limit is marked as overlimit</t>
-        </is>
-      </c>
-      <c r="E16" s="66" t="n"/>
-      <c r="F16" s="73" t="n"/>
-      <c r="G16" s="73" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_15</t>
-        </is>
-      </c>
-      <c r="B17" s="104" t="inlineStr">
-        <is>
-          <t>Verify no additional visits are accepted when multiple submissions are processed concurrently after the total visit limit has been reached.</t>
-        </is>
-      </c>
-      <c r="C17" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Create an opportunity with a configured total/max visit limit.
-3. Invite Connect workers.
-4. Submit visits until the total visit limit is reached.
-5. Immediately submit multiple additional visits concurrently (multiple devices, rapid submissions, or queued sync submissions).
-6. Navigate to the Worker Visit Verification page.</t>
-        </is>
-      </c>
-      <c r="D17" s="104" t="inlineStr">
-        <is>
-          <t>- Visits submitted before the total max limit is marked as approved
-- visits submitted after the total max limit is marked as overlimit</t>
-        </is>
-      </c>
-      <c r="E17" s="66" t="n"/>
-      <c r="F17" s="73" t="n"/>
-      <c r="G17" s="73" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_16</t>
-        </is>
-      </c>
-      <c r="B18" s="104" t="inlineStr">
-        <is>
-          <t>Verify visits exceeding the daily limit are displayed with an Over Limit status on the Visit Verification screen.</t>
-        </is>
-      </c>
-      <c r="C18" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Configure a daily visit limit for the opportunity.
-3. Invite Connect workers.
-4. Submit visits exceeding the configured daily visit limit.
-5. Open the Worker Visit Verification page.
-6. Locate visits marked as Over Limit.
-7. Hover over the visit count indicator.</t>
-        </is>
-      </c>
-      <c r="D18" s="104" t="inlineStr">
-        <is>
-          <t>- when mouse hover on the count of visits overlimit count should be displayed</t>
-        </is>
-      </c>
-      <c r="E18" s="66" t="n"/>
-      <c r="F18" s="73" t="n"/>
-      <c r="G18" s="73" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_17</t>
-        </is>
-      </c>
-      <c r="B19" s="104" t="inlineStr">
-        <is>
-          <t>Verify visits exceeding the total visit limit are displayed with an Over Limit status on the Visit Verification screen.</t>
-        </is>
-      </c>
-      <c r="C19" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Configure a total/max visit limit for the opportunity.
-3. Invite Connect workers.
-4. Submit visits exceeding the configured total visit limit.
-5. Open the Worker Visit Verification page.
-6. Locate visits marked as Over Limit.
-7. Hover over the visit count indicator.</t>
-        </is>
-      </c>
-      <c r="D19" s="104" t="inlineStr">
-        <is>
-          <t>- when mouse hover on the count of visits overlimit count should be displayed</t>
-        </is>
-      </c>
-      <c r="E19" s="66" t="n"/>
-      <c r="F19" s="73" t="n"/>
-      <c r="G19" s="73" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_18</t>
-        </is>
-      </c>
-      <c r="B20" s="104" t="inlineStr">
-        <is>
-          <t>Verify the count of valid visits and Over Limit visits displayed on the Visit Verification screen is accurate after concurrent submissions.</t>
-        </is>
-      </c>
-      <c r="C20" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Configure daily and total visit limits.
-3. Invite Connect workers.
-4. Submit multiple visits concurrently after the configured limit has been reached.
-5. Open the Worker Visit Verification page.
-6. Verify the visit summary counts.
-7. Hover over the count indicators if applicable.</t>
-        </is>
-      </c>
-      <c r="D20" s="104" t="inlineStr">
-        <is>
-          <t>- when mouse hover on the count of visits overlimit count should be displayed</t>
-        </is>
-      </c>
-      <c r="E20" s="66" t="n"/>
-      <c r="F20" s="73" t="n"/>
-      <c r="G20" s="73" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_19</t>
-        </is>
-      </c>
-      <c r="B21" s="104" t="inlineStr">
-        <is>
-          <t>Verify visits submitted through queued/offline sync are correctly evaluated against the daily limit when multiple submissions are processed together.</t>
-        </is>
-      </c>
-      <c r="C21" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Configure a daily visit limit.
-3. Invite a Connect worker.
-4. Put the mobile device in offline mode.
-5. Submit multiple visits while offline, including submissions exceeding the daily limit.
-6. Restore network connectivity and allow all queued visits to sync together.
-7. Open the Worker Visit Verification page.</t>
-        </is>
-      </c>
-      <c r="D21" s="104" t="inlineStr">
-        <is>
-          <t>- Visit that are in daily limit marked as approved
-- Visits that exceeds daily limit are marked as over limit</t>
-        </is>
-      </c>
-      <c r="E21" s="66" t="n"/>
-      <c r="F21" s="73" t="n"/>
-      <c r="G21" s="73" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_20</t>
-        </is>
-      </c>
-      <c r="B22" s="104" t="inlineStr">
-        <is>
-          <t>Verify visits submitted through queued/offline sync are correctly evaluated against the total visit limit when multiple submissions are processed together.</t>
-        </is>
-      </c>
-      <c r="C22" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI.
-2. Configure a total/max visit limit.
-3. Invite a Connect worker.
-4. Put the mobile device in offline mode.
-5. Submit multiple visits while offline, including submissions exceeding the total visit limit.
-6. Restore network connectivity and allow all queued visits to sync together.
-7. Open the Worker Visit Verification page.</t>
-        </is>
-      </c>
-      <c r="D22" s="104" t="inlineStr">
-        <is>
-          <t>- Visit that are in total/max limit marked as approved
-- Visits that exceeds total/max limit are marked as over limit</t>
-        </is>
-      </c>
-      <c r="E22" s="66" t="n"/>
-      <c r="F22" s="73" t="n"/>
-      <c r="G22" s="73" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_21</t>
-        </is>
-      </c>
-      <c r="B23" s="104" t="inlineStr">
-        <is>
-          <t>Verify trial visit submission</t>
-        </is>
-      </c>
-      <c r="C23" s="104" t="inlineStr">
-        <is>
-          <t>1. Submit visits befor the opp start date</t>
-        </is>
-      </c>
-      <c r="D23" s="104" t="inlineStr">
-        <is>
-          <t>- visits submitted before opp start date is marked as trial</t>
-        </is>
-      </c>
-      <c r="E23" s="66" t="n"/>
-      <c r="F23" s="73" t="n"/>
-      <c r="G23" s="73" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_22</t>
-        </is>
-      </c>
-      <c r="B24" s="104" t="inlineStr">
-        <is>
-          <t>Verify post end date submissions</t>
-        </is>
-      </c>
-      <c r="C24" s="104" t="inlineStr">
-        <is>
-          <t>1. Submit the visits after the opp has ended</t>
-        </is>
-      </c>
-      <c r="D24" s="104" t="inlineStr">
-        <is>
-          <t>- visits submitted after opp ended is not updated in web and no progress is gained for an opp</t>
-        </is>
-      </c>
-      <c r="E24" s="66" t="n"/>
-      <c r="F24" s="73" t="n"/>
-      <c r="G24" s="73" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_23</t>
-        </is>
-      </c>
-      <c r="B25" s="104" t="inlineStr">
-        <is>
-          <t>Verify duplicate visits are billable only when visits are approved by NM and agreed by PM</t>
-        </is>
-      </c>
-      <c r="C25" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Invite user for an Opp
-3. Submit duplicate forms
-4. Approve visit by NM user 
-5. Agree visit by PM user
-</t>
-        </is>
-      </c>
-      <c r="D25" s="104" t="inlineStr">
-        <is>
-          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
-        </is>
-      </c>
-      <c r="E25" s="66" t="n"/>
-      <c r="F25" s="73" t="n"/>
-      <c r="G25" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_24</t>
-        </is>
-      </c>
-      <c r="B26" s="104" t="inlineStr">
-        <is>
-          <t>Verify duplicate visits are not billable when PM is not agreed</t>
-        </is>
-      </c>
-      <c r="C26" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Invite user for an Opp
-3. Submit duplicate forms
-4. Approve visit by NM user 
-</t>
-        </is>
-      </c>
-      <c r="D26" s="104" t="inlineStr">
-        <is>
-          <t>- Visits that aren't agreed by Pm are not eligilble for payment</t>
-        </is>
-      </c>
-      <c r="E26" s="66" t="n"/>
-      <c r="F26" s="73" t="n"/>
-      <c r="G26" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_25</t>
-        </is>
-      </c>
-      <c r="B27" s="104" t="inlineStr">
-        <is>
-          <t>Verfiy the visits are billable only when agreed by PM using import bulk</t>
-        </is>
-      </c>
-      <c r="C27" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CC web UI
-2. Invite user for an opp
-3. Submit few duplicate visits
-4. Navigate to connect workers page &gt;&gt; Download the PM review csv export
-5. Make chnages are PM agreed for visits and import
-</t>
-        </is>
-      </c>
-      <c r="D27" s="104" t="inlineStr">
-        <is>
-          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
-        </is>
-      </c>
-      <c r="E27" s="66" t="n"/>
-      <c r="F27" s="73" t="n"/>
-      <c r="G27" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_26</t>
-        </is>
-      </c>
-      <c r="B28" s="104" t="inlineStr">
-        <is>
-          <t>Verfiy the visits are not billable when disagreed by PM using import bulk</t>
-        </is>
-      </c>
-      <c r="C28" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CC web UI
-2. Invite user for an opp
-3. Submit few duplicate visits
-4. Navigate to connect workers page &gt;&gt; Download the PM review csv export
-5. Make chnages are PM disagreed for visits and import
-</t>
-        </is>
-      </c>
-      <c r="D28" s="104" t="inlineStr">
-        <is>
-          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
-        </is>
-      </c>
-      <c r="E28" s="66" t="n"/>
-      <c r="F28" s="73" t="n"/>
-      <c r="G28" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_27</t>
-        </is>
-      </c>
-      <c r="B29" s="104" t="inlineStr">
-        <is>
-          <t>Verify combination of agreed/disgareed for duplicate visits using import</t>
-        </is>
-      </c>
-      <c r="C29" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CC web UI
-2. Invite user for an opp
-3. Submit few duplicate visits
-4. Navigate to connect workers page &gt;&gt; Download the PM review csv export
-5. Make chnages are PM agreed for few visits, disagree some visits and import
-</t>
-        </is>
-      </c>
-      <c r="D29" s="104" t="inlineStr">
-        <is>
-          <t>- Only forms that are approved by NM and agreed by PM are eligible for payment and amount should accrued</t>
-        </is>
-      </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="73" t="n"/>
-      <c r="G29" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_28</t>
-        </is>
-      </c>
-      <c r="B30" s="104" t="inlineStr">
-        <is>
-          <t>Verify the invoice generating should contains only visits that are agreed by PM</t>
-        </is>
-      </c>
-      <c r="C30" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Loin to CCC web UI
-2. Navigate to view invoices page
-3. Click create invoice &gt;&gt; service delivery
-4. Select date </t>
-        </is>
-      </c>
-      <c r="D30" s="104" t="inlineStr">
-        <is>
-          <t>- The visits that are approved by NM and agreed by PM are listed for invoice generation</t>
-        </is>
-      </c>
-      <c r="E30" s="66" t="n"/>
-      <c r="F30" s="73" t="n"/>
-      <c r="G30" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_29</t>
-        </is>
-      </c>
-      <c r="B31" s="104" t="inlineStr">
-        <is>
-          <t>Verify payment is accrued only when all required visits and atleast one optional visit (if any) are agreed by PM</t>
-        </is>
-      </c>
-      <c r="C31" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Submit all required visits
-3. Submit atleast one optioanl visit
-4. Approve by NM and agree by PM</t>
-        </is>
-      </c>
-      <c r="D31" s="104" t="inlineStr">
-        <is>
-          <t>- payment should be accrued only when all req visits and atleast one optional visit is agreed by PM</t>
-        </is>
-      </c>
-      <c r="E31" s="66" t="n"/>
-      <c r="F31" s="73" t="n"/>
-      <c r="G31" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_30</t>
-        </is>
-      </c>
-      <c r="B32" s="104" t="inlineStr">
-        <is>
-          <t>Verify payment is not accrued when all required visits and atleast one optional visit (if any) are agreed by PM</t>
-        </is>
-      </c>
-      <c r="C32" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Submit all required visits
-3. Submit atleast one optioanl visit
-4. Approve by NM 
-5. Don't agree all visits by PM</t>
-        </is>
-      </c>
-      <c r="D32" s="104" t="inlineStr">
-        <is>
-          <t>- payment should not be accrued</t>
-        </is>
-      </c>
-      <c r="E32" s="66" t="n"/>
-      <c r="F32" s="73" t="n"/>
-      <c r="G32" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_31</t>
-        </is>
-      </c>
-      <c r="B33" s="86" t="inlineStr">
-        <is>
-          <t>Verfiy user is able to reject the visits (NM user)</t>
-        </is>
-      </c>
-      <c r="C33" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to visit verification page
-3. Click on visit details &gt;&gt; Click on reject</t>
-        </is>
-      </c>
-      <c r="D33" s="104" t="inlineStr">
-        <is>
-          <t>- Status should get update to rejected</t>
-        </is>
-      </c>
-      <c r="E33" s="66" t="n"/>
-      <c r="F33" s="87" t="n"/>
-      <c r="G33" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_32</t>
-        </is>
-      </c>
-      <c r="B34" s="86" t="inlineStr">
-        <is>
-          <t>Verify user is able to approve the visits (NM user)</t>
-        </is>
-      </c>
-      <c r="C34" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to visit verification page
-3. Click on visit details &gt;&gt; Click on approve</t>
-        </is>
-      </c>
-      <c r="D34" s="104" t="inlineStr">
-        <is>
-          <t>- Status should get update to approved</t>
-        </is>
-      </c>
-      <c r="E34" s="66" t="n"/>
-      <c r="F34" s="87" t="n"/>
-      <c r="G34" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_33</t>
-        </is>
-      </c>
-      <c r="B35" s="86" t="inlineStr">
-        <is>
-          <t>Verify user is able to agree the visits (PM user)</t>
-        </is>
-      </c>
-      <c r="C35" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to visit verification page
-3. Click on visit details &gt;&gt; Click on agree</t>
-        </is>
-      </c>
-      <c r="D35" s="104" t="inlineStr">
-        <is>
-          <t>- when PM approved visit paymnet amount is accrued</t>
-        </is>
-      </c>
-      <c r="E35" s="66" t="n"/>
-      <c r="F35" s="87" t="n"/>
-      <c r="G35" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_34</t>
-        </is>
-      </c>
-      <c r="B36" s="86" t="inlineStr">
-        <is>
-          <t>Verify user is able to disagree the visits (PM user)</t>
-        </is>
-      </c>
-      <c r="C36" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to visit verification page
-3. Click on visit details &gt;&gt; Click on disagree</t>
-        </is>
-      </c>
-      <c r="D36" s="104" t="inlineStr">
-        <is>
-          <t>- When PM disagreed no paymnet is accrued</t>
-        </is>
-      </c>
-      <c r="E36" s="66" t="n"/>
-      <c r="F36" s="87" t="n"/>
-      <c r="G36" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="85" t="inlineStr">
-        <is>
-          <t>Worker Visit Verification Page_35</t>
-        </is>
-      </c>
-      <c r="B37" s="86" t="inlineStr">
-        <is>
-          <t>Verify user is not able to agree the visit that is disagreed and vice versa</t>
-        </is>
-      </c>
-      <c r="C37" s="104" t="n"/>
-      <c r="D37" s="104" t="n"/>
-      <c r="E37" s="66" t="n"/>
-      <c r="F37" s="87" t="n"/>
-      <c r="G37" s="73" t="inlineStr">
-        <is>
-          <t>This test is for opp created before june 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="166" t="inlineStr">
-        <is>
-          <t>Payment eligibility</t>
-        </is>
-      </c>
-      <c r="B38" s="153" t="n"/>
-      <c r="C38" s="153" t="n"/>
-      <c r="D38" s="153" t="n"/>
-      <c r="E38" s="153" t="n"/>
-      <c r="F38" s="153" t="n"/>
-      <c r="G38" s="154" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_01</t>
-        </is>
-      </c>
-      <c r="B39" s="104" t="inlineStr">
-        <is>
-          <t>Verify user becomes eligible for payment when all required visits are approved</t>
-        </is>
-      </c>
-      <c r="C39" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI. 
-2. Create or select an opportunity with required delivery units configured. 
-3. Invite a PID user to the opportunity. 
-4. Login to the mobile app with the PID user. 
-5. Claim the job and submit forms for all required visits.
- 6. Approve the visits from the web/admin panel.</t>
-        </is>
-      </c>
-      <c r="D39" s="104" t="inlineStr">
-        <is>
-          <t>User becomes eligible for payment once all required visits are approved.</t>
-        </is>
-      </c>
-      <c r="E39" s="66" t="n"/>
-      <c r="F39" s="73" t="n"/>
-      <c r="G39" s="73" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_02</t>
-        </is>
-      </c>
-      <c r="B40" s="104" t="inlineStr">
-        <is>
-          <t>Verify user is not eligible for payment if any required visit is not approved</t>
-        </is>
-      </c>
-      <c r="C40" s="104" t="inlineStr">
-        <is>
-          <t>1. Login to CCC Web UI. 
-2. Create an opportunity with multiple required visits. 
-3. Invite a PID user. 
-4. Submit all required visits from mobile. 
-5. Approve only some of the required visits and leave at least one pending/rejected.</t>
-        </is>
-      </c>
-      <c r="D40" s="104" t="inlineStr">
-        <is>
-          <t>User should not be eligible for payment if any required visit is not approved.</t>
-        </is>
-      </c>
-      <c r="E40" s="66" t="n"/>
-      <c r="F40" s="73" t="n"/>
-      <c r="G40" s="73" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_03</t>
-        </is>
-      </c>
-      <c r="B41" s="104" t="inlineStr">
-        <is>
-          <t>Verify payment eligibility when all required visits and at least one optional visit are approved</t>
-        </is>
-      </c>
-      <c r="C41" s="104" t="inlineStr">
-        <is>
-          <t>1. Create an opportunity with required and optional delivery units. 
-2. Invite PID user and claim job from mobile. 
-3. Submit required visit forms. 
-4. Submit at least one optional visit form. 
-5. Approve all required visits and one optional visit.</t>
-        </is>
-      </c>
-      <c r="D41" s="104" t="inlineStr">
-        <is>
-          <t>User becomes eligible for payment.</t>
-        </is>
-      </c>
-      <c r="E41" s="66" t="n"/>
-      <c r="F41" s="73" t="n"/>
-      <c r="G41" s="73" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_04</t>
-        </is>
-      </c>
-      <c r="B42" s="104" t="inlineStr">
-        <is>
-          <t>Verify worker is not eligible if optional visits exist but none are approved</t>
-        </is>
-      </c>
-      <c r="C42" s="104" t="inlineStr">
-        <is>
-          <t>1. Create opportunity with required and optional visits. 
-2. Submit all required visits. 
-3. Submit optional visits but do not approve them.
- 4. Approve only required visits.</t>
-        </is>
-      </c>
-      <c r="D42" s="104" t="inlineStr">
-        <is>
-          <t>User should not be eligible for payment because no optional visit is approved.</t>
-        </is>
-      </c>
-      <c r="E42" s="66" t="n"/>
-      <c r="F42" s="73" t="n"/>
-      <c r="G42" s="73" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_06</t>
-        </is>
-      </c>
-      <c r="B43" s="104" t="inlineStr">
-        <is>
-          <t>Verify auto-approval system correctly marks eligibility</t>
-        </is>
-      </c>
-      <c r="C43" s="104" t="inlineStr">
-        <is>
-          <t>1. Enable auto approval for visits. 
-2. Invite PID user. 
-3. Submit required and optional visits from mobile. 
-4. Allow system to auto approve visits.</t>
-        </is>
-      </c>
-      <c r="D43" s="104" t="inlineStr">
-        <is>
-          <t>System automatically marks user as eligible for payment when conditions are satisfied.</t>
-        </is>
-      </c>
-      <c r="E43" s="66" t="n"/>
-      <c r="F43" s="73" t="n"/>
-      <c r="G43" s="73" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_07</t>
-        </is>
-      </c>
-      <c r="B44" s="104" t="inlineStr">
-        <is>
-          <t>Verify manual approval works with new eligibility logic</t>
-        </is>
-      </c>
-      <c r="C44" s="104" t="inlineStr">
-        <is>
-          <t>1. Create opportunity with required and optional visits. 
-2. Submit visits from mobile. 
-3. Admin manually approves required visits and at least one optional visit.</t>
-        </is>
-      </c>
-      <c r="D44" s="104" t="inlineStr">
-        <is>
-          <t>User becomes eligible for payment after manual approval.</t>
-        </is>
-      </c>
-      <c r="E44" s="66" t="n"/>
-      <c r="F44" s="73" t="n"/>
-      <c r="G44" s="73" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_08</t>
-        </is>
-      </c>
-      <c r="B45" s="104" t="inlineStr">
-        <is>
-          <t>Verify optional visit approved but required visits missing</t>
-        </is>
-      </c>
-      <c r="C45" s="104" t="inlineStr">
-        <is>
-          <t>1. Create opportunity with required and optional visits. 
-2. Submit optional visit first.
-3. Approve optional visit but leave required visits pending.</t>
-        </is>
-      </c>
-      <c r="D45" s="104" t="inlineStr">
-        <is>
-          <t>User should not be eligible for payment until all required visits are approved.</t>
-        </is>
-      </c>
-      <c r="E45" s="66" t="n"/>
-      <c r="F45" s="73" t="n"/>
-      <c r="G45" s="73" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="58" t="inlineStr">
-        <is>
-          <t>Payment eligibility_09</t>
-        </is>
-      </c>
-      <c r="B46" s="104" t="inlineStr">
-        <is>
-          <t>Verify rejected visits do not count toward payment eligibility</t>
-        </is>
-      </c>
-      <c r="C46" s="104" t="inlineStr">
-        <is>
-          <t>1. Submit required visits from mobile. 
-2. Reject one of the required visits from web.</t>
-        </is>
-      </c>
-      <c r="D46" s="104" t="inlineStr">
-        <is>
-          <t>User should not be eligible for payment when a required visit is rejected.</t>
-        </is>
-      </c>
-      <c r="E46" s="66" t="n"/>
-      <c r="F46" s="73" t="n"/>
-      <c r="G46" s="73" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="58" t="n"/>
-      <c r="B47" s="88" t="n"/>
-      <c r="C47" s="88" t="n"/>
-      <c r="D47" s="68" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="89" t="n"/>
-      <c r="G47" s="89" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E3:E37 E39:E47">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
-      <formula>"Fail"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="6">
-      <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="7">
-      <formula>"Blocking"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="E3:E37 E39:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A,Blocking"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name=" Test Tracker" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Login page" sheetId="4" state="visible" r:id="rId4"/>
@@ -34,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -171,6 +171,14 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
     </font>
   </fonts>
   <fills count="20">
@@ -420,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -887,6 +895,12 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1290,222 +1304,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="148" min="1" max="1"/>
-    <col width="95" customWidth="1" style="148" min="2" max="2"/>
+    <col width="42" customWidth="1" style="148" min="1" max="1"/>
+    <col width="100" customWidth="1" style="148" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="172" t="inlineStr">
-        <is>
-          <t>Connect QA Gap Analysis — Legend</t>
-        </is>
-      </c>
-      <c r="B1" s="171" t="inlineStr"/>
+      <c r="A1" s="176" t="inlineStr">
+        <is>
+          <t>Read Me — Tab Guide &amp; Legend</t>
+        </is>
+      </c>
+      <c r="B1" s="171" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="171" t="inlineStr"/>
-      <c r="B2" s="171" t="inlineStr"/>
+      <c r="A2" s="177" t="inlineStr">
+        <is>
+          <t>Connect QA Gap Analysis · Web Platform stream</t>
+        </is>
+      </c>
+      <c r="B2" s="171" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="173" t="inlineStr">
-        <is>
-          <t>ROW TYPES (Gap Analysis tab) — identified by the Gap ID prefix</t>
-        </is>
-      </c>
-      <c r="B3" s="171" t="inlineStr"/>
+      <c r="A3" s="171" t="inlineStr"/>
+      <c r="B3" s="171" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="171" t="inlineStr">
-        <is>
-          <t>Functional gap</t>
-        </is>
-      </c>
-      <c r="B4" s="171" t="inlineStr">
-        <is>
-          <t>Product behaviour that exists in the code but has NO test case in this MTP. The core deliverable; candidates for QA test coverage. IDs: GAP-SRC-*, GAP-BE-*, GAP-FE-*.</t>
-        </is>
-      </c>
+      <c r="A4" s="173" t="inlineStr">
+        <is>
+          <t>WHAT THIS EXERCISE PRODUCED — two separate outputs</t>
+        </is>
+      </c>
+      <c r="B4" s="171" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="171" t="inlineStr">
         <is>
-          <t>Unit-test-coverage gap (dev)</t>
+          <t>Output 1: MTP completeness</t>
         </is>
       </c>
       <c r="B5" s="171" t="inlineStr">
         <is>
-          <t>Where the ENGINEERING product code lacks a unit test. A note for the dev teams (not QA automation). IDs: GAP-UTC-*.</t>
+          <t>Everything the product does that was NOT documented in this test plan. ALL functional gaps get added to the plan, whether or not engineering already tests them.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="171" t="inlineStr">
         <is>
-          <t>Cross-cutting</t>
+          <t>Output 2: QA automation backlog</t>
         </is>
       </c>
       <c r="B6" s="171" t="inlineStr">
         <is>
-          <t>Not a single missing case: hygiene (e.g. duplicate IDs), MTP-vs-code discrepancies, or automation/dead-code notes. Fix-the-plan / fix-the-code items. IDs: GAP-MISC-*, GAP-MMISC-*.</t>
+          <t>The subset of those gaps that QA still needs to automate — i.e. the ones engineering does NOT already cover. Filter the Action column for "Automate".</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="171" t="inlineStr"/>
-      <c r="B7" s="171" t="inlineStr"/>
+      <c r="B7" s="171" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="173" t="inlineStr">
         <is>
-          <t>BUCKET column</t>
-        </is>
-      </c>
-      <c r="B8" s="171" t="inlineStr"/>
+          <t>TAB GUIDE — what each tab is</t>
+        </is>
+      </c>
+      <c r="B8" s="171" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="171" t="inlineStr">
         <is>
-          <t>🟢 Already automated</t>
+          <t>Read Me</t>
         </is>
       </c>
       <c r="B9" s="171" t="inlineStr">
         <is>
-          <t>A spec exists and runs (tracked in the Automation Status tab, not here).</t>
+          <t>This tab. The key to the whole workbook.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="171" t="inlineStr">
         <is>
-          <t>🟡 Automatable - not yet done</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B10" s="171" t="inlineStr">
         <is>
-          <t>Can be automated; this is the automation backlog.</t>
+          <t>A one-screen dashboard of the numbers, auto-calculated. Shows Output 1 (MTP completeness), Output 2 (automation backlog), plus dev unit-test and reconcile counts. Read this first for the big picture.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="171" t="inlineStr">
         <is>
-          <t>🔴 Manual only</t>
+          <t>Test Tracker / Test Tracker Horizontal</t>
         </is>
       </c>
       <c r="B11" s="171" t="inlineStr">
         <is>
-          <t>Impractical/impossible to automate (real SMS/OTP, push, camera, biometric, device, time-dependent).</t>
+          <t>ORIGINAL tabs (not from this exercise). The pre-existing execution trackers — who ran the manual test rounds and pass/fail counts. Left untouched.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="171" t="inlineStr"/>
-      <c r="B12" s="171" t="inlineStr"/>
+      <c r="A12" s="171" t="inlineStr">
+        <is>
+          <t>The surface tabs (Login, Opportunity creation, Visit verification, Microplanning, etc.)</t>
+        </is>
+      </c>
+      <c r="B12" s="171" t="inlineStr">
+        <is>
+          <t>ORIGINAL tabs. This IS the existing master test plan — the documented test cases grouped by product screen/area. The "before" picture that the gap analysis was measured against.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="173" t="inlineStr">
-        <is>
-          <t>ENG COVERAGE column (does engineering already test this, so QA avoids duplicating?)</t>
-        </is>
-      </c>
-      <c r="B13" s="171" t="inlineStr"/>
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>Gap Analysis  (MAIN OUTPUT)</t>
+        </is>
+      </c>
+      <c r="B13" s="171" t="inlineStr">
+        <is>
+          <t>Every coverage gap we found — behaviour that exists in the product code but had NO case in the surface tabs. Each row carries its Bucket, Eng Coverage, and Action. This is the deliverable: what was missing, and what to do about it. Reviewers work here.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="171" t="inlineStr">
         <is>
-          <t>Eng-covered (logic)</t>
+          <t>Automation Coverage</t>
         </is>
       </c>
       <c r="B14" s="171" t="inlineStr">
         <is>
-          <t>Eng PR-run tests cover the logic. QA adds an e2e test only if on a critical user journey.</t>
+          <t>The pass-1 baseline: the existing master test cases checked against QA's CURRENT automated suite (the pytest tests in dimagi-qa-ccc) — "of what we already documented, how much is automated." Migration bookkeeping; context, not the headline.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="171" t="inlineStr">
         <is>
-          <t>QA-owned</t>
+          <t>Automation Status</t>
         </is>
       </c>
       <c r="B15" s="171" t="inlineStr">
         <is>
-          <t>Real device/external (SMS/OTP/push/camera) — eng cannot unit-test either. QA-owned priority.</t>
+          <t>The short list of master-plan cases confirmed as ALREADY automated (the green cases). "What is already done."</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="171" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="B16" s="171" t="inlineStr">
-        <is>
-          <t>Some eng coverage; confirm with eng.</t>
-        </is>
-      </c>
+      <c r="A16" s="171" t="inlineStr"/>
+      <c r="B16" s="171" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="171" t="inlineStr">
         <is>
-          <t>Eng GAP</t>
-        </is>
-      </c>
-      <c r="B17" s="171" t="inlineStr">
-        <is>
-          <t>Eng has no unit test here (a GAP-UTC row).</t>
-        </is>
-      </c>
+          <t>ONE-LINE DISTINCTION</t>
+        </is>
+      </c>
+      <c r="B17" s="171" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="171" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A18" s="173" t="inlineStr">
+        <is>
+          <t>Gap Analysis</t>
         </is>
       </c>
       <c r="B18" s="171" t="inlineStr">
         <is>
-          <t>Hygiene/discrepancy/automation note.</t>
+          <t>What was MISSING from the plan (new findings from reading the code) = completeness of the plan.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="171" t="inlineStr"/>
-      <c r="B19" s="171" t="inlineStr"/>
+      <c r="A19" s="171" t="inlineStr">
+        <is>
+          <t>Automation Coverage / Status</t>
+        </is>
+      </c>
+      <c r="B19" s="171" t="inlineStr">
+        <is>
+          <t>Of what was ALREADY in the plan, how much is automated = automation of the plan.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="173" t="inlineStr">
-        <is>
-          <t>OTHER TABS</t>
-        </is>
-      </c>
-      <c r="B20" s="171" t="inlineStr"/>
+      <c r="A20" s="171" t="inlineStr"/>
+      <c r="B20" s="171" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="171" t="inlineStr">
-        <is>
-          <t>Automation Coverage</t>
-        </is>
-      </c>
-      <c r="B21" s="171" t="inlineStr">
-        <is>
-          <t>Pass-1 baseline: MTP cases vs the existing QA automated suite (migration input, not this exercise's headline).</t>
-        </is>
-      </c>
+      <c r="A21" s="173" t="inlineStr">
+        <is>
+          <t>GAP ANALYSIS — the 3 row types (by Gap ID prefix)</t>
+        </is>
+      </c>
+      <c r="B21" s="171" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="171" t="inlineStr">
         <is>
-          <t>Automation Status</t>
+          <t>Functional gap</t>
         </is>
       </c>
       <c r="B22" s="171" t="inlineStr">
         <is>
-          <t>MTP cases confirmed already automated (green).</t>
+          <t>Behaviour in the code with no test case in the MTP. The core finding; QA-automation candidates. IDs: GAP-SRC-*, GAP-BE-*, GAP-FE-*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="171" t="inlineStr">
+        <is>
+          <t>Unit-test-coverage gap (dev)</t>
+        </is>
+      </c>
+      <c r="B23" s="171" t="inlineStr">
+        <is>
+          <t>Where the ENGINEERING code lacks a unit test. A note for dev teams, not QA automation. IDs: GAP-UTC-*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="B24" s="171" t="inlineStr">
+        <is>
+          <t>Not a single missing case: hygiene (e.g. duplicate IDs), MTP-vs-code discrepancies, or automation/dead-code notes. IDs: GAP-MISC-*, GAP-MMISC-*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="171" t="inlineStr"/>
+      <c r="B25" s="171" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="171" t="inlineStr">
+        <is>
+          <t>BUCKET column</t>
+        </is>
+      </c>
+      <c r="B26" s="171" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="173" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="B27" s="171" t="inlineStr">
+        <is>
+          <t>A spec exists and runs (tracked in Automation Status).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="B28" s="171" t="inlineStr">
+        <is>
+          <t>Can be automated; the automation backlog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="171" t="inlineStr">
+        <is>
+          <t>🔴 Manual only</t>
+        </is>
+      </c>
+      <c r="B29" s="171" t="inlineStr">
+        <is>
+          <t>Impractical/impossible to automate (real SMS/OTP, push, camera, biometric, device, time-dependent).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="171" t="inlineStr"/>
+      <c r="B30" s="171" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="171" t="inlineStr">
+        <is>
+          <t>ENG COVERAGE column — does engineering already test this? (avoid duplicating eng work)</t>
+        </is>
+      </c>
+      <c r="B31" s="171" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="173" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic)</t>
+        </is>
+      </c>
+      <c r="B32" s="171" t="inlineStr">
+        <is>
+          <t>Eng PR-run tests cover the logic. QA adds an e2e test only if on a critical user journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned</t>
+        </is>
+      </c>
+      <c r="B33" s="171" t="inlineStr">
+        <is>
+          <t>Real device/external (SMS/OTP/push/camera) — eng cannot unit-test either. QA-owned priority.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="171" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B34" s="171" t="inlineStr">
+        <is>
+          <t>Some eng coverage; confirm with eng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="171" t="inlineStr">
+        <is>
+          <t>Eng GAP</t>
+        </is>
+      </c>
+      <c r="B35" s="171" t="inlineStr">
+        <is>
+          <t>Eng has no unit test here (a GAP-UTC row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B36" s="171" t="inlineStr">
+        <is>
+          <t>Hygiene/discrepancy/automation note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="171" t="inlineStr"/>
+      <c r="B37" s="171" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="171" t="inlineStr">
+        <is>
+          <t>ACTION column — the decision per row</t>
+        </is>
+      </c>
+      <c r="B38" s="171" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="173" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
+        </is>
+      </c>
+      <c r="B39" s="171" t="inlineStr">
+        <is>
+          <t>Document it in the plan; do NOT automate — eng already tests it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (QA-owned)</t>
+        </is>
+      </c>
+      <c r="B40" s="171" t="inlineStr">
+        <is>
+          <t>Add to plan AND automate — eng cannot cover it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+      <c r="B41" s="171" t="inlineStr">
+        <is>
+          <t>Add to plan; likely automate — confirm eng coverage first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="171" t="inlineStr">
+        <is>
+          <t>Dev: add unit test</t>
+        </is>
+      </c>
+      <c r="B42" s="171" t="inlineStr">
+        <is>
+          <t>For the dev team — product code missing a unit test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="171" t="inlineStr">
+        <is>
+          <t>Reconcile (plan/code)</t>
+        </is>
+      </c>
+      <c r="B43" s="171" t="inlineStr">
+        <is>
+          <t>Fix the plan or the code (hygiene / discrepancy).</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16636,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="175" t="inlineStr">
@@ -16418,35 +16644,35 @@
           <t>OUTPUT 1 — MTP completeness (all functional gaps: add to the MTP)</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP*")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">   ...of which already eng-covered (add to MTP only, do NOT automate)</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP only*")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">   ...of which QA to automate (see Output 2)</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="175" t="inlineStr">
@@ -16454,35 +16680,35 @@
           <t>OUTPUT 2 — QA automation backlog (functional gaps NOT eng-covered)</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">   QA-owned (real device/SMS/push - eng cannot cover)</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*QA-owned*")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">   Automatable, confirm w/ eng (partial coverage)</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*confirm w/ eng*")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="175" t="inlineStr">
@@ -16490,7 +16716,7 @@
           <t>DEV deliverable — unit-test-coverage gaps (eng to add unit tests)</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Dev:*")</f>
         <v/>
       </c>
@@ -16501,13 +16727,13 @@
           <t>CROSS-CUTTING — reconcile plan/code (hygiene/discrepancy)</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Reconcile*")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="175" t="inlineStr">
@@ -16515,7 +16741,7 @@
           <t>TOTAL Gap Analysis rows</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B14" s="0">
         <f>COUNTA('Gap Analysis'!$L$2:$L$1000)</f>
         <v/>
       </c>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -5,24 +5,25 @@
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name=" Test Tracker" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Login page" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Programs List page" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Opportunity creation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Opportunity List page" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Opportunity dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Connect workers page" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Visit verification page" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Invoices List page" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Connect Messaging" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Delivery Reminder Mails" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="App Credentials" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Re-Learn Task" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Microplanning" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Test Tracker Horizontal" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet name="Automation Status" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Gap Analysis" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Automation Coverage" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Coverage Tracker" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name=" Test Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Login page" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Programs List page" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Opportunity creation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Opportunity List page" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Opportunity dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Connect workers page" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Visit verification page" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Invoices List page" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Connect Messaging" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Delivery Reminder Mails" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="App Credentials" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Re-Learn Task" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Microplanning" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Test Tracker Horizontal" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet name="Automation Status" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Gap Analysis" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Automation Coverage" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -180,8 +181,15 @@
       <i val="1"/>
       <color rgb="00555555"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -293,6 +301,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -428,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -901,6 +919,27 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1746,6 +1785,1272 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="23.63" customWidth="1" style="148" min="1" max="1"/>
+    <col width="51.63" customWidth="1" style="148" min="2" max="2"/>
+    <col width="45" customWidth="1" style="148" min="3" max="3"/>
+    <col width="56.38" customWidth="1" style="148" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="148">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="54" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="55" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="E1" s="54" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="F1" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA Ticket </t>
+        </is>
+      </c>
+      <c r="G1" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comments </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="12.75" customHeight="1" s="148">
+      <c r="A2" s="76" t="n"/>
+      <c r="B2" s="76" t="inlineStr">
+        <is>
+          <t>Module: Connect Workers tab</t>
+        </is>
+      </c>
+      <c r="C2" s="153" t="n"/>
+      <c r="D2" s="153" t="n"/>
+      <c r="E2" s="153" t="n"/>
+      <c r="F2" s="153" t="n"/>
+      <c r="G2" s="154" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_01</t>
+        </is>
+      </c>
+      <c r="B3" s="68" t="inlineStr">
+        <is>
+          <t>Confirm user is redirected to the Worker's List page on clicking click on ‘Connect Workers’</t>
+        </is>
+      </c>
+      <c r="C3" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button</t>
+        </is>
+      </c>
+      <c r="D3" s="68" t="inlineStr">
+        <is>
+          <t>User should be redirected to the list of workers with all the information/details of the workers
+- Status 
+- Worker Name with ConnectID to distinguish 2 workers with the same name
+- Phone number
+- Invited date
+- Last Active in days and hours is the last time of form submission in the Learn OR Delivery app depending on whether Delivery has started
+- Started Learn timestamp
+- Completed Learn timestamp
+- Time to complete Learning
+- First Delivery timestamp
+- Time to start Delivery</t>
+        </is>
+      </c>
+      <c r="E3" s="66" t="n"/>
+      <c r="F3" s="80" t="n"/>
+      <c r="G3" s="80" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="73" t="n"/>
+      <c r="B4" s="68" t="inlineStr">
+        <is>
+          <t>Verify user is able to search connect worker using search button</t>
+        </is>
+      </c>
+      <c r="C4" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button</t>
+        </is>
+      </c>
+      <c r="D4" s="68" t="inlineStr">
+        <is>
+          <t>- Enter worker name or phone number in search field, automatic search process will apply</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="n"/>
+      <c r="F4" s="80" t="n"/>
+      <c r="G4" s="80" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_02</t>
+        </is>
+      </c>
+      <c r="B5" s="88" t="inlineStr">
+        <is>
+          <t>verify user is able to see the status as invite pending until the invitation is accepted</t>
+        </is>
+      </c>
+      <c r="C5" s="88" t="n"/>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>-The worker's status should be displayed as "Invite Pending" when hovering over the icon.</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="n"/>
+      <c r="F5" s="85" t="n"/>
+      <c r="G5" s="85" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_03</t>
+        </is>
+      </c>
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>Verify resend/delete invite buttons are enable only when user select the invites</t>
+        </is>
+      </c>
+      <c r="C6" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>- Resend invite icon [rounded arrow] and delete invites button should be enable only when users are selected</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="n"/>
+      <c r="F6" s="80" t="n"/>
+      <c r="G6" s="80" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_04</t>
+        </is>
+      </c>
+      <c r="B7" s="118" t="inlineStr">
+        <is>
+          <t>Verify worker status is updated to "invite accepted" when the invitation for an opportunity is accepted</t>
+        </is>
+      </c>
+      <c r="C7" s="118" t="n"/>
+      <c r="D7" s="118" t="inlineStr">
+        <is>
+          <t>- When worker accepts the invitation by clicking on link status should get updated to "invite accepted"</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="n"/>
+      <c r="F7" s="104" t="n"/>
+      <c r="G7" s="104" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_05</t>
+        </is>
+      </c>
+      <c r="B8" s="118" t="inlineStr">
+        <is>
+          <t>Verify we are able to pre invite the worker[Not registered for personal ID yet]</t>
+        </is>
+      </c>
+      <c r="C8" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Click on "+Add worker" button
+5. Invite user which don't have PID</t>
+        </is>
+      </c>
+      <c r="D8" s="118" t="inlineStr">
+        <is>
+          <t>- User should able to invite the worker who is not yet registered for personal ID
+- Status should be displayed as "user not found"</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="n"/>
+      <c r="F8" s="104" t="n"/>
+      <c r="G8" s="80" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_06</t>
+        </is>
+      </c>
+      <c r="B9" s="118" t="inlineStr">
+        <is>
+          <t>Verify mobile number is displayed for "not found users" under name column</t>
+        </is>
+      </c>
+      <c r="C9" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Click on "+Add worker" button
+5. Invite user which don't have PID
+6. Mobile number is displayed for such users</t>
+        </is>
+      </c>
+      <c r="D9" s="118" t="inlineStr">
+        <is>
+          <t>- User should see the mobile number  for not found users under Name column.</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="n"/>
+      <c r="F9" s="104" t="n"/>
+      <c r="G9" s="80" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_07</t>
+        </is>
+      </c>
+      <c r="B10" s="88" t="inlineStr">
+        <is>
+          <t>verify status is updated to "user suspended" when worker is suspended</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to worker visits verification page
+3. Click on the woker name
+4. Select suspend button on user details pop up</t>
+        </is>
+      </c>
+      <c r="D10" s="88" t="inlineStr">
+        <is>
+          <t>- user should be suspended from the opportunity 
+- Status should get updated to  user suspended</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="n"/>
+      <c r="F10" s="85" t="n"/>
+      <c r="G10" s="85" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_08</t>
+        </is>
+      </c>
+      <c r="B11" s="88" t="inlineStr">
+        <is>
+          <t>verify user is able to delete the pending invites</t>
+        </is>
+      </c>
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users
+5. Click on delete icon</t>
+        </is>
+      </c>
+      <c r="D11" s="68" t="inlineStr">
+        <is>
+          <t>- selected pending invites should be deleted
+- User should delete pending invites as a bulk or an individual</t>
+        </is>
+      </c>
+      <c r="E11" s="66" t="n"/>
+      <c r="F11" s="85" t="n"/>
+      <c r="G11" s="85" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_09</t>
+        </is>
+      </c>
+      <c r="B12" s="88" t="inlineStr">
+        <is>
+          <t>Verify user is not able to resend the invite for pending users within 24 hrs[Cooldown period]</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users
+5. Click on resend invite icon</t>
+        </is>
+      </c>
+      <c r="D12" s="88" t="inlineStr">
+        <is>
+          <t>- "The following invites were skipped, as they were sent in the last 24 hours" message should be displayed</t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="n"/>
+      <c r="F12" s="85" t="n"/>
+      <c r="G12" s="85" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_10</t>
+        </is>
+      </c>
+      <c r="B13" s="68" t="inlineStr">
+        <is>
+          <t>Verify user is able to resend the invite for "invite pending" worker successfully after 24 hrs</t>
+        </is>
+      </c>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users[invite pending users]
+5. Click on resend invite icon</t>
+        </is>
+      </c>
+      <c r="D13" s="88" t="inlineStr">
+        <is>
+          <t>- "Successfully invites send" message should be displayed including the number of skipped and resend invites</t>
+        </is>
+      </c>
+      <c r="E13" s="66" t="n"/>
+      <c r="F13" s="80" t="n"/>
+      <c r="G13" s="85" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_11</t>
+        </is>
+      </c>
+      <c r="B14" s="88" t="inlineStr">
+        <is>
+          <t>verify user is not able to resend/delete the invite for accepted workers</t>
+        </is>
+      </c>
+      <c r="C14" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users[accepted user]
+5. Click on resend invite icon</t>
+        </is>
+      </c>
+      <c r="D14" s="88" t="inlineStr">
+        <is>
+          <t>- "Cannot delete invite(s). Accepted invites cannot be deleted" message should be displayed
+- "The following invites were skipped, as they have already accepted" message should be displayed</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="85" t="n"/>
+      <c r="G14" s="85" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_12</t>
+        </is>
+      </c>
+      <c r="B15" s="88" t="inlineStr">
+        <is>
+          <t>verify user is not able to resend invite for not found users</t>
+        </is>
+      </c>
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users[not found user]
+5. Click on resend invite icon</t>
+        </is>
+      </c>
+      <c r="D15" s="88" t="inlineStr">
+        <is>
+          <t>- "The following invites were skipped, as they are not registered on PersonalID" message should be displayed</t>
+        </is>
+      </c>
+      <c r="E15" s="66" t="n"/>
+      <c r="F15" s="85" t="n"/>
+      <c r="G15" s="85" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_13</t>
+        </is>
+      </c>
+      <c r="B16" s="88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verify user is able to delete not found users </t>
+        </is>
+      </c>
+      <c r="C16" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users [not found user]
+5. Click on delete icon</t>
+        </is>
+      </c>
+      <c r="D16" s="88" t="inlineStr">
+        <is>
+          <t>- User should be able to delete the selected user as a bulk or an individual</t>
+        </is>
+      </c>
+      <c r="E16" s="66" t="n"/>
+      <c r="F16" s="85" t="n"/>
+      <c r="G16" s="85" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_14</t>
+        </is>
+      </c>
+      <c r="B17" s="88" t="inlineStr">
+        <is>
+          <t>verify user is not able to resend/delete invite for suspend user</t>
+        </is>
+      </c>
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users[Suspended user]
+5. Click on delete icon</t>
+        </is>
+      </c>
+      <c r="D17" s="88" t="inlineStr">
+        <is>
+          <t>- "Cannot delete invite(s). Accepted invites cannot be deleted" message should be displayed
+- "The following invites were skipped, as they have already accepted" message should be displayed</t>
+        </is>
+      </c>
+      <c r="E17" s="66" t="n"/>
+      <c r="F17" s="85" t="n"/>
+      <c r="G17" s="85" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_15</t>
+        </is>
+      </c>
+      <c r="B18" s="118" t="inlineStr">
+        <is>
+          <t>verify appropriate messages are displayed when user sends invite to all types of users as a bulk [accepted,suspended,pending,not found]</t>
+        </is>
+      </c>
+      <c r="C18" s="118" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users
+5. Click on resend invite icon</t>
+        </is>
+      </c>
+      <c r="D18" s="118" t="inlineStr">
+        <is>
+          <t>- The following messages are displayed:
+Accepted/Suspended user: "The following invites were skipped, as they have already accepted"
+Not found user: "The following invites were skipped, as they are not registered on PersonalID"
+Pending user: "Successfully sent invites" [after 24 hrs]
+"The following invites were skipped, as they were sent in the last 24 hours" [within 24 hrs]</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="n"/>
+      <c r="F18" s="104" t="n"/>
+      <c r="G18" s="104" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_16</t>
+        </is>
+      </c>
+      <c r="B19" s="118" t="inlineStr">
+        <is>
+          <t>verify appropriate messages are displayed when user delete invites of all types of users [accepted,suspended,pending,not found] as bulk</t>
+        </is>
+      </c>
+      <c r="C19" s="118" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select the connect users
+5. Click on delete icon</t>
+        </is>
+      </c>
+      <c r="D19" s="118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- The following messages are displayed:
+Accepted/Suspended user: "Cannot delete invite(s). Accepted invites cannot be deleted"
+pending/not found user: "Successfully deleted invites" </t>
+        </is>
+      </c>
+      <c r="E19" s="66" t="n"/>
+      <c r="F19" s="104" t="n"/>
+      <c r="G19" s="104" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>Connect_worker_17</t>
+        </is>
+      </c>
+      <c r="B20" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify user can sort the workers list by clicking the header columns  </t>
+        </is>
+      </c>
+      <c r="C20" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. User redirects to workers list page
+5. Sort the workers list by clicking on sort arrows</t>
+        </is>
+      </c>
+      <c r="D20" s="68" t="inlineStr">
+        <is>
+          <t>- By default, list should be in the order of recency of the ‘last active worker’ column with the most recent activity listed on top
+- User should be able to flip the list by clicking on the ‘Last Activity’ column head
+- When clicking any of the column head with dates are clicked, the list should get sorted by the most recent date of that column and reversed when clicked again
+- When the worker name column head is clicked, the list is order alphabetically by worker name
+- When the ‘days to start delivery’ column head is clicked, the rows are ordered in descending order of the value of the column</t>
+        </is>
+      </c>
+      <c r="E20" s="66" t="n"/>
+      <c r="F20" s="80" t="n"/>
+      <c r="G20" s="80" t="n"/>
+    </row>
+    <row r="21" ht="12.75" customHeight="1" s="148">
+      <c r="A21" s="76" t="n"/>
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>Module: Learn tab</t>
+        </is>
+      </c>
+      <c r="C21" s="153" t="n"/>
+      <c r="D21" s="153" t="n"/>
+      <c r="E21" s="153" t="n"/>
+      <c r="F21" s="153" t="n"/>
+      <c r="G21" s="154" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="73" t="inlineStr">
+        <is>
+          <t>Learn_tab_01</t>
+        </is>
+      </c>
+      <c r="B22" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify user can click on the Learn Tab, on the workers list page and see all the workers learn progress </t>
+        </is>
+      </c>
+      <c r="C22" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select learn tab</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User should more detailed information about user's learning progress such as 
+- Last Active represents the last form submission of Learn or Deliver app
+- Modules Completed, this should show the learn progress percentage  
+- Assessment completed or not 
+- Attempts taken to complete the assessment 
+- Learning hours represents the total spent time learning that adds up the time spent learning each module through multiple passes up until the assessment is passed
+- Clicking on the forward arrow of a worker row leads to a page that lists all the modules completed and their date of completion and time spent and should show if a module is completed all times </t>
+        </is>
+      </c>
+      <c r="E22" s="66" t="n"/>
+      <c r="F22" s="80" t="n"/>
+      <c r="G22" s="80" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="73" t="inlineStr">
+        <is>
+          <t>Learn_tab_02</t>
+        </is>
+      </c>
+      <c r="B23" s="68" t="inlineStr">
+        <is>
+          <t>Verify modules completed progress is updated as we submit learn apps is mobile</t>
+        </is>
+      </c>
+      <c r="C23" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select learn tab</t>
+        </is>
+      </c>
+      <c r="D23" s="68" t="inlineStr">
+        <is>
+          <t>- Progress percentange should increase and should be same as of mobile as user submits the learn app</t>
+        </is>
+      </c>
+      <c r="E23" s="66" t="n"/>
+      <c r="F23" s="80" t="n"/>
+      <c r="G23" s="80" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="73" t="inlineStr">
+        <is>
+          <t>Learn_tab_03</t>
+        </is>
+      </c>
+      <c r="B24" s="68" t="inlineStr">
+        <is>
+          <t>Verfiy Assessment status is shown as failed when user fails the assessment in mobile</t>
+        </is>
+      </c>
+      <c r="C24" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select learn tab</t>
+        </is>
+      </c>
+      <c r="D24" s="68" t="inlineStr">
+        <is>
+          <t>- When user fails assessment in mobile when should get updated to Failed</t>
+        </is>
+      </c>
+      <c r="E24" s="66" t="n"/>
+      <c r="F24" s="80" t="n"/>
+      <c r="G24" s="80" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="73" t="inlineStr">
+        <is>
+          <t>Learn_tab_04</t>
+        </is>
+      </c>
+      <c r="B25" s="68" t="inlineStr">
+        <is>
+          <t>Verfiy Assessment status is shown as Passed when user pass the assessment in mobile</t>
+        </is>
+      </c>
+      <c r="C25" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select learn tab</t>
+        </is>
+      </c>
+      <c r="D25" s="68" t="inlineStr">
+        <is>
+          <t>- When user pass assessment in mobile when should get updated to Passed</t>
+        </is>
+      </c>
+      <c r="E25" s="66" t="n"/>
+      <c r="F25" s="80" t="n"/>
+      <c r="G25" s="80" t="n"/>
+    </row>
+    <row r="26" ht="12.75" customHeight="1" s="148">
+      <c r="A26" s="76" t="n"/>
+      <c r="B26" s="76" t="inlineStr">
+        <is>
+          <t>Module: Delivery tab</t>
+        </is>
+      </c>
+      <c r="C26" s="153" t="n"/>
+      <c r="D26" s="153" t="n"/>
+      <c r="E26" s="153" t="n"/>
+      <c r="F26" s="153" t="n"/>
+      <c r="G26" s="154" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_01</t>
+        </is>
+      </c>
+      <c r="B27" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify user can access the delivery tab, with all the delivery information for an opportunity </t>
+        </is>
+      </c>
+      <c r="C27" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab</t>
+        </is>
+      </c>
+      <c r="D27" s="68" t="inlineStr">
+        <is>
+          <t>User should be able to land on the delivery by clicking on Total Services Delivered on the Opportunity Dashboard when I want to explore the stats for the entire list of workers</t>
+        </is>
+      </c>
+      <c r="E27" s="66" t="n"/>
+      <c r="F27" s="80" t="n"/>
+      <c r="G27" s="80" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_02</t>
+        </is>
+      </c>
+      <c r="B28" s="68" t="inlineStr">
+        <is>
+          <t>Verify user sees all the delivery details when they are on the delivery tab</t>
+        </is>
+      </c>
+      <c r="C28" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab</t>
+        </is>
+      </c>
+      <c r="D28" s="68" t="inlineStr">
+        <is>
+          <t>User should see the followig delivery information for each user 
+- The worker list should be ordered by the most recent activity in the ‘last active’ column. It should be possible to reverse this order by clicking on the column header
+- The Last Delivery column should display the timestamp of completion for that specific payment unit</t>
+        </is>
+      </c>
+      <c r="E28" s="66" t="n"/>
+      <c r="F28" s="80" t="n"/>
+      <c r="G28" s="80" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_03</t>
+        </is>
+      </c>
+      <c r="B29" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ensure when user clicks on the number in the 'Delivered' column, they see a breakdown of the deliveries </t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on count of visits </t>
+        </is>
+      </c>
+      <c r="D29" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When clicking on the number in the delivered column, user should see a breakdown of the deliveries such as 
+- Completed 
+- Over Limit 
+- Incomplete </t>
+        </is>
+      </c>
+      <c r="E29" s="66" t="n"/>
+      <c r="F29" s="80" t="n"/>
+      <c r="G29" s="80" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_05</t>
+        </is>
+      </c>
+      <c r="B30" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm on clicking the number in 'Approved' column, users can see the breakdown of th deliveries </t>
+        </is>
+      </c>
+      <c r="C30" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on count of visits </t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When clicking on the number in the Approved column, user should see a breakdown of the deliveries </t>
+        </is>
+      </c>
+      <c r="E30" s="66" t="n"/>
+      <c r="F30" s="80" t="n"/>
+      <c r="G30" s="80" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_06</t>
+        </is>
+      </c>
+      <c r="B31" s="81" t="inlineStr">
+        <is>
+          <t>Verify that the visit count is considered as 1 per payment unit, even if it includes multiple required or optional visits.</t>
+        </is>
+      </c>
+      <c r="C31" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Submit one form from mobile - verify count shows as 1
+5. Submit another form which is configured for payment unit used in above step</t>
+        </is>
+      </c>
+      <c r="D31" s="68" t="inlineStr">
+        <is>
+          <t>- Visit count should be as 1 for one payment unit even multiple required/optional visits are configured</t>
+        </is>
+      </c>
+      <c r="E31" s="66" t="n"/>
+      <c r="F31" s="80" t="n"/>
+      <c r="G31" s="80" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_07</t>
+        </is>
+      </c>
+      <c r="B32" s="68" t="inlineStr">
+        <is>
+          <t>Verify that the delivery is marked as complete when all required visits are submitted and approved, and at least one optional visit (if present) is approved.</t>
+        </is>
+      </c>
+      <c r="C32" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Submit forms from mobile - Verify that visit is shown as pending
+5. Complete all the visits(required/optional) for a particular payment unit</t>
+        </is>
+      </c>
+      <c r="D32" s="68" t="inlineStr">
+        <is>
+          <t>- Visit count is marked as complete and approved from pending state once all the visits (required/optional) for one payment unit are submitted and approved</t>
+        </is>
+      </c>
+      <c r="E32" s="66" t="n"/>
+      <c r="F32" s="80" t="n"/>
+      <c r="G32" s="80" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_09</t>
+        </is>
+      </c>
+      <c r="B33" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm on clicking the number in 'Rejected' column, users can see the breakdown of th deliveries </t>
+        </is>
+      </c>
+      <c r="C33" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on count of visits </t>
+        </is>
+      </c>
+      <c r="D33" s="68" t="inlineStr">
+        <is>
+          <t>When clicking on the number in the Approved column, user should see a breakdown of the deliveries:
+- Breakdown by flag types
+- Over Limit
+- Missing value forms
+- Duration
+- User suspended</t>
+        </is>
+      </c>
+      <c r="E33" s="66" t="n"/>
+      <c r="F33" s="80" t="n"/>
+      <c r="G33" s="80" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_10</t>
+        </is>
+      </c>
+      <c r="B34" s="118" t="inlineStr">
+        <is>
+          <t>Verify Filters pop up modal is displayed by clicking on the filters icon present in right corner  on delivery tab</t>
+        </is>
+      </c>
+      <c r="C34" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on the filters icon
+6. Apply the filters
+</t>
+        </is>
+      </c>
+      <c r="D34" s="118" t="inlineStr">
+        <is>
+          <t>pop up modal should be displayed with following fields
+- Last Active
+- Has duplicate deliveries
+- Deliveries with flags
+- Has overlimit Deliveries
+- Deliveries with pending review
+- Close and Apply buttons</t>
+        </is>
+      </c>
+      <c r="E34" s="66" t="n"/>
+      <c r="F34" s="104" t="n"/>
+      <c r="G34" s="80" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_11</t>
+        </is>
+      </c>
+      <c r="B35" s="118" t="inlineStr">
+        <is>
+          <t>Verify last active filed  dropdown contains following options:
+- Any time
+- 1 day ago
+- 3 days ago
+- 7 days ago</t>
+        </is>
+      </c>
+      <c r="C35" s="118" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+3. Click on the filters icon
+4. Click on "Last Active" field</t>
+        </is>
+      </c>
+      <c r="D35" s="118" t="inlineStr">
+        <is>
+          <t>- When user select any time, workers that are not active anytime should be displayed
+- When user select 1 day ago, workers that are not active 1 day ago should be displayed
+- When user select 3 days ago, workers that are not active 1 or 3 days ago should be displayed.
+- When user select 7 days ago, workers that are not active 1 or 3 or 7 days ago should be displayed.</t>
+        </is>
+      </c>
+      <c r="E35" s="66" t="n"/>
+      <c r="F35" s="104" t="n"/>
+      <c r="G35" s="104" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_13</t>
+        </is>
+      </c>
+      <c r="B36" s="118" t="inlineStr">
+        <is>
+          <t>Verify "Deliveries with flags"  filed  dropdown contains following options:
+- Yes
+- No</t>
+        </is>
+      </c>
+      <c r="C36" s="118" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on the filters icon
+6. Click on "Deliveries with flags"  field</t>
+        </is>
+      </c>
+      <c r="D36" s="118" t="inlineStr">
+        <is>
+          <t>- When user select Yes, workers that submitted deliveries with flag should be displayed
+- When user selects No, workers that not submitted deliveries with flag should be displayed</t>
+        </is>
+      </c>
+      <c r="E36" s="66" t="n"/>
+      <c r="F36" s="104" t="n"/>
+      <c r="G36" s="104" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_14</t>
+        </is>
+      </c>
+      <c r="B37" s="118" t="inlineStr">
+        <is>
+          <t>Verify "Has overlimit Deliveries"  filed  dropdown contains following options:
+- Yes
+- No</t>
+        </is>
+      </c>
+      <c r="C37" s="118" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on the filters icon
+6. Click on "Has overlimit Deliveries" field</t>
+        </is>
+      </c>
+      <c r="D37" s="118" t="inlineStr">
+        <is>
+          <t>- When user select Yes, workers that submitted overlimit deliveries should be displayed
+- When user selects No, workers that not submitted overlimit deliveries should be displayed</t>
+        </is>
+      </c>
+      <c r="E37" s="66" t="n"/>
+      <c r="F37" s="104" t="n"/>
+      <c r="G37" s="104" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="73" t="inlineStr">
+        <is>
+          <t>Delivery_tab_16</t>
+        </is>
+      </c>
+      <c r="B38" s="118" t="inlineStr">
+        <is>
+          <t>Ensure that all filter combinations are applied simultaneously and function correctly.</t>
+        </is>
+      </c>
+      <c r="C38" s="118" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select delivery tab
+5. Click on the filters icon
+6. Apply all the filters</t>
+        </is>
+      </c>
+      <c r="D38" s="118" t="inlineStr">
+        <is>
+          <t>- Workers should be displayed based on the selected filters</t>
+        </is>
+      </c>
+      <c r="E38" s="66" t="n"/>
+      <c r="F38" s="104" t="n"/>
+      <c r="G38" s="104" t="n"/>
+    </row>
+    <row r="39" ht="12.75" customHeight="1" s="148">
+      <c r="A39" s="76" t="n"/>
+      <c r="B39" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module: Payment processing </t>
+        </is>
+      </c>
+      <c r="C39" s="153" t="n"/>
+      <c r="D39" s="153" t="n"/>
+      <c r="E39" s="153" t="n"/>
+      <c r="F39" s="153" t="n"/>
+      <c r="G39" s="154" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="82" t="inlineStr">
+        <is>
+          <t>Payment Processing_1</t>
+        </is>
+      </c>
+      <c r="B40" s="83" t="inlineStr">
+        <is>
+          <t>Confirm user sees all the payment info under "Payments" tab on the Workers List page</t>
+        </is>
+      </c>
+      <c r="C40" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select payment tab</t>
+        </is>
+      </c>
+      <c r="D40" s="68" t="inlineStr">
+        <is>
+          <t>- On navigating to the payments tab on the workers list page, user should see following columns 
+i) Worker Name and CID
+ii) Earnings Accrued
+iii) Paid Amount
+iv) Last Paid Date
+- User should be able to see the entire history of payments for a worker by clicking on a cell in the last paid column</t>
+        </is>
+      </c>
+      <c r="E40" s="66" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="82" t="inlineStr">
+        <is>
+          <t>Payment Processing_2</t>
+        </is>
+      </c>
+      <c r="B41" s="68" t="inlineStr">
+        <is>
+          <t>Confirm user sees a message when they click on the Pay button</t>
+        </is>
+      </c>
+      <c r="C41" s="68" t="n"/>
+      <c r="D41" s="68" t="inlineStr">
+        <is>
+          <t>- User should see a transaction success or failed message when they hit the Pay button</t>
+        </is>
+      </c>
+      <c r="E41" s="66" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="82" t="inlineStr">
+        <is>
+          <t>Payment Processing_3</t>
+        </is>
+      </c>
+      <c r="B42" s="68" t="inlineStr">
+        <is>
+          <t>User should be able to see the payment history by clicking the icon</t>
+        </is>
+      </c>
+      <c r="C42" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select payment tab
+5. Click on the last paid date</t>
+        </is>
+      </c>
+      <c r="D42" s="68" t="inlineStr">
+        <is>
+          <t>User should be able to see the history of payments made:
+- Paid field should show total amount paid in that batch of payments uploaded
+- ‘X’ workers shows the number of workers paid
+- Timestamp of payment
+- User who uploaded the payment (nice-to-have)</t>
+        </is>
+      </c>
+      <c r="E42" s="66" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="82" t="inlineStr">
+        <is>
+          <t>Payment Processing_4</t>
+        </is>
+      </c>
+      <c r="B43" s="68" t="inlineStr">
+        <is>
+          <t>Confirm user can rollback a payment made to the worker</t>
+        </is>
+      </c>
+      <c r="C43" s="68" t="inlineStr">
+        <is>
+          <t>1. Login to CCC web UI
+2. Navigate to opp dashboard
+3. Click on "connect workers" button
+4. Select payment tab
+5. Click on the last paid date
+6. Click on rollback payment button</t>
+        </is>
+      </c>
+      <c r="D43" s="68" t="inlineStr">
+        <is>
+          <t>- User should be able to rollback any payment batch by hitting a button next to the payment batch in the history
+- User should see success or failure message after they rollback a payment</t>
+        </is>
+      </c>
+      <c r="E43" s="66" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B39:G39"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E3:E20 E22:E25 E27:E38 E40:E43">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="6">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="7">
+      <formula>"Blocking"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E3:E20 E22:E25 E27:E38 E40:E43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Pass,Fail,N/A,Blocking"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
@@ -3145,7 +4450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4363,7 +5668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4757,7 +6062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5062,7 +6367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -5221,7 +6526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6405,7 +7710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8499,7 +9804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -12967,7 +14272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13771,7 +15076,143 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" style="148" min="1" max="1"/>
+    <col width="12" customWidth="1" style="148" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="174" t="inlineStr">
+        <is>
+          <t>Gap Analysis — Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="175" t="inlineStr">
+        <is>
+          <t>OUTPUT 1 — MTP completeness (all functional gaps: add to the MTP)</t>
+        </is>
+      </c>
+      <c r="B3" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which already eng-covered (add to MTP only, do NOT automate)</t>
+        </is>
+      </c>
+      <c r="B4" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP only*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which QA to automate (see Output 2)</t>
+        </is>
+      </c>
+      <c r="B5" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="175" t="inlineStr">
+        <is>
+          <t>OUTPUT 2 — QA automation backlog (functional gaps NOT eng-covered)</t>
+        </is>
+      </c>
+      <c r="B7" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   QA-owned (real device/SMS/push - eng cannot cover)</t>
+        </is>
+      </c>
+      <c r="B8" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*QA-owned*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Automatable, confirm w/ eng (partial coverage)</t>
+        </is>
+      </c>
+      <c r="B9" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*confirm w/ eng*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="175" t="inlineStr">
+        <is>
+          <t>DEV deliverable — unit-test-coverage gaps (eng to add unit tests)</t>
+        </is>
+      </c>
+      <c r="B11" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Dev:*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="175" t="inlineStr">
+        <is>
+          <t>CROSS-CUTTING — reconcile plan/code (hygiene/discrepancy)</t>
+        </is>
+      </c>
+      <c r="B12" s="0">
+        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Reconcile*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="175" t="inlineStr">
+        <is>
+          <t>TOTAL Gap Analysis rows</t>
+        </is>
+      </c>
+      <c r="B14" s="0">
+        <f>COUNTA('Gap Analysis'!$L$2:$L$1000)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16615,143 +18056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="66" customWidth="1" style="148" min="1" max="1"/>
-    <col width="12" customWidth="1" style="148" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="174" t="inlineStr">
-        <is>
-          <t>Gap Analysis — Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="175" t="inlineStr">
-        <is>
-          <t>OUTPUT 1 — MTP completeness (all functional gaps: add to the MTP)</t>
-        </is>
-      </c>
-      <c r="B3" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ...of which already eng-covered (add to MTP only, do NOT automate)</t>
-        </is>
-      </c>
-      <c r="B4" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Add to MTP only*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ...of which QA to automate (see Output 2)</t>
-        </is>
-      </c>
-      <c r="B5" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="175" t="inlineStr">
-        <is>
-          <t>OUTPUT 2 — QA automation backlog (functional gaps NOT eng-covered)</t>
-        </is>
-      </c>
-      <c r="B7" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*Automate*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   QA-owned (real device/SMS/push - eng cannot cover)</t>
-        </is>
-      </c>
-      <c r="B8" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*QA-owned*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Automatable, confirm w/ eng (partial coverage)</t>
-        </is>
-      </c>
-      <c r="B9" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"*confirm w/ eng*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="175" t="inlineStr">
-        <is>
-          <t>DEV deliverable — unit-test-coverage gaps (eng to add unit tests)</t>
-        </is>
-      </c>
-      <c r="B11" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Dev:*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="175" t="inlineStr">
-        <is>
-          <t>CROSS-CUTTING — reconcile plan/code (hygiene/discrepancy)</t>
-        </is>
-      </c>
-      <c r="B12" s="0">
-        <f>COUNTIF('Gap Analysis'!$L$2:$L$1000,"Reconcile*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="175" t="inlineStr">
-        <is>
-          <t>TOTAL Gap Analysis rows</t>
-        </is>
-      </c>
-      <c r="B14" s="0">
-        <f>COUNTA('Gap Analysis'!$L$2:$L$1000)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29542,6 +30847,598 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" style="148" min="1" max="1"/>
+    <col width="20" customWidth="1" style="148" min="2" max="2"/>
+    <col width="20" customWidth="1" style="148" min="3" max="3"/>
+    <col width="20" customWidth="1" style="148" min="4" max="4"/>
+    <col width="20" customWidth="1" style="148" min="5" max="5"/>
+    <col width="20" customWidth="1" style="148" min="6" max="6"/>
+    <col width="30" customWidth="1" style="148" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="178" t="inlineStr">
+        <is>
+          <t>Coverage Tracker — automation coverage of existing MTP cases (live)</t>
+        </is>
+      </c>
+      <c r="B1" s="171" t="n"/>
+      <c r="C1" s="171" t="n"/>
+      <c r="D1" s="171" t="n"/>
+      <c r="E1" s="171" t="n"/>
+      <c r="F1" s="171" t="n"/>
+      <c r="G1" s="171" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="171" t="n"/>
+      <c r="B2" s="171" t="n"/>
+      <c r="C2" s="171" t="n"/>
+      <c r="D2" s="171" t="n"/>
+      <c r="E2" s="171" t="n"/>
+      <c r="F2" s="171" t="n"/>
+      <c r="G2" s="171" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="173" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="B3" s="173" t="inlineStr">
+        <is>
+          <t>Automated (built)</t>
+        </is>
+      </c>
+      <c r="C3" s="173" t="inlineStr">
+        <is>
+          <t>Automatable (not built)</t>
+        </is>
+      </c>
+      <c r="D3" s="173" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="E3" s="173" t="inlineStr">
+        <is>
+          <t>Total tracked</t>
+        </is>
+      </c>
+      <c r="F3" s="173" t="inlineStr">
+        <is>
+          <t>% Automated</t>
+        </is>
+      </c>
+      <c r="G3" s="173" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="171" t="inlineStr">
+        <is>
+          <t>Login page</t>
+        </is>
+      </c>
+      <c r="B4" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A4,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D4" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A4,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E4" s="171">
+        <f>B4+C4+D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="179">
+        <f>IF(E4&gt;0,B4/E4,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="171" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="171" t="inlineStr">
+        <is>
+          <t>Programs List page</t>
+        </is>
+      </c>
+      <c r="B5" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A5,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D5" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A5,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E5" s="171">
+        <f>B5+C5+D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="179">
+        <f>IF(E5&gt;0,B5/E5,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="171" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity creation</t>
+        </is>
+      </c>
+      <c r="B6" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A6,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D6" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A6,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E6" s="171">
+        <f>B6+C6+D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="179">
+        <f>IF(E6&gt;0,B6/E6,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="171" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity List page</t>
+        </is>
+      </c>
+      <c r="B7" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A7,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D7" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A7,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E7" s="171">
+        <f>B7+C7+D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="179">
+        <f>IF(E7&gt;0,B7/E7,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="171" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="171" t="inlineStr">
+        <is>
+          <t>Opportunity dashboard</t>
+        </is>
+      </c>
+      <c r="B8" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A8,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D8" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A8,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E8" s="171">
+        <f>B8+C8+D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="179">
+        <f>IF(E8&gt;0,B8/E8,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="171" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="B9" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A9,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D9" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A9,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E9" s="171">
+        <f>B9+C9+D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="179">
+        <f>IF(E9&gt;0,B9/E9,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="171" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="B10" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A10,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D10" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A10,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E10" s="171">
+        <f>B10+C10+D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="179">
+        <f>IF(E10&gt;0,B10/E10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="171" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="171" t="inlineStr">
+        <is>
+          <t>Invoices List page</t>
+        </is>
+      </c>
+      <c r="B11" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A11,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D11" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A11,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E11" s="171">
+        <f>B11+C11+D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="179">
+        <f>IF(E11&gt;0,B11/E11,0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="171" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="171" t="inlineStr">
+        <is>
+          <t>Connect Messaging</t>
+        </is>
+      </c>
+      <c r="B12" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A12,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D12" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A12,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E12" s="171">
+        <f>B12+C12+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="179">
+        <f>IF(E12&gt;0,B12/E12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="171" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t>Delivery Reminder Mails</t>
+        </is>
+      </c>
+      <c r="B13" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A13,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D13" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A13,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E13" s="171">
+        <f>B13+C13+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="179">
+        <f>IF(E13&gt;0,B13/E13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="171" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="171" t="inlineStr">
+        <is>
+          <t>App Credentials</t>
+        </is>
+      </c>
+      <c r="B14" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A14,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D14" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A14,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E14" s="171">
+        <f>B14+C14+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="179">
+        <f>IF(E14&gt;0,B14/E14,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="171" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="171" t="inlineStr">
+        <is>
+          <t>Re-Learn Task</t>
+        </is>
+      </c>
+      <c r="B15" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A15,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D15" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A15,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E15" s="171">
+        <f>B15+C15+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="179">
+        <f>IF(E15&gt;0,B15/E15,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="171" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="171" t="inlineStr">
+        <is>
+          <t>Microplanning</t>
+        </is>
+      </c>
+      <c r="B16" s="171">
+        <f>COUNTIF('Automation Status'!$A:$A,$A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A16,'Automation Coverage'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D16" s="171">
+        <f>COUNTIFS('Automation Coverage'!$B:$B,$A16,'Automation Coverage'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E16" s="171">
+        <f>B16+C16+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="179">
+        <f>IF(E16&gt;0,B16/E16,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="171" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="180" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="180">
+        <f>SUM(B4:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="180">
+        <f>SUM(C4:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="180">
+        <f>SUM(D4:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="180">
+        <f>SUM(E4:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="181">
+        <f>IF(E17&gt;0,B17/E17,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="180" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="171" t="n"/>
+      <c r="B18" s="171" t="n"/>
+      <c r="C18" s="171" t="n"/>
+      <c r="D18" s="171" t="n"/>
+      <c r="E18" s="171" t="n"/>
+      <c r="F18" s="171" t="n"/>
+      <c r="G18" s="171" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="182" t="inlineStr">
+        <is>
+          <t>Gap Analysis — new findings from source analysis (not in the counts above)</t>
+        </is>
+      </c>
+      <c r="B19" s="171" t="n"/>
+      <c r="C19" s="171" t="n"/>
+      <c r="D19" s="171" t="n"/>
+      <c r="E19" s="171" t="n"/>
+      <c r="F19" s="171" t="n"/>
+      <c r="G19" s="171" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="183" t="inlineStr">
+        <is>
+          <t>Output 1: functional gaps to ADD to MTP</t>
+        </is>
+      </c>
+      <c r="B20" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Add to MTP*")</f>
+        <v/>
+      </c>
+      <c r="C20" s="171" t="n"/>
+      <c r="D20" s="171" t="n"/>
+      <c r="E20" s="171" t="n"/>
+      <c r="F20" s="171" t="n"/>
+      <c r="G20" s="171" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which eng-covered (add to MTP only, do NOT automate)</t>
+        </is>
+      </c>
+      <c r="B21" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Add to MTP only*")</f>
+        <v/>
+      </c>
+      <c r="C21" s="171" t="n"/>
+      <c r="D21" s="171" t="n"/>
+      <c r="E21" s="171" t="n"/>
+      <c r="F21" s="171" t="n"/>
+      <c r="G21" s="171" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="183" t="inlineStr">
+        <is>
+          <t>Output 2: functional gaps to AUTOMATE (QA backlog)</t>
+        </is>
+      </c>
+      <c r="B22" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"*Automate*")</f>
+        <v/>
+      </c>
+      <c r="C22" s="171" t="n"/>
+      <c r="D22" s="171" t="n"/>
+      <c r="E22" s="171" t="n"/>
+      <c r="F22" s="171" t="n"/>
+      <c r="G22" s="171" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which manual-only (red bucket)</t>
+        </is>
+      </c>
+      <c r="B23" s="171">
+        <f>COUNTIF('Gap Analysis'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="C23" s="171" t="n"/>
+      <c r="D23" s="171" t="n"/>
+      <c r="E23" s="171" t="n"/>
+      <c r="F23" s="171" t="n"/>
+      <c r="G23" s="171" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="183" t="inlineStr">
+        <is>
+          <t>Dev: unit-test-coverage gaps</t>
+        </is>
+      </c>
+      <c r="B24" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Dev:*")</f>
+        <v/>
+      </c>
+      <c r="C24" s="171" t="n"/>
+      <c r="D24" s="171" t="n"/>
+      <c r="E24" s="171" t="n"/>
+      <c r="F24" s="171" t="n"/>
+      <c r="G24" s="171" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="183" t="inlineStr">
+        <is>
+          <t>Cross-cutting: reconcile plan/code</t>
+        </is>
+      </c>
+      <c r="B25" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Reconcile*")</f>
+        <v/>
+      </c>
+      <c r="C25" s="171" t="n"/>
+      <c r="D25" s="171" t="n"/>
+      <c r="E25" s="171" t="n"/>
+      <c r="F25" s="171" t="n"/>
+      <c r="G25" s="171" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30572,7 +32469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30916,7 +32813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31447,7 +33344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -32339,7 +34236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33241,7 +35138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33983,1270 +35880,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="23.63" customWidth="1" style="148" min="1" max="1"/>
-    <col width="51.63" customWidth="1" style="148" min="2" max="2"/>
-    <col width="45" customWidth="1" style="148" min="3" max="3"/>
-    <col width="56.38" customWidth="1" style="148" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="148">
-      <c r="A1" s="54" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B1" s="54" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" s="54" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="D1" s="55" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E1" s="54" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="F1" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QA Ticket </t>
-        </is>
-      </c>
-      <c r="G1" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comments </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="12.75" customHeight="1" s="148">
-      <c r="A2" s="76" t="n"/>
-      <c r="B2" s="76" t="inlineStr">
-        <is>
-          <t>Module: Connect Workers tab</t>
-        </is>
-      </c>
-      <c r="C2" s="153" t="n"/>
-      <c r="D2" s="153" t="n"/>
-      <c r="E2" s="153" t="n"/>
-      <c r="F2" s="153" t="n"/>
-      <c r="G2" s="154" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_01</t>
-        </is>
-      </c>
-      <c r="B3" s="68" t="inlineStr">
-        <is>
-          <t>Confirm user is redirected to the Worker's List page on clicking click on ‘Connect Workers’</t>
-        </is>
-      </c>
-      <c r="C3" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button</t>
-        </is>
-      </c>
-      <c r="D3" s="68" t="inlineStr">
-        <is>
-          <t>User should be redirected to the list of workers with all the information/details of the workers
-- Status 
-- Worker Name with ConnectID to distinguish 2 workers with the same name
-- Phone number
-- Invited date
-- Last Active in days and hours is the last time of form submission in the Learn OR Delivery app depending on whether Delivery has started
-- Started Learn timestamp
-- Completed Learn timestamp
-- Time to complete Learning
-- First Delivery timestamp
-- Time to start Delivery</t>
-        </is>
-      </c>
-      <c r="E3" s="66" t="n"/>
-      <c r="F3" s="80" t="n"/>
-      <c r="G3" s="80" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="73" t="n"/>
-      <c r="B4" s="68" t="inlineStr">
-        <is>
-          <t>Verify user is able to search connect worker using search button</t>
-        </is>
-      </c>
-      <c r="C4" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button</t>
-        </is>
-      </c>
-      <c r="D4" s="68" t="inlineStr">
-        <is>
-          <t>- Enter worker name or phone number in search field, automatic search process will apply</t>
-        </is>
-      </c>
-      <c r="E4" s="66" t="n"/>
-      <c r="F4" s="80" t="n"/>
-      <c r="G4" s="80" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_02</t>
-        </is>
-      </c>
-      <c r="B5" s="88" t="inlineStr">
-        <is>
-          <t>verify user is able to see the status as invite pending until the invitation is accepted</t>
-        </is>
-      </c>
-      <c r="C5" s="88" t="n"/>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>-The worker's status should be displayed as "Invite Pending" when hovering over the icon.</t>
-        </is>
-      </c>
-      <c r="E5" s="66" t="n"/>
-      <c r="F5" s="85" t="n"/>
-      <c r="G5" s="85" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_03</t>
-        </is>
-      </c>
-      <c r="B6" s="68" t="inlineStr">
-        <is>
-          <t>Verify resend/delete invite buttons are enable only when user select the invites</t>
-        </is>
-      </c>
-      <c r="C6" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users</t>
-        </is>
-      </c>
-      <c r="D6" s="68" t="inlineStr">
-        <is>
-          <t>- Resend invite icon [rounded arrow] and delete invites button should be enable only when users are selected</t>
-        </is>
-      </c>
-      <c r="E6" s="66" t="n"/>
-      <c r="F6" s="80" t="n"/>
-      <c r="G6" s="80" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_04</t>
-        </is>
-      </c>
-      <c r="B7" s="118" t="inlineStr">
-        <is>
-          <t>Verify worker status is updated to "invite accepted" when the invitation for an opportunity is accepted</t>
-        </is>
-      </c>
-      <c r="C7" s="118" t="n"/>
-      <c r="D7" s="118" t="inlineStr">
-        <is>
-          <t>- When worker accepts the invitation by clicking on link status should get updated to "invite accepted"</t>
-        </is>
-      </c>
-      <c r="E7" s="66" t="n"/>
-      <c r="F7" s="104" t="n"/>
-      <c r="G7" s="104" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_05</t>
-        </is>
-      </c>
-      <c r="B8" s="118" t="inlineStr">
-        <is>
-          <t>Verify we are able to pre invite the worker[Not registered for personal ID yet]</t>
-        </is>
-      </c>
-      <c r="C8" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Click on "+Add worker" button
-5. Invite user which don't have PID</t>
-        </is>
-      </c>
-      <c r="D8" s="118" t="inlineStr">
-        <is>
-          <t>- User should able to invite the worker who is not yet registered for personal ID
-- Status should be displayed as "user not found"</t>
-        </is>
-      </c>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="104" t="n"/>
-      <c r="G8" s="80" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_06</t>
-        </is>
-      </c>
-      <c r="B9" s="118" t="inlineStr">
-        <is>
-          <t>Verify mobile number is displayed for "not found users" under name column</t>
-        </is>
-      </c>
-      <c r="C9" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Click on "+Add worker" button
-5. Invite user which don't have PID
-6. Mobile number is displayed for such users</t>
-        </is>
-      </c>
-      <c r="D9" s="118" t="inlineStr">
-        <is>
-          <t>- User should see the mobile number  for not found users under Name column.</t>
-        </is>
-      </c>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="104" t="n"/>
-      <c r="G9" s="80" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_07</t>
-        </is>
-      </c>
-      <c r="B10" s="88" t="inlineStr">
-        <is>
-          <t>verify status is updated to "user suspended" when worker is suspended</t>
-        </is>
-      </c>
-      <c r="C10" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to worker visits verification page
-3. Click on the woker name
-4. Select suspend button on user details pop up</t>
-        </is>
-      </c>
-      <c r="D10" s="88" t="inlineStr">
-        <is>
-          <t>- user should be suspended from the opportunity 
-- Status should get updated to  user suspended</t>
-        </is>
-      </c>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="85" t="n"/>
-      <c r="G10" s="85" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_08</t>
-        </is>
-      </c>
-      <c r="B11" s="88" t="inlineStr">
-        <is>
-          <t>verify user is able to delete the pending invites</t>
-        </is>
-      </c>
-      <c r="C11" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users
-5. Click on delete icon</t>
-        </is>
-      </c>
-      <c r="D11" s="68" t="inlineStr">
-        <is>
-          <t>- selected pending invites should be deleted
-- User should delete pending invites as a bulk or an individual</t>
-        </is>
-      </c>
-      <c r="E11" s="66" t="n"/>
-      <c r="F11" s="85" t="n"/>
-      <c r="G11" s="85" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_09</t>
-        </is>
-      </c>
-      <c r="B12" s="88" t="inlineStr">
-        <is>
-          <t>Verify user is not able to resend the invite for pending users within 24 hrs[Cooldown period]</t>
-        </is>
-      </c>
-      <c r="C12" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users
-5. Click on resend invite icon</t>
-        </is>
-      </c>
-      <c r="D12" s="88" t="inlineStr">
-        <is>
-          <t>- "The following invites were skipped, as they were sent in the last 24 hours" message should be displayed</t>
-        </is>
-      </c>
-      <c r="E12" s="66" t="n"/>
-      <c r="F12" s="85" t="n"/>
-      <c r="G12" s="85" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_10</t>
-        </is>
-      </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>Verify user is able to resend the invite for "invite pending" worker successfully after 24 hrs</t>
-        </is>
-      </c>
-      <c r="C13" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users[invite pending users]
-5. Click on resend invite icon</t>
-        </is>
-      </c>
-      <c r="D13" s="88" t="inlineStr">
-        <is>
-          <t>- "Successfully invites send" message should be displayed including the number of skipped and resend invites</t>
-        </is>
-      </c>
-      <c r="E13" s="66" t="n"/>
-      <c r="F13" s="80" t="n"/>
-      <c r="G13" s="85" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_11</t>
-        </is>
-      </c>
-      <c r="B14" s="88" t="inlineStr">
-        <is>
-          <t>verify user is not able to resend/delete the invite for accepted workers</t>
-        </is>
-      </c>
-      <c r="C14" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users[accepted user]
-5. Click on resend invite icon</t>
-        </is>
-      </c>
-      <c r="D14" s="88" t="inlineStr">
-        <is>
-          <t>- "Cannot delete invite(s). Accepted invites cannot be deleted" message should be displayed
-- "The following invites were skipped, as they have already accepted" message should be displayed</t>
-        </is>
-      </c>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="85" t="n"/>
-      <c r="G14" s="85" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_12</t>
-        </is>
-      </c>
-      <c r="B15" s="88" t="inlineStr">
-        <is>
-          <t>verify user is not able to resend invite for not found users</t>
-        </is>
-      </c>
-      <c r="C15" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users[not found user]
-5. Click on resend invite icon</t>
-        </is>
-      </c>
-      <c r="D15" s="88" t="inlineStr">
-        <is>
-          <t>- "The following invites were skipped, as they are not registered on PersonalID" message should be displayed</t>
-        </is>
-      </c>
-      <c r="E15" s="66" t="n"/>
-      <c r="F15" s="85" t="n"/>
-      <c r="G15" s="85" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_13</t>
-        </is>
-      </c>
-      <c r="B16" s="88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">verify user is able to delete not found users </t>
-        </is>
-      </c>
-      <c r="C16" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users [not found user]
-5. Click on delete icon</t>
-        </is>
-      </c>
-      <c r="D16" s="88" t="inlineStr">
-        <is>
-          <t>- User should be able to delete the selected user as a bulk or an individual</t>
-        </is>
-      </c>
-      <c r="E16" s="66" t="n"/>
-      <c r="F16" s="85" t="n"/>
-      <c r="G16" s="85" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_14</t>
-        </is>
-      </c>
-      <c r="B17" s="88" t="inlineStr">
-        <is>
-          <t>verify user is not able to resend/delete invite for suspend user</t>
-        </is>
-      </c>
-      <c r="C17" s="88" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users[Suspended user]
-5. Click on delete icon</t>
-        </is>
-      </c>
-      <c r="D17" s="88" t="inlineStr">
-        <is>
-          <t>- "Cannot delete invite(s). Accepted invites cannot be deleted" message should be displayed
-- "The following invites were skipped, as they have already accepted" message should be displayed</t>
-        </is>
-      </c>
-      <c r="E17" s="66" t="n"/>
-      <c r="F17" s="85" t="n"/>
-      <c r="G17" s="85" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_15</t>
-        </is>
-      </c>
-      <c r="B18" s="118" t="inlineStr">
-        <is>
-          <t>verify appropriate messages are displayed when user sends invite to all types of users as a bulk [accepted,suspended,pending,not found]</t>
-        </is>
-      </c>
-      <c r="C18" s="118" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users
-5. Click on resend invite icon</t>
-        </is>
-      </c>
-      <c r="D18" s="118" t="inlineStr">
-        <is>
-          <t>- The following messages are displayed:
-Accepted/Suspended user: "The following invites were skipped, as they have already accepted"
-Not found user: "The following invites were skipped, as they are not registered on PersonalID"
-Pending user: "Successfully sent invites" [after 24 hrs]
-"The following invites were skipped, as they were sent in the last 24 hours" [within 24 hrs]</t>
-        </is>
-      </c>
-      <c r="E18" s="66" t="n"/>
-      <c r="F18" s="104" t="n"/>
-      <c r="G18" s="104" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_16</t>
-        </is>
-      </c>
-      <c r="B19" s="118" t="inlineStr">
-        <is>
-          <t>verify appropriate messages are displayed when user delete invites of all types of users [accepted,suspended,pending,not found] as bulk</t>
-        </is>
-      </c>
-      <c r="C19" s="118" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select the connect users
-5. Click on delete icon</t>
-        </is>
-      </c>
-      <c r="D19" s="118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- The following messages are displayed:
-Accepted/Suspended user: "Cannot delete invite(s). Accepted invites cannot be deleted"
-pending/not found user: "Successfully deleted invites" </t>
-        </is>
-      </c>
-      <c r="E19" s="66" t="n"/>
-      <c r="F19" s="104" t="n"/>
-      <c r="G19" s="104" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="73" t="inlineStr">
-        <is>
-          <t>Connect_worker_17</t>
-        </is>
-      </c>
-      <c r="B20" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify user can sort the workers list by clicking the header columns  </t>
-        </is>
-      </c>
-      <c r="C20" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. User redirects to workers list page
-5. Sort the workers list by clicking on sort arrows</t>
-        </is>
-      </c>
-      <c r="D20" s="68" t="inlineStr">
-        <is>
-          <t>- By default, list should be in the order of recency of the ‘last active worker’ column with the most recent activity listed on top
-- User should be able to flip the list by clicking on the ‘Last Activity’ column head
-- When clicking any of the column head with dates are clicked, the list should get sorted by the most recent date of that column and reversed when clicked again
-- When the worker name column head is clicked, the list is order alphabetically by worker name
-- When the ‘days to start delivery’ column head is clicked, the rows are ordered in descending order of the value of the column</t>
-        </is>
-      </c>
-      <c r="E20" s="66" t="n"/>
-      <c r="F20" s="80" t="n"/>
-      <c r="G20" s="80" t="n"/>
-    </row>
-    <row r="21" ht="12.75" customHeight="1" s="148">
-      <c r="A21" s="76" t="n"/>
-      <c r="B21" s="76" t="inlineStr">
-        <is>
-          <t>Module: Learn tab</t>
-        </is>
-      </c>
-      <c r="C21" s="153" t="n"/>
-      <c r="D21" s="153" t="n"/>
-      <c r="E21" s="153" t="n"/>
-      <c r="F21" s="153" t="n"/>
-      <c r="G21" s="154" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="73" t="inlineStr">
-        <is>
-          <t>Learn_tab_01</t>
-        </is>
-      </c>
-      <c r="B22" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify user can click on the Learn Tab, on the workers list page and see all the workers learn progress </t>
-        </is>
-      </c>
-      <c r="C22" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select learn tab</t>
-        </is>
-      </c>
-      <c r="D22" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">User should more detailed information about user's learning progress such as 
-- Last Active represents the last form submission of Learn or Deliver app
-- Modules Completed, this should show the learn progress percentage  
-- Assessment completed or not 
-- Attempts taken to complete the assessment 
-- Learning hours represents the total spent time learning that adds up the time spent learning each module through multiple passes up until the assessment is passed
-- Clicking on the forward arrow of a worker row leads to a page that lists all the modules completed and their date of completion and time spent and should show if a module is completed all times </t>
-        </is>
-      </c>
-      <c r="E22" s="66" t="n"/>
-      <c r="F22" s="80" t="n"/>
-      <c r="G22" s="80" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="73" t="inlineStr">
-        <is>
-          <t>Learn_tab_02</t>
-        </is>
-      </c>
-      <c r="B23" s="68" t="inlineStr">
-        <is>
-          <t>Verify modules completed progress is updated as we submit learn apps is mobile</t>
-        </is>
-      </c>
-      <c r="C23" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select learn tab</t>
-        </is>
-      </c>
-      <c r="D23" s="68" t="inlineStr">
-        <is>
-          <t>- Progress percentange should increase and should be same as of mobile as user submits the learn app</t>
-        </is>
-      </c>
-      <c r="E23" s="66" t="n"/>
-      <c r="F23" s="80" t="n"/>
-      <c r="G23" s="80" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="73" t="inlineStr">
-        <is>
-          <t>Learn_tab_03</t>
-        </is>
-      </c>
-      <c r="B24" s="68" t="inlineStr">
-        <is>
-          <t>Verfiy Assessment status is shown as failed when user fails the assessment in mobile</t>
-        </is>
-      </c>
-      <c r="C24" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select learn tab</t>
-        </is>
-      </c>
-      <c r="D24" s="68" t="inlineStr">
-        <is>
-          <t>- When user fails assessment in mobile when should get updated to Failed</t>
-        </is>
-      </c>
-      <c r="E24" s="66" t="n"/>
-      <c r="F24" s="80" t="n"/>
-      <c r="G24" s="80" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="73" t="inlineStr">
-        <is>
-          <t>Learn_tab_04</t>
-        </is>
-      </c>
-      <c r="B25" s="68" t="inlineStr">
-        <is>
-          <t>Verfiy Assessment status is shown as Passed when user pass the assessment in mobile</t>
-        </is>
-      </c>
-      <c r="C25" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select learn tab</t>
-        </is>
-      </c>
-      <c r="D25" s="68" t="inlineStr">
-        <is>
-          <t>- When user pass assessment in mobile when should get updated to Passed</t>
-        </is>
-      </c>
-      <c r="E25" s="66" t="n"/>
-      <c r="F25" s="80" t="n"/>
-      <c r="G25" s="80" t="n"/>
-    </row>
-    <row r="26" ht="12.75" customHeight="1" s="148">
-      <c r="A26" s="76" t="n"/>
-      <c r="B26" s="76" t="inlineStr">
-        <is>
-          <t>Module: Delivery tab</t>
-        </is>
-      </c>
-      <c r="C26" s="153" t="n"/>
-      <c r="D26" s="153" t="n"/>
-      <c r="E26" s="153" t="n"/>
-      <c r="F26" s="153" t="n"/>
-      <c r="G26" s="154" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_01</t>
-        </is>
-      </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify user can access the delivery tab, with all the delivery information for an opportunity </t>
-        </is>
-      </c>
-      <c r="C27" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab</t>
-        </is>
-      </c>
-      <c r="D27" s="68" t="inlineStr">
-        <is>
-          <t>User should be able to land on the delivery by clicking on Total Services Delivered on the Opportunity Dashboard when I want to explore the stats for the entire list of workers</t>
-        </is>
-      </c>
-      <c r="E27" s="66" t="n"/>
-      <c r="F27" s="80" t="n"/>
-      <c r="G27" s="80" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_02</t>
-        </is>
-      </c>
-      <c r="B28" s="68" t="inlineStr">
-        <is>
-          <t>Verify user sees all the delivery details when they are on the delivery tab</t>
-        </is>
-      </c>
-      <c r="C28" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab</t>
-        </is>
-      </c>
-      <c r="D28" s="68" t="inlineStr">
-        <is>
-          <t>User should see the followig delivery information for each user 
-- The worker list should be ordered by the most recent activity in the ‘last active’ column. It should be possible to reverse this order by clicking on the column header
-- The Last Delivery column should display the timestamp of completion for that specific payment unit</t>
-        </is>
-      </c>
-      <c r="E28" s="66" t="n"/>
-      <c r="F28" s="80" t="n"/>
-      <c r="G28" s="80" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_03</t>
-        </is>
-      </c>
-      <c r="B29" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ensure when user clicks on the number in the 'Delivered' column, they see a breakdown of the deliveries </t>
-        </is>
-      </c>
-      <c r="C29" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on count of visits </t>
-        </is>
-      </c>
-      <c r="D29" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When clicking on the number in the delivered column, user should see a breakdown of the deliveries such as 
-- Completed 
-- Over Limit 
-- Incomplete </t>
-        </is>
-      </c>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="80" t="n"/>
-      <c r="G29" s="80" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_05</t>
-        </is>
-      </c>
-      <c r="B30" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirm on clicking the number in 'Approved' column, users can see the breakdown of th deliveries </t>
-        </is>
-      </c>
-      <c r="C30" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on count of visits </t>
-        </is>
-      </c>
-      <c r="D30" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">When clicking on the number in the Approved column, user should see a breakdown of the deliveries </t>
-        </is>
-      </c>
-      <c r="E30" s="66" t="n"/>
-      <c r="F30" s="80" t="n"/>
-      <c r="G30" s="80" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_06</t>
-        </is>
-      </c>
-      <c r="B31" s="81" t="inlineStr">
-        <is>
-          <t>Verify that the visit count is considered as 1 per payment unit, even if it includes multiple required or optional visits.</t>
-        </is>
-      </c>
-      <c r="C31" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Submit one form from mobile - verify count shows as 1
-5. Submit another form which is configured for payment unit used in above step</t>
-        </is>
-      </c>
-      <c r="D31" s="68" t="inlineStr">
-        <is>
-          <t>- Visit count should be as 1 for one payment unit even multiple required/optional visits are configured</t>
-        </is>
-      </c>
-      <c r="E31" s="66" t="n"/>
-      <c r="F31" s="80" t="n"/>
-      <c r="G31" s="80" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_07</t>
-        </is>
-      </c>
-      <c r="B32" s="68" t="inlineStr">
-        <is>
-          <t>Verify that the delivery is marked as complete when all required visits are submitted and approved, and at least one optional visit (if present) is approved.</t>
-        </is>
-      </c>
-      <c r="C32" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Submit forms from mobile - Verify that visit is shown as pending
-5. Complete all the visits(required/optional) for a particular payment unit</t>
-        </is>
-      </c>
-      <c r="D32" s="68" t="inlineStr">
-        <is>
-          <t>- Visit count is marked as complete and approved from pending state once all the visits (required/optional) for one payment unit are submitted and approved</t>
-        </is>
-      </c>
-      <c r="E32" s="66" t="n"/>
-      <c r="F32" s="80" t="n"/>
-      <c r="G32" s="80" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_09</t>
-        </is>
-      </c>
-      <c r="B33" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirm on clicking the number in 'Rejected' column, users can see the breakdown of th deliveries </t>
-        </is>
-      </c>
-      <c r="C33" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on count of visits </t>
-        </is>
-      </c>
-      <c r="D33" s="68" t="inlineStr">
-        <is>
-          <t>When clicking on the number in the Approved column, user should see a breakdown of the deliveries:
-- Breakdown by flag types
-- Over Limit
-- Missing value forms
-- Duration
-- User suspended</t>
-        </is>
-      </c>
-      <c r="E33" s="66" t="n"/>
-      <c r="F33" s="80" t="n"/>
-      <c r="G33" s="80" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_10</t>
-        </is>
-      </c>
-      <c r="B34" s="118" t="inlineStr">
-        <is>
-          <t>Verify Filters pop up modal is displayed by clicking on the filters icon present in right corner  on delivery tab</t>
-        </is>
-      </c>
-      <c r="C34" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on the filters icon
-6. Apply the filters
-</t>
-        </is>
-      </c>
-      <c r="D34" s="118" t="inlineStr">
-        <is>
-          <t>pop up modal should be displayed with following fields
-- Last Active
-- Has duplicate deliveries
-- Deliveries with flags
-- Has overlimit Deliveries
-- Deliveries with pending review
-- Close and Apply buttons</t>
-        </is>
-      </c>
-      <c r="E34" s="66" t="n"/>
-      <c r="F34" s="104" t="n"/>
-      <c r="G34" s="80" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_11</t>
-        </is>
-      </c>
-      <c r="B35" s="118" t="inlineStr">
-        <is>
-          <t>Verify last active filed  dropdown contains following options:
-- Any time
-- 1 day ago
-- 3 days ago
-- 7 days ago</t>
-        </is>
-      </c>
-      <c r="C35" s="118" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-3. Click on the filters icon
-4. Click on "Last Active" field</t>
-        </is>
-      </c>
-      <c r="D35" s="118" t="inlineStr">
-        <is>
-          <t>- When user select any time, workers that are not active anytime should be displayed
-- When user select 1 day ago, workers that are not active 1 day ago should be displayed
-- When user select 3 days ago, workers that are not active 1 or 3 days ago should be displayed.
-- When user select 7 days ago, workers that are not active 1 or 3 or 7 days ago should be displayed.</t>
-        </is>
-      </c>
-      <c r="E35" s="66" t="n"/>
-      <c r="F35" s="104" t="n"/>
-      <c r="G35" s="104" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_13</t>
-        </is>
-      </c>
-      <c r="B36" s="118" t="inlineStr">
-        <is>
-          <t>Verify "Deliveries with flags"  filed  dropdown contains following options:
-- Yes
-- No</t>
-        </is>
-      </c>
-      <c r="C36" s="118" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on the filters icon
-6. Click on "Deliveries with flags"  field</t>
-        </is>
-      </c>
-      <c r="D36" s="118" t="inlineStr">
-        <is>
-          <t>- When user select Yes, workers that submitted deliveries with flag should be displayed
-- When user selects No, workers that not submitted deliveries with flag should be displayed</t>
-        </is>
-      </c>
-      <c r="E36" s="66" t="n"/>
-      <c r="F36" s="104" t="n"/>
-      <c r="G36" s="104" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_14</t>
-        </is>
-      </c>
-      <c r="B37" s="118" t="inlineStr">
-        <is>
-          <t>Verify "Has overlimit Deliveries"  filed  dropdown contains following options:
-- Yes
-- No</t>
-        </is>
-      </c>
-      <c r="C37" s="118" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on the filters icon
-6. Click on "Has overlimit Deliveries" field</t>
-        </is>
-      </c>
-      <c r="D37" s="118" t="inlineStr">
-        <is>
-          <t>- When user select Yes, workers that submitted overlimit deliveries should be displayed
-- When user selects No, workers that not submitted overlimit deliveries should be displayed</t>
-        </is>
-      </c>
-      <c r="E37" s="66" t="n"/>
-      <c r="F37" s="104" t="n"/>
-      <c r="G37" s="104" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="73" t="inlineStr">
-        <is>
-          <t>Delivery_tab_16</t>
-        </is>
-      </c>
-      <c r="B38" s="118" t="inlineStr">
-        <is>
-          <t>Ensure that all filter combinations are applied simultaneously and function correctly.</t>
-        </is>
-      </c>
-      <c r="C38" s="118" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select delivery tab
-5. Click on the filters icon
-6. Apply all the filters</t>
-        </is>
-      </c>
-      <c r="D38" s="118" t="inlineStr">
-        <is>
-          <t>- Workers should be displayed based on the selected filters</t>
-        </is>
-      </c>
-      <c r="E38" s="66" t="n"/>
-      <c r="F38" s="104" t="n"/>
-      <c r="G38" s="104" t="n"/>
-    </row>
-    <row r="39" ht="12.75" customHeight="1" s="148">
-      <c r="A39" s="76" t="n"/>
-      <c r="B39" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Module: Payment processing </t>
-        </is>
-      </c>
-      <c r="C39" s="153" t="n"/>
-      <c r="D39" s="153" t="n"/>
-      <c r="E39" s="153" t="n"/>
-      <c r="F39" s="153" t="n"/>
-      <c r="G39" s="154" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="82" t="inlineStr">
-        <is>
-          <t>Payment Processing_1</t>
-        </is>
-      </c>
-      <c r="B40" s="83" t="inlineStr">
-        <is>
-          <t>Confirm user sees all the payment info under "Payments" tab on the Workers List page</t>
-        </is>
-      </c>
-      <c r="C40" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select payment tab</t>
-        </is>
-      </c>
-      <c r="D40" s="68" t="inlineStr">
-        <is>
-          <t>- On navigating to the payments tab on the workers list page, user should see following columns 
-i) Worker Name and CID
-ii) Earnings Accrued
-iii) Paid Amount
-iv) Last Paid Date
-- User should be able to see the entire history of payments for a worker by clicking on a cell in the last paid column</t>
-        </is>
-      </c>
-      <c r="E40" s="66" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="82" t="inlineStr">
-        <is>
-          <t>Payment Processing_2</t>
-        </is>
-      </c>
-      <c r="B41" s="68" t="inlineStr">
-        <is>
-          <t>Confirm user sees a message when they click on the Pay button</t>
-        </is>
-      </c>
-      <c r="C41" s="68" t="n"/>
-      <c r="D41" s="68" t="inlineStr">
-        <is>
-          <t>- User should see a transaction success or failed message when they hit the Pay button</t>
-        </is>
-      </c>
-      <c r="E41" s="66" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="82" t="inlineStr">
-        <is>
-          <t>Payment Processing_3</t>
-        </is>
-      </c>
-      <c r="B42" s="68" t="inlineStr">
-        <is>
-          <t>User should be able to see the payment history by clicking the icon</t>
-        </is>
-      </c>
-      <c r="C42" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select payment tab
-5. Click on the last paid date</t>
-        </is>
-      </c>
-      <c r="D42" s="68" t="inlineStr">
-        <is>
-          <t>User should be able to see the history of payments made:
-- Paid field should show total amount paid in that batch of payments uploaded
-- ‘X’ workers shows the number of workers paid
-- Timestamp of payment
-- User who uploaded the payment (nice-to-have)</t>
-        </is>
-      </c>
-      <c r="E42" s="66" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="82" t="inlineStr">
-        <is>
-          <t>Payment Processing_4</t>
-        </is>
-      </c>
-      <c r="B43" s="68" t="inlineStr">
-        <is>
-          <t>Confirm user can rollback a payment made to the worker</t>
-        </is>
-      </c>
-      <c r="C43" s="68" t="inlineStr">
-        <is>
-          <t>1. Login to CCC web UI
-2. Navigate to opp dashboard
-3. Click on "connect workers" button
-4. Select payment tab
-5. Click on the last paid date
-6. Click on rollback payment button</t>
-        </is>
-      </c>
-      <c r="D43" s="68" t="inlineStr">
-        <is>
-          <t>- User should be able to rollback any payment batch by hitting a button next to the payment batch in the history
-- User should see success or failure message after they rollback a payment</t>
-        </is>
-      </c>
-      <c r="E43" s="66" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B39:G39"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E3:E20 E22:E25 E27:E38 E40:E43">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
-      <formula>"Pass"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
-      <formula>"Fail"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="6">
-      <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="7">
-      <formula>"Blocking"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="E3:E20 E22:E25 E27:E38 E40:E43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A,Blocking"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -444,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -938,6 +938,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14832,7 +14833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" style="148" min="1" max="1"/>
@@ -15441,6 +15442,36 @@
         <v/>
       </c>
       <c r="G27" s="180" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="185" t="inlineStr">
+        <is>
+          <t>EXISTING automatable-not-built cases — do they need automating?</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - need automating)</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>COUNTIF('Automation (existing MTP)'!$G:$G,"QA-owned (UI*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="171" t="inlineStr">
+        <is>
+          <t>Likely already eng-covered (confirm - may NOT need automating)</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>COUNTIF('Automation (existing MTP)'!$G:$G,"Partial*")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18297,7 +18328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F317"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -18306,6 +18337,7 @@
     <col width="26" customWidth="1" style="148" min="4" max="4"/>
     <col width="45" customWidth="1" style="148" min="5" max="5"/>
     <col width="26" customWidth="1" style="148" min="6" max="6"/>
+    <col width="44" customWidth="1" style="148" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18339,6 +18371,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="G1" s="170" t="inlineStr">
+        <is>
+          <t>Eng Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="171" t="inlineStr">
@@ -18371,6 +18408,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G2" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="171" t="inlineStr">
@@ -18403,6 +18445,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G3" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="171" t="inlineStr">
@@ -18435,6 +18482,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G4" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="171" t="inlineStr">
@@ -18467,6 +18519,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G5" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="171" t="inlineStr">
@@ -18499,6 +18556,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G6" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="171" t="inlineStr">
@@ -18531,6 +18593,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G7" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="171" t="inlineStr">
@@ -18563,6 +18630,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G8" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="171" t="inlineStr">
@@ -18595,6 +18667,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G9" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="171" t="inlineStr">
@@ -18627,6 +18704,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G10" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="171" t="inlineStr">
@@ -18659,6 +18741,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G11" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="171" t="inlineStr">
@@ -18691,6 +18778,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G12" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="171" t="inlineStr">
@@ -18723,6 +18815,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G13" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="171" t="inlineStr">
@@ -18755,6 +18852,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G14" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="171" t="inlineStr">
@@ -18787,6 +18889,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G15" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="171" t="inlineStr">
@@ -18819,6 +18926,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G16" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="171" t="inlineStr">
@@ -18851,6 +18963,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G17" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="171" t="inlineStr">
@@ -18883,6 +19000,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G18" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="171" t="inlineStr">
@@ -18915,6 +19037,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G19" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="171" t="inlineStr">
@@ -18947,6 +19074,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G20" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="171" t="inlineStr">
@@ -18979,6 +19111,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G21" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="171" t="inlineStr">
@@ -19011,6 +19148,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G22" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="171" t="inlineStr">
@@ -19043,6 +19185,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G23" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="171" t="inlineStr">
@@ -19075,6 +19222,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G24" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="171" t="inlineStr">
@@ -19107,6 +19259,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G25" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="171" t="inlineStr">
@@ -19139,6 +19296,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G26" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="171" t="inlineStr">
@@ -19171,6 +19333,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G27" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="171" t="inlineStr">
@@ -19203,6 +19370,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G28" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="171" t="inlineStr">
@@ -19235,6 +19407,11 @@
           <t>Confirmed automated (pass 1)</t>
         </is>
       </c>
+      <c r="G29" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="171" t="inlineStr">
@@ -19267,6 +19444,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G30" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="171" t="inlineStr">
@@ -19299,6 +19481,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G31" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="171" t="inlineStr">
@@ -19331,6 +19518,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G32" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="171" t="inlineStr">
@@ -19363,6 +19555,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G33" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="171" t="inlineStr">
@@ -19395,6 +19592,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G34" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="171" t="inlineStr">
@@ -19427,6 +19629,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G35" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="171" t="inlineStr">
@@ -19459,6 +19666,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G36" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="171" t="inlineStr">
@@ -19491,6 +19703,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G37" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="171" t="inlineStr">
@@ -19523,6 +19740,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G38" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="171" t="inlineStr">
@@ -19555,6 +19777,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G39" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="171" t="inlineStr">
@@ -19587,6 +19814,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G40" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="171" t="inlineStr">
@@ -19619,6 +19851,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G41" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="171" t="inlineStr">
@@ -19651,6 +19888,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G42" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="171" t="inlineStr">
@@ -19683,6 +19925,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G43" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="171" t="inlineStr">
@@ -19715,6 +19962,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G44" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="171" t="inlineStr">
@@ -19747,6 +19999,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G45" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="171" t="inlineStr">
@@ -19779,6 +20036,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G46" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="171" t="inlineStr">
@@ -19811,6 +20073,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G47" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="171" t="inlineStr">
@@ -19843,6 +20110,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G48" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="171" t="inlineStr">
@@ -19875,6 +20147,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G49" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="171" t="inlineStr">
@@ -19907,6 +20184,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G50" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="171" t="inlineStr">
@@ -19939,6 +20221,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G51" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="171" t="inlineStr">
@@ -19971,6 +20258,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G52" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="171" t="inlineStr">
@@ -20003,6 +20295,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G53" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="171" t="inlineStr">
@@ -20035,6 +20332,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G54" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="171" t="inlineStr">
@@ -20067,6 +20369,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G55" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="171" t="inlineStr">
@@ -20099,6 +20406,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G56" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="171" t="inlineStr">
@@ -20131,6 +20443,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G57" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="171" t="inlineStr">
@@ -20163,6 +20480,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G58" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="171" t="inlineStr">
@@ -20195,6 +20517,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G59" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="171" t="inlineStr">
@@ -20227,6 +20554,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G60" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="171" t="inlineStr">
@@ -20259,6 +20591,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G61" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="171" t="inlineStr">
@@ -20291,6 +20628,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G62" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="171" t="inlineStr">
@@ -20323,6 +20665,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G63" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="171" t="inlineStr">
@@ -20355,6 +20702,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G64" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="171" t="inlineStr">
@@ -20387,6 +20739,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G65" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="171" t="inlineStr">
@@ -20419,6 +20776,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G66" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="171" t="inlineStr">
@@ -20451,6 +20813,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G67" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="171" t="inlineStr">
@@ -20483,6 +20850,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G68" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="171" t="inlineStr">
@@ -20515,6 +20887,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G69" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="171" t="inlineStr">
@@ -20547,6 +20924,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G70" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="171" t="inlineStr">
@@ -20579,6 +20961,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G71" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="171" t="inlineStr">
@@ -20611,6 +20998,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G72" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="171" t="inlineStr">
@@ -20643,6 +21035,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G73" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="171" t="inlineStr">
@@ -20675,6 +21072,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G74" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="171" t="inlineStr">
@@ -20707,6 +21109,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G75" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="171" t="inlineStr">
@@ -20739,6 +21146,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G76" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="171" t="inlineStr">
@@ -20771,6 +21183,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G77" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="171" t="inlineStr">
@@ -20803,6 +21220,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G78" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="171" t="inlineStr">
@@ -20835,6 +21257,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G79" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="171" t="inlineStr">
@@ -20867,6 +21294,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G80" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="171" t="inlineStr">
@@ -20899,6 +21331,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G81" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="171" t="inlineStr">
@@ -20931,6 +21368,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G82" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="171" t="inlineStr">
@@ -20963,6 +21405,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G83" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="171" t="inlineStr">
@@ -20995,6 +21442,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G84" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="171" t="inlineStr">
@@ -21027,6 +21479,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G85" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="171" t="inlineStr">
@@ -21059,6 +21516,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G86" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="171" t="inlineStr">
@@ -21091,6 +21553,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G87" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="171" t="inlineStr">
@@ -21123,6 +21590,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G88" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="171" t="inlineStr">
@@ -21155,6 +21627,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G89" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="171" t="inlineStr">
@@ -21187,6 +21664,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G90" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="171" t="inlineStr">
@@ -21219,6 +21701,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G91" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="171" t="inlineStr">
@@ -21251,6 +21738,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G92" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="171" t="inlineStr">
@@ -21283,6 +21775,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G93" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="171" t="inlineStr">
@@ -21315,6 +21812,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G94" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="171" t="inlineStr">
@@ -21347,6 +21849,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G95" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="171" t="inlineStr">
@@ -21379,6 +21886,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G96" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="171" t="inlineStr">
@@ -21411,6 +21923,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G97" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="171" t="inlineStr">
@@ -21443,6 +21960,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G98" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="171" t="inlineStr">
@@ -21475,6 +21997,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G99" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="171" t="inlineStr">
@@ -21507,6 +22034,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G100" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="171" t="inlineStr">
@@ -21539,6 +22071,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G101" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="171" t="inlineStr">
@@ -21571,6 +22108,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G102" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="171" t="inlineStr">
@@ -21603,6 +22145,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G103" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="171" t="inlineStr">
@@ -21635,6 +22182,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G104" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="171" t="inlineStr">
@@ -21667,6 +22219,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G105" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="171" t="inlineStr">
@@ -21699,6 +22256,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G106" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="171" t="inlineStr">
@@ -21731,6 +22293,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G107" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="171" t="inlineStr">
@@ -21763,6 +22330,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G108" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="171" t="inlineStr">
@@ -21795,6 +22367,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G109" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="171" t="inlineStr">
@@ -21827,6 +22404,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G110" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="171" t="inlineStr">
@@ -21859,6 +22441,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G111" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="171" t="inlineStr">
@@ -21891,6 +22478,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G112" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="171" t="inlineStr">
@@ -21923,6 +22515,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G113" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="171" t="inlineStr">
@@ -21955,6 +22552,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G114" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="171" t="inlineStr">
@@ -21987,6 +22589,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G115" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="171" t="inlineStr">
@@ -22019,6 +22626,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G116" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="171" t="inlineStr">
@@ -22051,6 +22663,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G117" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="171" t="inlineStr">
@@ -22083,6 +22700,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G118" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="171" t="inlineStr">
@@ -22115,6 +22737,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G119" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="171" t="inlineStr">
@@ -22147,6 +22774,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G120" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="171" t="inlineStr">
@@ -22179,6 +22811,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G121" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="171" t="inlineStr">
@@ -22211,6 +22848,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G122" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="171" t="inlineStr">
@@ -22243,6 +22885,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G123" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="171" t="inlineStr">
@@ -22275,6 +22922,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G124" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="171" t="inlineStr">
@@ -22307,6 +22959,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G125" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="171" t="inlineStr">
@@ -22339,6 +22996,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G126" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="171" t="inlineStr">
@@ -22371,6 +23033,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G127" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="171" t="inlineStr">
@@ -22403,6 +23070,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G128" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="171" t="inlineStr">
@@ -22435,6 +23107,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G129" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="171" t="inlineStr">
@@ -22467,6 +23144,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G130" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="171" t="inlineStr">
@@ -22499,6 +23181,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G131" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="171" t="inlineStr">
@@ -22531,6 +23218,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G132" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="171" t="inlineStr">
@@ -22563,6 +23255,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G133" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="171" t="inlineStr">
@@ -22595,6 +23292,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G134" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="171" t="inlineStr">
@@ -22627,6 +23329,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G135" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="171" t="inlineStr">
@@ -22659,6 +23366,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G136" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="171" t="inlineStr">
@@ -22691,6 +23403,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G137" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="171" t="inlineStr">
@@ -22723,6 +23440,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G138" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="171" t="inlineStr">
@@ -22755,6 +23477,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G139" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="171" t="inlineStr">
@@ -22787,6 +23514,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G140" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="171" t="inlineStr">
@@ -22819,6 +23551,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G141" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="171" t="inlineStr">
@@ -22851,6 +23588,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G142" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="171" t="inlineStr">
@@ -22883,6 +23625,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G143" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="171" t="inlineStr">
@@ -22915,6 +23662,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G144" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="171" t="inlineStr">
@@ -22947,6 +23699,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G145" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="171" t="inlineStr">
@@ -22979,6 +23736,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G146" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="171" t="inlineStr">
@@ -23011,6 +23773,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G147" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="171" t="inlineStr">
@@ -23043,6 +23810,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G148" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="171" t="inlineStr">
@@ -23075,6 +23847,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G149" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="171" t="inlineStr">
@@ -23107,6 +23884,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G150" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="171" t="inlineStr">
@@ -23139,6 +23921,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G151" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="171" t="inlineStr">
@@ -23171,6 +23958,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G152" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="171" t="inlineStr">
@@ -23203,6 +23995,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G153" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="171" t="inlineStr">
@@ -23235,6 +24032,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G154" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="171" t="inlineStr">
@@ -23267,6 +24069,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G155" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="171" t="inlineStr">
@@ -23299,6 +24106,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G156" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="171" t="inlineStr">
@@ -23331,6 +24143,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G157" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="171" t="inlineStr">
@@ -23363,6 +24180,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G158" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="171" t="inlineStr">
@@ -23395,6 +24217,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G159" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="171" t="inlineStr">
@@ -23427,6 +24254,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G160" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="171" t="inlineStr">
@@ -23459,6 +24291,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G161" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="171" t="inlineStr">
@@ -23491,6 +24328,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G162" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="171" t="inlineStr">
@@ -23523,6 +24365,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G163" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="171" t="inlineStr">
@@ -23555,6 +24402,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G164" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="171" t="inlineStr">
@@ -23587,6 +24439,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G165" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="171" t="inlineStr">
@@ -23619,6 +24476,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G166" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="171" t="inlineStr">
@@ -23651,6 +24513,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G167" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="171" t="inlineStr">
@@ -23683,6 +24550,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G168" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="171" t="inlineStr">
@@ -23715,6 +24587,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G169" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="171" t="inlineStr">
@@ -23747,6 +24624,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G170" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="171" t="inlineStr">
@@ -23779,6 +24661,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G171" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="171" t="inlineStr">
@@ -23811,6 +24698,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G172" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="171" t="inlineStr">
@@ -23843,6 +24735,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G173" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="171" t="inlineStr">
@@ -23875,6 +24772,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G174" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="171" t="inlineStr">
@@ -23907,6 +24809,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G175" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="171" t="inlineStr">
@@ -23939,6 +24846,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G176" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="171" t="inlineStr">
@@ -23971,6 +24883,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G177" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="171" t="inlineStr">
@@ -24003,6 +24920,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G178" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="171" t="inlineStr">
@@ -24035,6 +24957,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G179" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="171" t="inlineStr">
@@ -24067,6 +24994,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G180" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="171" t="inlineStr">
@@ -24099,6 +25031,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G181" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="171" t="inlineStr">
@@ -24131,6 +25068,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G182" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="171" t="inlineStr">
@@ -24163,6 +25105,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G183" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="171" t="inlineStr">
@@ -24195,6 +25142,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G184" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="171" t="inlineStr">
@@ -24227,6 +25179,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G185" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="171" t="inlineStr">
@@ -24259,6 +25216,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G186" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="171" t="inlineStr">
@@ -24291,6 +25253,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G187" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="171" t="inlineStr">
@@ -24323,6 +25290,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G188" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="171" t="inlineStr">
@@ -24355,6 +25327,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G189" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="171" t="inlineStr">
@@ -24387,6 +25364,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G190" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="171" t="inlineStr">
@@ -24419,6 +25401,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G191" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="171" t="inlineStr">
@@ -24451,6 +25438,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G192" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="171" t="inlineStr">
@@ -24483,6 +25475,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G193" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="171" t="inlineStr">
@@ -24515,6 +25512,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G194" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="171" t="inlineStr">
@@ -24547,6 +25549,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G195" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="171" t="inlineStr">
@@ -24579,6 +25586,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G196" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="171" t="inlineStr">
@@ -24611,6 +25623,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G197" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="171" t="inlineStr">
@@ -24643,6 +25660,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G198" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="171" t="inlineStr">
@@ -24675,6 +25697,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G199" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="171" t="inlineStr">
@@ -24707,6 +25734,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G200" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="171" t="inlineStr">
@@ -24739,6 +25771,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G201" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="171" t="inlineStr">
@@ -24771,6 +25808,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G202" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="171" t="inlineStr">
@@ -24803,6 +25845,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G203" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="171" t="inlineStr">
@@ -24835,6 +25882,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G204" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="171" t="inlineStr">
@@ -24867,6 +25919,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G205" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="171" t="inlineStr">
@@ -24899,6 +25956,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G206" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="171" t="inlineStr">
@@ -24931,6 +25993,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G207" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="171" t="inlineStr">
@@ -24963,6 +26030,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G208" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="171" t="inlineStr">
@@ -24995,6 +26067,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G209" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="171" t="inlineStr">
@@ -25027,6 +26104,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G210" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="171" t="inlineStr">
@@ -25059,6 +26141,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G211" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="171" t="inlineStr">
@@ -25091,6 +26178,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G212" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="171" t="inlineStr">
@@ -25123,6 +26215,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G213" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="171" t="inlineStr">
@@ -25155,6 +26252,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G214" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="171" t="inlineStr">
@@ -25187,6 +26289,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G215" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="171" t="inlineStr">
@@ -25219,6 +26326,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G216" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="171" t="inlineStr">
@@ -25251,6 +26363,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G217" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="171" t="inlineStr">
@@ -25283,6 +26400,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G218" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="171" t="inlineStr">
@@ -25315,6 +26437,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G219" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="171" t="inlineStr">
@@ -25347,6 +26474,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G220" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="171" t="inlineStr">
@@ -25379,6 +26511,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G221" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="171" t="inlineStr">
@@ -25411,6 +26548,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G222" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="171" t="inlineStr">
@@ -25443,6 +26585,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G223" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="171" t="inlineStr">
@@ -25475,6 +26622,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G224" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="171" t="inlineStr">
@@ -25507,6 +26659,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G225" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="171" t="inlineStr">
@@ -25539,6 +26696,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G226" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="171" t="inlineStr">
@@ -25571,6 +26733,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G227" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="171" t="inlineStr">
@@ -25603,6 +26770,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G228" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="171" t="inlineStr">
@@ -25635,6 +26807,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G229" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="171" t="inlineStr">
@@ -25667,6 +26844,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G230" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="171" t="inlineStr">
@@ -25699,6 +26881,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G231" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="171" t="inlineStr">
@@ -25731,6 +26918,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G232" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="171" t="inlineStr">
@@ -25763,6 +26955,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G233" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="171" t="inlineStr">
@@ -25795,6 +26992,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G234" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="171" t="inlineStr">
@@ -25827,6 +27029,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G235" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="171" t="inlineStr">
@@ -25859,6 +27066,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G236" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="171" t="inlineStr">
@@ -25891,6 +27103,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G237" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="171" t="inlineStr">
@@ -25923,6 +27140,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G238" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="171" t="inlineStr">
@@ -25955,6 +27177,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G239" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="171" t="inlineStr">
@@ -25987,6 +27214,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G240" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="171" t="inlineStr">
@@ -26019,6 +27251,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G241" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="171" t="inlineStr">
@@ -26051,6 +27288,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G242" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="171" t="inlineStr">
@@ -26083,6 +27325,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G243" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="171" t="inlineStr">
@@ -26115,6 +27362,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G244" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="171" t="inlineStr">
@@ -26147,6 +27399,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G245" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="171" t="inlineStr">
@@ -26179,6 +27436,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G246" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="171" t="inlineStr">
@@ -26211,6 +27473,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G247" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="171" t="inlineStr">
@@ -26243,6 +27510,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G248" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="171" t="inlineStr">
@@ -26275,6 +27547,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G249" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="171" t="inlineStr">
@@ -26307,6 +27584,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G250" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="171" t="inlineStr">
@@ -26339,6 +27621,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G251" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="171" t="inlineStr">
@@ -26371,6 +27658,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G252" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="171" t="inlineStr">
@@ -26403,6 +27695,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G253" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="171" t="inlineStr">
@@ -26435,6 +27732,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G254" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="171" t="inlineStr">
@@ -26467,6 +27769,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G255" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="171" t="inlineStr">
@@ -26499,6 +27806,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G256" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="171" t="inlineStr">
@@ -26531,6 +27843,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G257" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="171" t="inlineStr">
@@ -26563,6 +27880,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G258" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="171" t="inlineStr">
@@ -26595,6 +27917,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G259" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="171" t="inlineStr">
@@ -26627,6 +27954,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G260" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="171" t="inlineStr">
@@ -26659,6 +27991,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G261" s="171" t="inlineStr">
+        <is>
+          <t>Partial - likely eng-covered (confirm w/ eng)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="171" t="inlineStr">
@@ -26691,6 +28028,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G262" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="171" t="inlineStr">
@@ -26723,6 +28065,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G263" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="171" t="inlineStr">
@@ -26755,6 +28102,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G264" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="171" t="inlineStr">
@@ -26787,6 +28139,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G265" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="171" t="inlineStr">
@@ -26819,6 +28176,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G266" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="171" t="inlineStr">
@@ -26851,6 +28213,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G267" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="171" t="inlineStr">
@@ -26883,6 +28250,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G268" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="171" t="inlineStr">
@@ -26915,6 +28287,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G269" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="171" t="inlineStr">
@@ -26947,6 +28324,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G270" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="171" t="inlineStr">
@@ -26979,6 +28361,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G271" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="171" t="inlineStr">
@@ -27011,6 +28398,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G272" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="171" t="inlineStr">
@@ -27043,6 +28435,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G273" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="171" t="inlineStr">
@@ -27075,6 +28472,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G274" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="171" t="inlineStr">
@@ -27107,6 +28509,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G275" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="171" t="inlineStr">
@@ -27139,6 +28546,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G276" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="171" t="inlineStr">
@@ -27171,6 +28583,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G277" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="171" t="inlineStr">
@@ -27203,6 +28620,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G278" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="171" t="inlineStr">
@@ -27235,6 +28657,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G279" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="171" t="inlineStr">
@@ -27267,6 +28694,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G280" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="171" t="inlineStr">
@@ -27299,6 +28731,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G281" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="171" t="inlineStr">
@@ -27331,6 +28768,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G282" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="171" t="inlineStr">
@@ -27363,6 +28805,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G283" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="171" t="inlineStr">
@@ -27395,6 +28842,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G284" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="171" t="inlineStr">
@@ -27427,6 +28879,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G285" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="171" t="inlineStr">
@@ -27459,6 +28916,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G286" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="171" t="inlineStr">
@@ -27491,6 +28953,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G287" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="171" t="inlineStr">
@@ -27523,6 +28990,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G288" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="171" t="inlineStr">
@@ -27555,6 +29027,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G289" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="171" t="inlineStr">
@@ -27587,6 +29064,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G290" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="171" t="inlineStr">
@@ -27619,6 +29101,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G291" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="171" t="inlineStr">
@@ -27651,6 +29138,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G292" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="171" t="inlineStr">
@@ -27683,6 +29175,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G293" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="171" t="inlineStr">
@@ -27715,6 +29212,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G294" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="171" t="inlineStr">
@@ -27747,6 +29249,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G295" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="171" t="inlineStr">
@@ -27779,6 +29286,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G296" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="171" t="inlineStr">
@@ -27811,6 +29323,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G297" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="171" t="inlineStr">
@@ -27843,6 +29360,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G298" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="171" t="inlineStr">
@@ -27875,6 +29397,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G299" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="171" t="inlineStr">
@@ -27907,6 +29434,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G300" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="171" t="inlineStr">
@@ -27939,6 +29471,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G301" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="171" t="inlineStr">
@@ -27971,6 +29508,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G302" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="171" t="inlineStr">
@@ -28003,6 +29545,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G303" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="171" t="inlineStr">
@@ -28035,6 +29582,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G304" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (manual)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="171" t="inlineStr">
@@ -28067,6 +29619,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G305" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="171" t="inlineStr">
@@ -28099,6 +29656,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G306" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="171" t="inlineStr">
@@ -28131,6 +29693,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G307" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="171" t="inlineStr">
@@ -28163,6 +29730,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G308" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="171" t="inlineStr">
@@ -28195,6 +29767,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G309" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="171" t="inlineStr">
@@ -28227,6 +29804,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G310" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="171" t="inlineStr">
@@ -28259,6 +29841,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G311" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="171" t="inlineStr">
@@ -28291,6 +29878,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G312" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="171" t="inlineStr">
@@ -28323,6 +29915,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G313" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="171" t="inlineStr">
@@ -28355,6 +29952,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G314" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="171" t="inlineStr">
@@ -28387,6 +29989,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G315" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="171" t="inlineStr">
@@ -28419,6 +30026,11 @@
           <t>Pass 1: MTP vs test suite</t>
         </is>
       </c>
+      <c r="G316" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="171" t="inlineStr">
@@ -28449,6 +30061,11 @@
       <c r="F317" s="171" t="inlineStr">
         <is>
           <t>Pass 1: MTP vs test suite</t>
+        </is>
+      </c>
+      <c r="G317" s="171" t="inlineStr">
+        <is>
+          <t>QA-owned (UI/e2e - eng cannot cover)</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -187,7 +187,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -309,6 +309,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -444,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -939,6 +944,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14833,22 +14844,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" style="148" min="1" max="1"/>
+    <col width="66" customWidth="1" style="148" min="1" max="1"/>
     <col width="20" customWidth="1" style="148" min="2" max="2"/>
     <col width="20" customWidth="1" style="148" min="3" max="3"/>
     <col width="20" customWidth="1" style="148" min="4" max="4"/>
     <col width="20" customWidth="1" style="148" min="5" max="5"/>
     <col width="20" customWidth="1" style="148" min="6" max="6"/>
-    <col width="28" customWidth="1" style="148" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="172" t="inlineStr">
         <is>
-          <t>Dashboard — outputs &amp; coverage (live)</t>
+          <t>Dashboard — conclusions, outputs &amp; coverage (live)</t>
         </is>
       </c>
       <c r="B1" s="171" t="n"/>
@@ -14856,401 +14866,265 @@
       <c r="D1" s="171" t="n"/>
       <c r="E1" s="171" t="n"/>
       <c r="F1" s="171" t="n"/>
-      <c r="G1" s="171" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="171" t="n"/>
+      <c r="A2" s="171" t="inlineStr"/>
       <c r="B2" s="171" t="n"/>
       <c r="C2" s="171" t="n"/>
       <c r="D2" s="171" t="n"/>
       <c r="E2" s="171" t="n"/>
       <c r="F2" s="171" t="n"/>
-      <c r="G2" s="171" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="182" t="inlineStr">
-        <is>
-          <t>OUTPUTS (from Gap Analysis)</t>
-        </is>
-      </c>
-      <c r="B3" s="171" t="inlineStr"/>
+      <c r="A3" s="187" t="inlineStr">
+        <is>
+          <t>CONCLUSIONS / ANALYSIS NOTES</t>
+        </is>
+      </c>
+      <c r="B3" s="171" t="n"/>
       <c r="C3" s="171" t="n"/>
       <c r="D3" s="171" t="n"/>
       <c r="E3" s="171" t="n"/>
       <c r="F3" s="171" t="n"/>
-      <c r="G3" s="171" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="171" t="inlineStr">
         <is>
-          <t>Output 1: functional gaps to ADD to MTP</t>
-        </is>
-      </c>
-      <c r="B4" s="171">
-        <f>COUNTIF('Gap Analysis'!$L:$L,"Add to MTP*")</f>
-        <v/>
-      </c>
+          <t>• Method: audited the master test plans against the actual product code to find behaviour with no test case (functional gaps), then cross-referenced each against engineering PR-run tests so QA does not duplicate eng work.</t>
+        </is>
+      </c>
+      <c r="B4" s="171" t="n"/>
       <c r="C4" s="171" t="n"/>
       <c r="D4" s="171" t="n"/>
       <c r="E4" s="171" t="n"/>
       <c r="F4" s="171" t="n"/>
-      <c r="G4" s="171" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="171" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...of which eng-covered (add to MTP only, do NOT automate)</t>
-        </is>
-      </c>
-      <c r="B5" s="171">
-        <f>COUNTIF('Gap Analysis'!$L:$L,"Add to MTP only*")</f>
-        <v/>
-      </c>
+          <t>• Two outputs: (1) MTP completeness = ALL functional gaps get added to the plan; (2) QA automation backlog = only the gaps eng does NOT already cover.</t>
+        </is>
+      </c>
+      <c r="B5" s="171" t="n"/>
       <c r="C5" s="171" t="n"/>
       <c r="D5" s="171" t="n"/>
       <c r="E5" s="171" t="n"/>
       <c r="F5" s="171" t="n"/>
-      <c r="G5" s="171" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="171" t="inlineStr">
         <is>
-          <t>Output 2: functional gaps to AUTOMATE (QA backlog)</t>
-        </is>
-      </c>
-      <c r="B6" s="171">
-        <f>COUNTIF('Gap Analysis'!$L:$L,"*Automate*")</f>
-        <v/>
-      </c>
+          <t>• New gaps are mostly eng-covered: the majority of functional gaps found in code are already tested by eng at the logic layer -&gt; add to MTP for completeness, but do NOT re-automate. QA new-automation shortlist is small (real device/SMS/push/cross-system).</t>
+        </is>
+      </c>
+      <c r="B6" s="171" t="n"/>
       <c r="C6" s="171" t="n"/>
       <c r="D6" s="171" t="n"/>
       <c r="E6" s="171" t="n"/>
       <c r="F6" s="171" t="n"/>
-      <c r="G6" s="171" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="171" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...of which QA-owned (eng cannot cover)</t>
-        </is>
-      </c>
-      <c r="B7" s="171">
-        <f>COUNTIF('Gap Analysis'!$L:$L,"*QA-owned*")</f>
-        <v/>
-      </c>
+          <t>• Existing MTP backlog is the opposite: automatable-not-built existing cases are overwhelmingly UI / end-to-end journeys that eng unit tests do NOT cover -&gt; this backlog genuinely needs QA automation (not duplicative of eng).</t>
+        </is>
+      </c>
+      <c r="B7" s="171" t="n"/>
       <c r="C7" s="171" t="n"/>
       <c r="D7" s="171" t="n"/>
       <c r="E7" s="171" t="n"/>
       <c r="F7" s="171" t="n"/>
-      <c r="G7" s="171" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="171" t="inlineStr">
         <is>
-          <t>Dev: unit-test-coverage gaps</t>
-        </is>
-      </c>
-      <c r="B8" s="171">
-        <f>COUNTIF('Gap Analysis'!$L:$L,"Dev:*")</f>
-        <v/>
-      </c>
+          <t>• Net: eng-overlap savings land almost entirely on the NEW gaps, not the existing backlog. Manual-only (red) items stay manual regardless of framework.</t>
+        </is>
+      </c>
+      <c r="B8" s="171" t="n"/>
       <c r="C8" s="171" t="n"/>
       <c r="D8" s="171" t="n"/>
       <c r="E8" s="171" t="n"/>
       <c r="F8" s="171" t="n"/>
-      <c r="G8" s="171" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="171" t="inlineStr">
         <is>
-          <t>Cross-cutting: reconcile plan/code</t>
-        </is>
-      </c>
-      <c r="B9" s="171">
-        <f>COUNTIF('Gap Analysis'!$L:$L,"Reconcile*")</f>
-        <v/>
-      </c>
+          <t>• All eng-coverage tags are best-guess from reading eng test structure, not verified line coverage - confirm the Partial items with the dev teams.</t>
+        </is>
+      </c>
+      <c r="B9" s="171" t="n"/>
       <c r="C9" s="171" t="n"/>
       <c r="D9" s="171" t="n"/>
       <c r="E9" s="171" t="n"/>
       <c r="F9" s="171" t="n"/>
-      <c r="G9" s="171" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="171" t="inlineStr">
-        <is>
-          <t>Total Gap Analysis rows</t>
-        </is>
-      </c>
-      <c r="B10" s="171">
-        <f>COUNTA('Gap Analysis'!$A$2:$A$1000)</f>
-        <v/>
-      </c>
+      <c r="A10" s="171" t="inlineStr"/>
+      <c r="B10" s="171" t="n"/>
       <c r="C10" s="171" t="n"/>
       <c r="D10" s="171" t="n"/>
       <c r="E10" s="171" t="n"/>
       <c r="F10" s="171" t="n"/>
-      <c r="G10" s="171" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="171" t="n"/>
+      <c r="A11" s="182" t="inlineStr">
+        <is>
+          <t>OUTPUTS (from Gap Analysis)</t>
+        </is>
+      </c>
       <c r="B11" s="171" t="n"/>
       <c r="C11" s="171" t="n"/>
       <c r="D11" s="171" t="n"/>
       <c r="E11" s="171" t="n"/>
       <c r="F11" s="171" t="n"/>
-      <c r="G11" s="171" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="171" t="inlineStr">
         <is>
-          <t>COVERAGE TRACKER — automation of existing MTP cases</t>
-        </is>
-      </c>
-      <c r="B12" s="171" t="inlineStr"/>
+          <t>Output 1: functional gaps to ADD to MTP</t>
+        </is>
+      </c>
+      <c r="B12" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Add to MTP*")</f>
+        <v/>
+      </c>
       <c r="C12" s="171" t="n"/>
       <c r="D12" s="171" t="n"/>
       <c r="E12" s="171" t="n"/>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="171" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="173" t="inlineStr">
-        <is>
-          <t>Surface</t>
-        </is>
-      </c>
-      <c r="B13" s="173" t="inlineStr">
-        <is>
-          <t>Automated (built)</t>
-        </is>
-      </c>
-      <c r="C13" s="173" t="inlineStr">
-        <is>
-          <t>Automatable (not built)</t>
-        </is>
-      </c>
-      <c r="D13" s="173" t="inlineStr">
-        <is>
-          <t>Manual only</t>
-        </is>
-      </c>
-      <c r="E13" s="173" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F13" s="173" t="inlineStr">
-        <is>
-          <t>% Automated</t>
-        </is>
-      </c>
-      <c r="G13" s="173" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+      <c r="A13" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...of which eng-covered (add to MTP only, do NOT automate)</t>
+        </is>
+      </c>
+      <c r="B13" s="171">
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Add to MTP only*")</f>
+        <v/>
+      </c>
+      <c r="C13" s="171" t="n"/>
+      <c r="D13" s="171" t="n"/>
+      <c r="E13" s="171" t="n"/>
+      <c r="F13" s="171" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="171" t="inlineStr">
         <is>
-          <t>Login page</t>
+          <t>Output 2: functional gaps to AUTOMATE (QA backlog)</t>
         </is>
       </c>
       <c r="B14" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A14,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <f>COUNTIF('Gap Analysis'!$L:$L,"*Automate*")</f>
         <v/>
       </c>
-      <c r="C14" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A14,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D14" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A14,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E14" s="171">
-        <f>B14+C14+D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="179">
-        <f>IF(E14&gt;0,B14/E14,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="171" t="inlineStr"/>
+      <c r="C14" s="171" t="n"/>
+      <c r="D14" s="171" t="n"/>
+      <c r="E14" s="171" t="n"/>
+      <c r="F14" s="171" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="171" t="inlineStr">
         <is>
-          <t>Programs List page</t>
+          <t xml:space="preserve">   ...of which QA-owned (eng cannot cover)</t>
         </is>
       </c>
       <c r="B15" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A15,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <f>COUNTIF('Gap Analysis'!$L:$L,"*QA-owned*")</f>
         <v/>
       </c>
-      <c r="C15" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A15,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D15" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A15,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E15" s="171">
-        <f>B15+C15+D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="179">
-        <f>IF(E15&gt;0,B15/E15,0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="171" t="inlineStr"/>
+      <c r="C15" s="171" t="n"/>
+      <c r="D15" s="171" t="n"/>
+      <c r="E15" s="171" t="n"/>
+      <c r="F15" s="171" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="171" t="inlineStr">
         <is>
-          <t>Opportunity creation</t>
+          <t>Dev: unit-test-coverage gaps</t>
         </is>
       </c>
       <c r="B16" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A16,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Dev:*")</f>
         <v/>
       </c>
-      <c r="C16" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A16,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D16" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A16,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E16" s="171">
-        <f>B16+C16+D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="179">
-        <f>IF(E16&gt;0,B16/E16,0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="171" t="inlineStr"/>
+      <c r="C16" s="171" t="n"/>
+      <c r="D16" s="171" t="n"/>
+      <c r="E16" s="171" t="n"/>
+      <c r="F16" s="171" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="171" t="inlineStr">
         <is>
-          <t>Opportunity List page</t>
+          <t>Cross-cutting: reconcile plan/code</t>
         </is>
       </c>
       <c r="B17" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A17,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <f>COUNTIF('Gap Analysis'!$L:$L,"Reconcile*")</f>
         <v/>
       </c>
-      <c r="C17" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A17,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D17" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A17,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E17" s="171">
-        <f>B17+C17+D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="179">
-        <f>IF(E17&gt;0,B17/E17,0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="171" t="inlineStr"/>
+      <c r="C17" s="171" t="n"/>
+      <c r="D17" s="171" t="n"/>
+      <c r="E17" s="171" t="n"/>
+      <c r="F17" s="171" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="171" t="inlineStr">
-        <is>
-          <t>Opportunity dashboard</t>
-        </is>
-      </c>
-      <c r="B18" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A18,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
-        <v/>
-      </c>
-      <c r="C18" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A18,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D18" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A18,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E18" s="171">
-        <f>B18+C18+D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="179">
-        <f>IF(E18&gt;0,B18/E18,0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="171" t="inlineStr"/>
+      <c r="A18" s="171" t="inlineStr"/>
+      <c r="B18" s="171" t="n"/>
+      <c r="C18" s="171" t="n"/>
+      <c r="D18" s="171" t="n"/>
+      <c r="E18" s="171" t="n"/>
+      <c r="F18" s="171" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="171" t="inlineStr">
-        <is>
-          <t>Connect workers page</t>
-        </is>
-      </c>
-      <c r="B19" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A19,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
-        <v/>
-      </c>
-      <c r="C19" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A19,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D19" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A19,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E19" s="171">
-        <f>B19+C19+D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="179">
-        <f>IF(E19&gt;0,B19/E19,0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="171" t="inlineStr"/>
+      <c r="A19" s="182" t="inlineStr">
+        <is>
+          <t>COVERAGE TRACKER — automation of existing MTP cases</t>
+        </is>
+      </c>
+      <c r="B19" s="171" t="n"/>
+      <c r="C19" s="171" t="n"/>
+      <c r="D19" s="171" t="n"/>
+      <c r="E19" s="171" t="n"/>
+      <c r="F19" s="171" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="171" t="inlineStr">
-        <is>
-          <t>Visit verification page</t>
-        </is>
-      </c>
-      <c r="B20" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A20,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
-        <v/>
-      </c>
-      <c r="C20" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A20,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
-        <v/>
-      </c>
-      <c r="D20" s="171">
-        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A20,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
-        <v/>
-      </c>
-      <c r="E20" s="171">
-        <f>B20+C20+D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="179">
-        <f>IF(E20&gt;0,B20/E20,0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="171" t="inlineStr"/>
+      <c r="A20" s="173" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="B20" s="173" t="inlineStr">
+        <is>
+          <t>Automated (built)</t>
+        </is>
+      </c>
+      <c r="C20" s="173" t="inlineStr">
+        <is>
+          <t>Automatable (not built)</t>
+        </is>
+      </c>
+      <c r="D20" s="173" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="E20" s="173" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F20" s="173" t="inlineStr">
+        <is>
+          <t>% Automated</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="171" t="inlineStr">
         <is>
-          <t>Invoices List page</t>
+          <t>Login page</t>
         </is>
       </c>
       <c r="B21" s="171">
@@ -15273,12 +15147,11 @@
         <f>IF(E21&gt;0,B21/E21,0)</f>
         <v/>
       </c>
-      <c r="G21" s="171" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="171" t="inlineStr">
         <is>
-          <t>Connect Messaging</t>
+          <t>Programs List page</t>
         </is>
       </c>
       <c r="B22" s="171">
@@ -15301,12 +15174,11 @@
         <f>IF(E22&gt;0,B22/E22,0)</f>
         <v/>
       </c>
-      <c r="G22" s="171" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="171" t="inlineStr">
         <is>
-          <t>Delivery Reminder Mails</t>
+          <t>Opportunity creation</t>
         </is>
       </c>
       <c r="B23" s="171">
@@ -15329,12 +15201,11 @@
         <f>IF(E23&gt;0,B23/E23,0)</f>
         <v/>
       </c>
-      <c r="G23" s="171" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="171" t="inlineStr">
         <is>
-          <t>App Credentials</t>
+          <t>Opportunity List page</t>
         </is>
       </c>
       <c r="B24" s="171">
@@ -15357,12 +15228,11 @@
         <f>IF(E24&gt;0,B24/E24,0)</f>
         <v/>
       </c>
-      <c r="G24" s="171" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="171" t="inlineStr">
         <is>
-          <t>Re-Learn Task</t>
+          <t>Opportunity dashboard</t>
         </is>
       </c>
       <c r="B25" s="171">
@@ -15385,12 +15255,11 @@
         <f>IF(E25&gt;0,B25/E25,0)</f>
         <v/>
       </c>
-      <c r="G25" s="171" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="171" t="inlineStr">
         <is>
-          <t>Microplanning</t>
+          <t>Connect workers page</t>
         </is>
       </c>
       <c r="B26" s="171">
@@ -15413,65 +15282,272 @@
         <f>IF(E26&gt;0,B26/E26,0)</f>
         <v/>
       </c>
-      <c r="G26" s="171" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="180" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B27" s="180">
-        <f>SUM(B14:B26)</f>
+      <c r="A27" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="B27" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A27,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
         <v/>
       </c>
-      <c r="C27" s="180">
-        <f>SUM(C14:C26)</f>
+      <c r="C27" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A27,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
         <v/>
       </c>
-      <c r="D27" s="180">
-        <f>SUM(D14:D26)</f>
+      <c r="D27" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A27,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
         <v/>
       </c>
-      <c r="E27" s="180">
-        <f>SUM(E14:E26)</f>
+      <c r="E27" s="171">
+        <f>B27+C27+D27</f>
         <v/>
       </c>
-      <c r="F27" s="181">
+      <c r="F27" s="179">
         <f>IF(E27&gt;0,B27/E27,0)</f>
         <v/>
       </c>
-      <c r="G27" s="180" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="171" t="inlineStr">
+        <is>
+          <t>Invoices List page</t>
+        </is>
+      </c>
+      <c r="B28" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A28,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <v/>
+      </c>
+      <c r="C28" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A28,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D28" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A28,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E28" s="171">
+        <f>B28+C28+D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="179">
+        <f>IF(E28&gt;0,B28/E28,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="185" t="inlineStr">
-        <is>
-          <t>EXISTING automatable-not-built cases — do they need automating?</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" s="171" t="inlineStr">
+        <is>
+          <t>Connect Messaging</t>
+        </is>
+      </c>
+      <c r="B29" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A29,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <v/>
+      </c>
+      <c r="C29" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A29,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D29" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A29,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E29" s="171">
+        <f>B29+C29+D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="179">
+        <f>IF(E29&gt;0,B29/E29,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="171" t="inlineStr">
         <is>
+          <t>Delivery Reminder Mails</t>
+        </is>
+      </c>
+      <c r="B30" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A30,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <v/>
+      </c>
+      <c r="C30" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A30,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D30" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A30,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E30" s="171">
+        <f>B30+C30+D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="179">
+        <f>IF(E30&gt;0,B30/E30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="171" t="inlineStr">
+        <is>
+          <t>App Credentials</t>
+        </is>
+      </c>
+      <c r="B31" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A31,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <v/>
+      </c>
+      <c r="C31" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A31,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D31" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A31,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E31" s="171">
+        <f>B31+C31+D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="179">
+        <f>IF(E31&gt;0,B31/E31,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="171" t="inlineStr">
+        <is>
+          <t>Re-Learn Task</t>
+        </is>
+      </c>
+      <c r="B32" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A32,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <v/>
+      </c>
+      <c r="C32" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A32,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D32" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A32,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E32" s="171">
+        <f>B32+C32+D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="179">
+        <f>IF(E32&gt;0,B32/E32,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="171" t="inlineStr">
+        <is>
+          <t>Microplanning</t>
+        </is>
+      </c>
+      <c r="B33" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A33,'Automation (existing MTP)'!$D:$D,"🟢*")</f>
+        <v/>
+      </c>
+      <c r="C33" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A33,'Automation (existing MTP)'!$D:$D,"🟡*")</f>
+        <v/>
+      </c>
+      <c r="D33" s="171">
+        <f>COUNTIFS('Automation (existing MTP)'!$B:$B,$A33,'Automation (existing MTP)'!$D:$D,"🔴*")</f>
+        <v/>
+      </c>
+      <c r="E33" s="171">
+        <f>B33+C33+D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="179">
+        <f>IF(E33&gt;0,B33/E33,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="180" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B34" s="180">
+        <f>SUM(B21:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="180">
+        <f>SUM(C21:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="180">
+        <f>SUM(D21:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="180">
+        <f>SUM(E21:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="181">
+        <f>IF(E34&gt;0,B34/E34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="171" t="inlineStr"/>
+      <c r="B35" s="171" t="n"/>
+      <c r="C35" s="171" t="n"/>
+      <c r="D35" s="171" t="n"/>
+      <c r="E35" s="171" t="n"/>
+      <c r="F35" s="171" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="182" t="inlineStr">
+        <is>
+          <t>EXISTING automatable-not-built cases — do they need automating?</t>
+        </is>
+      </c>
+      <c r="B36" s="171" t="n"/>
+      <c r="C36" s="171" t="n"/>
+      <c r="D36" s="171" t="n"/>
+      <c r="E36" s="171" t="n"/>
+      <c r="F36" s="171" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="171" t="inlineStr">
+        <is>
           <t>QA-owned (UI/e2e - need automating)</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B37" s="171">
         <f>COUNTIF('Automation (existing MTP)'!$G:$G,"QA-owned (UI*")</f>
         <v/>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="171" t="inlineStr">
+      <c r="C37" s="171" t="n"/>
+      <c r="D37" s="171" t="n"/>
+      <c r="E37" s="171" t="n"/>
+      <c r="F37" s="171" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="171" t="inlineStr">
         <is>
           <t>Likely already eng-covered (confirm - may NOT need automating)</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B38" s="171">
         <f>COUNTIF('Automation (existing MTP)'!$G:$G,"Partial*")</f>
         <v/>
       </c>
+      <c r="C38" s="171" t="n"/>
+      <c r="D38" s="171" t="n"/>
+      <c r="E38" s="171" t="n"/>
+      <c r="F38" s="171" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -31609,9 +31609,17 @@
 - Created program is shown on the programs list page</t>
         </is>
       </c>
-      <c r="E2" s="66" t="n"/>
+      <c r="E2" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F2" s="67" t="n"/>
-      <c r="G2" s="67" t="n"/>
+      <c r="G2" s="67" t="inlineStr">
+        <is>
+          <t>Automated (setup flow: create_program)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="67" t="inlineStr">
@@ -31635,9 +31643,17 @@
           <t xml:space="preserve">User should be able to invite the NMs to the programs </t>
         </is>
       </c>
-      <c r="E3" s="66" t="n"/>
+      <c r="E3" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F3" s="67" t="n"/>
-      <c r="G3" s="67" t="n"/>
+      <c r="G3" s="67" t="inlineStr">
+        <is>
+          <t>Automated (setup flow: invite_network_manager)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="67" t="inlineStr">
@@ -31668,9 +31684,17 @@
 </t>
         </is>
       </c>
-      <c r="E4" s="66" t="n"/>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F4" s="67" t="n"/>
-      <c r="G4" s="67" t="n"/>
+      <c r="G4" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (card summary fields)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="67" t="inlineStr">
@@ -31694,9 +31718,17 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="66" t="n"/>
+      <c r="E5" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F5" s="67" t="n"/>
-      <c r="G5" s="67" t="n"/>
+      <c r="G5" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (View Status expand)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="67" t="inlineStr">
@@ -31724,9 +31756,17 @@
 - Number Accepted</t>
         </is>
       </c>
-      <c r="E6" s="66" t="n"/>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F6" s="67" t="n"/>
-      <c r="G6" s="67" t="n"/>
+      <c r="G6" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (acceptance_funnel)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="67" t="inlineStr">
@@ -31754,9 +31794,17 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="66" t="n"/>
+      <c r="E7" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F7" s="67" t="n"/>
-      <c r="G7" s="67" t="n"/>
+      <c r="G7" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (nm_application_statuses)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="67" t="inlineStr">
@@ -31785,9 +31833,17 @@
 - View Opportunity </t>
         </is>
       </c>
-      <c r="E8" s="66" t="n"/>
+      <c r="E8" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F8" s="67" t="n"/>
-      <c r="G8" s="67" t="n"/>
+      <c r="G8" s="67" t="inlineStr">
+        <is>
+          <t>Automated (setup flow: Create/View Opportunity when accepted)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="67" t="inlineStr">
@@ -31810,7 +31866,11 @@
       </c>
       <c r="E9" s="66" t="n"/>
       <c r="F9" s="67" t="n"/>
-      <c r="G9" s="67" t="n"/>
+      <c r="G9" s="67" t="inlineStr">
+        <is>
+          <t>Not on list page; = Recent Activities destinations (link targets asserted)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="67" t="inlineStr">
@@ -31836,7 +31896,11 @@
       </c>
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="67" t="n"/>
-      <c r="G10" s="67" t="n"/>
+      <c r="G10" s="67" t="inlineStr">
+        <is>
+          <t>Covered via Opportunity List PM columns (test_olp_list_page)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="67" t="inlineStr">
@@ -31862,9 +31926,17 @@
 - The accepted status appears after Opportunity creation, so confirm that as well</t>
         </is>
       </c>
-      <c r="E11" s="66" t="n"/>
+      <c r="E11" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F11" s="67" t="n"/>
-      <c r="G11" s="67" t="n"/>
+      <c r="G11" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (card summary fields)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="67" t="inlineStr">
@@ -31890,9 +31962,17 @@
           <t xml:space="preserve">- If there are any opportunities in a program, user should be able to see the list of all opportunities by clicking the button </t>
         </is>
       </c>
-      <c r="E12" s="66" t="n"/>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F12" s="67" t="n"/>
-      <c r="G12" s="67" t="n"/>
+      <c r="G12" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (click_view_opportunities)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="67" t="inlineStr">
@@ -31915,9 +31995,17 @@
 - The number of items in the list should be restricted to 3 per category</t>
         </is>
       </c>
-      <c r="E13" s="66" t="n"/>
+      <c r="E13" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F13" s="67" t="n"/>
-      <c r="G13" s="67" t="n"/>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (Recent Activities categories + rows)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="67" t="inlineStr">
@@ -31943,9 +32031,17 @@
 - When user clicks on an Opportunity under ‘Pending Payments’, they should jump to the Worker List page with the payment tab open</t>
         </is>
       </c>
-      <c r="E14" s="66" t="n"/>
+      <c r="E14" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F14" s="67" t="n"/>
-      <c r="G14" s="67" t="n"/>
+      <c r="G14" s="67" t="inlineStr">
+        <is>
+          <t>Automated (link target asserted): Recent Activities row hrefs</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="67" t="inlineStr">
@@ -31971,9 +32067,17 @@
 - When user clicks on an Opportunity under ‘Inactive Workers’, they should jump to the Worker List page with the filtered list of workers who have not delivered any visits or not completed a learning module in the last 3 days.</t>
         </is>
       </c>
-      <c r="E15" s="66" t="n"/>
+      <c r="E15" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F15" s="67" t="n"/>
-      <c r="G15" s="67" t="n"/>
+      <c r="G15" s="67" t="inlineStr">
+        <is>
+          <t>Automated (link target asserted): Recent Activities row hrefs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="67" t="inlineStr">
@@ -32000,9 +32104,17 @@
           <t xml:space="preserve">- Program manager should be able to see if someone applies for a program </t>
         </is>
       </c>
-      <c r="E16" s="66" t="n"/>
+      <c r="E16" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F16" s="67" t="n"/>
-      <c r="G16" s="67" t="n"/>
+      <c r="G16" s="67" t="inlineStr">
+        <is>
+          <t>Automated (setup flow: apply_to_program)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="67" t="inlineStr">
@@ -32028,9 +32140,17 @@
           <t>- User is able to see the opportunities related to specific NM user</t>
         </is>
       </c>
-      <c r="E17" s="66" t="n"/>
+      <c r="E17" s="66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F17" s="67" t="n"/>
-      <c r="G17" s="67" t="n"/>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>Automated: test_plp_list_page (View Opportunities)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E17">
@@ -33024,9 +33144,17 @@
 - Opportunities should be listed in the order of start date </t>
         </is>
       </c>
-      <c r="E2" s="69" t="n"/>
+      <c r="E2" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F2" s="73" t="n"/>
-      <c r="G2" s="73" t="n"/>
+      <c r="G2" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (verify_loaded)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="73" t="inlineStr">
@@ -33047,7 +33175,11 @@
       </c>
       <c r="E3" s="69" t="n"/>
       <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
+      <c r="G3" s="73" t="inlineStr">
+        <is>
+          <t>Not automated - stale (no Add New button on current list page)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="73" t="inlineStr">
@@ -33074,9 +33206,17 @@
 - User should also see "Add New" button </t>
         </is>
       </c>
-      <c r="E4" s="69" t="n"/>
+      <c r="E4" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F4" s="73" t="n"/>
-      <c r="G4" s="73" t="n"/>
+      <c r="G4" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (landing)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="73" t="inlineStr">
@@ -33118,9 +33258,17 @@
 - User should be able to sort the list by clicking on any column header </t>
         </is>
       </c>
-      <c r="E5" s="69" t="n"/>
+      <c r="E5" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F5" s="73" t="n"/>
-      <c r="G5" s="73" t="n"/>
+      <c r="G5" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (PM+NM columns, sortable headers)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="73" t="n"/>
@@ -33199,7 +33347,11 @@
       </c>
       <c r="E7" s="69" t="n"/>
       <c r="F7" s="73" t="n"/>
-      <c r="G7" s="73" t="n"/>
+      <c r="G7" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: filter behaviour)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="73" t="inlineStr">
@@ -33226,9 +33378,17 @@
 - User should be able to navigate forward backwards using the pagination arrows  </t>
         </is>
       </c>
-      <c r="E8" s="69" t="n"/>
+      <c r="E8" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F8" s="73" t="n"/>
-      <c r="G8" s="73" t="n"/>
+      <c r="G8" s="73" t="inlineStr">
+        <is>
+          <t>Automated: rows-per-page control (multi-page nav = Tier 2)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="73" t="inlineStr">
@@ -33249,9 +33409,17 @@
         </is>
       </c>
       <c r="D9" s="68" t="n"/>
-      <c r="E9" s="69" t="n"/>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F9" s="73" t="n"/>
-      <c r="G9" s="73" t="n"/>
+      <c r="G9" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (open_opportunity)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="73" t="inlineStr">
@@ -33280,9 +33448,17 @@
 </t>
         </is>
       </c>
-      <c r="E10" s="69" t="n"/>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F10" s="73" t="n"/>
-      <c r="G10" s="73" t="n"/>
+      <c r="G10" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (filter modal fields)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="73" t="inlineStr">
@@ -33311,9 +33487,17 @@
 - Non test opportunities should be displayed when 'no' is selected</t>
         </is>
       </c>
-      <c r="E11" s="69" t="n"/>
+      <c r="E11" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F11" s="73" t="n"/>
-      <c r="G11" s="73" t="n"/>
+      <c r="G11" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (is_test options)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
@@ -33344,9 +33528,17 @@
 - Inactive opportunities should be displayed when inactive is selected</t>
         </is>
       </c>
-      <c r="E12" s="69" t="n"/>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F12" s="73" t="n"/>
-      <c r="G12" s="73" t="n"/>
+      <c r="G12" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (status options)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="73" t="inlineStr">
@@ -33373,9 +33565,17 @@
 - Opportunities that are part of selected program should be displayed</t>
         </is>
       </c>
-      <c r="E13" s="69" t="n"/>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F13" s="73" t="n"/>
-      <c r="G13" s="73" t="n"/>
+      <c r="G13" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (program options, PM)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="73" t="inlineStr">
@@ -33404,7 +33604,11 @@
       </c>
       <c r="E14" s="69" t="n"/>
       <c r="F14" s="73" t="n"/>
-      <c r="G14" s="73" t="n"/>
+      <c r="G14" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: apply + filter badge)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
@@ -33434,7 +33638,11 @@
       </c>
       <c r="E15" s="69" t="n"/>
       <c r="F15" s="73" t="n"/>
-      <c r="G15" s="73" t="n"/>
+      <c r="G15" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: multi-select status)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="73" t="inlineStr">
@@ -33464,7 +33672,11 @@
       </c>
       <c r="E16" s="69" t="n"/>
       <c r="F16" s="73" t="n"/>
-      <c r="G16" s="73" t="n"/>
+      <c r="G16" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: multi-select program)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="73" t="inlineStr">
@@ -33492,7 +33704,11 @@
       </c>
       <c r="E17" s="69" t="n"/>
       <c r="F17" s="73" t="n"/>
-      <c r="G17" s="73" t="n"/>
+      <c r="G17" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: filter persistence)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="73" t="inlineStr">
@@ -33523,9 +33739,17 @@
 View Invoices </t>
         </is>
       </c>
-      <c r="E18" s="69" t="n"/>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F18" s="73" t="n"/>
-      <c r="G18" s="73" t="n"/>
+      <c r="G18" s="73" t="inlineStr">
+        <is>
+          <t>Automated: test_olp_list_page (kebab_options)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="73" t="inlineStr">
@@ -33551,7 +33775,11 @@
       </c>
       <c r="E19" s="69" t="n"/>
       <c r="F19" s="73" t="n"/>
-      <c r="G19" s="73" t="n"/>
+      <c r="G19" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: kebab nav target)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="73" t="inlineStr">
@@ -33577,7 +33805,11 @@
       </c>
       <c r="E20" s="69" t="n"/>
       <c r="F20" s="73" t="n"/>
-      <c r="G20" s="73" t="n"/>
+      <c r="G20" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: kebab nav target)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="73" t="inlineStr">
@@ -33603,7 +33835,11 @@
       </c>
       <c r="E21" s="69" t="n"/>
       <c r="F21" s="73" t="n"/>
-      <c r="G21" s="73" t="n"/>
+      <c r="G21" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: kebab nav target)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="73" t="inlineStr">
@@ -33631,7 +33867,11 @@
       </c>
       <c r="E22" s="69" t="n"/>
       <c r="F22" s="73" t="n"/>
-      <c r="G22" s="73" t="n"/>
+      <c r="G22" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 2: combined filters)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="73" t="inlineStr">
@@ -33659,7 +33899,11 @@
       </c>
       <c r="E23" s="69" t="n"/>
       <c r="F23" s="73" t="n"/>
-      <c r="G23" s="73" t="n"/>
+      <c r="G23" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: pending-invites drill-down)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="73" t="inlineStr">
@@ -33686,7 +33930,11 @@
       </c>
       <c r="E24" s="69" t="n"/>
       <c r="F24" s="73" t="n"/>
-      <c r="G24" s="73" t="n"/>
+      <c r="G24" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: inactive-workers drill-down)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="73" t="inlineStr">
@@ -33713,7 +33961,11 @@
       </c>
       <c r="E25" s="69" t="n"/>
       <c r="F25" s="73" t="n"/>
-      <c r="G25" s="73" t="n"/>
+      <c r="G25" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: payments-due drill-down)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="73" t="inlineStr">
@@ -33740,7 +33992,11 @@
       </c>
       <c r="E26" s="69" t="n"/>
       <c r="F26" s="73" t="n"/>
-      <c r="G26" s="73" t="n"/>
+      <c r="G26" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: active-workers drill-down)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="73" t="inlineStr">
@@ -33767,7 +34023,11 @@
       </c>
       <c r="E27" s="69" t="n"/>
       <c r="F27" s="73" t="n"/>
-      <c r="G27" s="73" t="n"/>
+      <c r="G27" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: total-deliveries drill-down)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="73" t="inlineStr">
@@ -33794,7 +34054,11 @@
       </c>
       <c r="E28" s="69" t="n"/>
       <c r="F28" s="73" t="n"/>
-      <c r="G28" s="73" t="n"/>
+      <c r="G28" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: verified-deliveries drill-down)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="73" t="inlineStr">
@@ -33821,7 +34085,11 @@
       </c>
       <c r="E29" s="69" t="n"/>
       <c r="F29" s="73" t="n"/>
-      <c r="G29" s="73" t="n"/>
+      <c r="G29" s="73" t="inlineStr">
+        <is>
+          <t>Pending (Tier 3: worker-earnings drill-down)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E29">

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -33345,11 +33345,15 @@
 Ended </t>
         </is>
       </c>
-      <c r="E7" s="69" t="n"/>
+      <c r="E7" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F7" s="73" t="n"/>
       <c r="G7" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: filter behaviour)</t>
+          <t>Automated: test_olp_list_behaviour (status filter)</t>
         </is>
       </c>
     </row>
@@ -33386,7 +33390,7 @@
       <c r="F8" s="73" t="n"/>
       <c r="G8" s="73" t="inlineStr">
         <is>
-          <t>Automated: rows-per-page control (multi-page nav = Tier 2)</t>
+          <t>Automated: test_olp_list_behaviour (pagination; skips when &lt;=20 opps)</t>
         </is>
       </c>
     </row>
@@ -33602,11 +33606,15 @@
 - Number of filters selected should be displayed on the filters icon</t>
         </is>
       </c>
-      <c r="E14" s="69" t="n"/>
+      <c r="E14" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F14" s="73" t="n"/>
       <c r="G14" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: apply + filter badge)</t>
+          <t>Automated: test_olp_list_behaviour (apply + filter badge)</t>
         </is>
       </c>
     </row>
@@ -33636,11 +33644,15 @@
           <t>- Multiple filters selected should be applied on the opportunities</t>
         </is>
       </c>
-      <c r="E15" s="69" t="n"/>
+      <c r="E15" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F15" s="73" t="n"/>
       <c r="G15" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: multi-select status)</t>
+          <t>Automated: test_olp_list_behaviour (multi-select status)</t>
         </is>
       </c>
     </row>
@@ -33670,11 +33682,15 @@
           <t>- Opportunities related to the selected programs should be displayed</t>
         </is>
       </c>
-      <c r="E16" s="69" t="n"/>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F16" s="73" t="n"/>
       <c r="G16" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: multi-select program)</t>
+          <t>Automated: test_olp_list_behaviour (program filter)</t>
         </is>
       </c>
     </row>
@@ -33702,11 +33718,15 @@
           <t>- Applied filters should be preserved when user navigate away and back</t>
         </is>
       </c>
-      <c r="E17" s="69" t="n"/>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F17" s="73" t="n"/>
       <c r="G17" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: filter persistence)</t>
+          <t>Automated: test_olp_list_behaviour (filter persistence)</t>
         </is>
       </c>
     </row>
@@ -33773,11 +33793,15 @@
           <t>- User should be land on opportunity dashboard</t>
         </is>
       </c>
-      <c r="E19" s="69" t="n"/>
+      <c r="E19" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F19" s="73" t="n"/>
       <c r="G19" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: kebab nav target)</t>
+          <t>Automated: test_olp_list_behaviour (kebab View Opportunity target)</t>
         </is>
       </c>
     </row>
@@ -33803,11 +33827,15 @@
           <t>- User should be land on Connect workers page</t>
         </is>
       </c>
-      <c r="E20" s="69" t="n"/>
+      <c r="E20" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F20" s="73" t="n"/>
       <c r="G20" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: kebab nav target)</t>
+          <t>Automated: test_olp_list_behaviour (kebab View Connect Workers target)</t>
         </is>
       </c>
     </row>
@@ -33833,11 +33861,15 @@
           <t>- User should be land on invoices page</t>
         </is>
       </c>
-      <c r="E21" s="69" t="n"/>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F21" s="73" t="n"/>
       <c r="G21" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: kebab nav target)</t>
+          <t>Automated: test_olp_list_behaviour (kebab View Invoices target)</t>
         </is>
       </c>
     </row>
@@ -33865,11 +33897,15 @@
           <t>- Opportunities based on the selected filters should be displayed</t>
         </is>
       </c>
-      <c r="E22" s="69" t="n"/>
+      <c r="E22" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F22" s="73" t="n"/>
       <c r="G22" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 2: combined filters)</t>
+          <t>Automated: test_olp_list_behaviour (combined is_test + status)</t>
         </is>
       </c>
     </row>
@@ -33897,11 +33933,15 @@
           <t>- User should be able to land on connect workers page and view the pending invites first</t>
         </is>
       </c>
-      <c r="E23" s="69" t="n"/>
+      <c r="E23" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F23" s="73" t="n"/>
       <c r="G23" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: pending-invites drill-down)</t>
+          <t>Automated: test_olp_list_page NM (Pending Invites count cell present)</t>
         </is>
       </c>
     </row>
@@ -33928,11 +33968,15 @@
           <t>- User should be able to land on connect workers page and view the Inactive workers</t>
         </is>
       </c>
-      <c r="E24" s="69" t="n"/>
+      <c r="E24" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F24" s="73" t="n"/>
       <c r="G24" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: inactive-workers drill-down)</t>
+          <t>Automated: test_olp_list_page NM (Inactive workers drill-down)</t>
         </is>
       </c>
     </row>
@@ -33959,11 +34003,15 @@
           <t>- User should be able to land on the payments tab and view the pending payments</t>
         </is>
       </c>
-      <c r="E25" s="69" t="n"/>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F25" s="73" t="n"/>
       <c r="G25" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: payments-due drill-down)</t>
+          <t>Automated: test_olp_list_page NM (Payments Due drill-down)</t>
         </is>
       </c>
     </row>
@@ -33990,11 +34038,15 @@
           <t>- User should be able to land on connect workers page</t>
         </is>
       </c>
-      <c r="E26" s="69" t="n"/>
+      <c r="E26" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F26" s="73" t="n"/>
       <c r="G26" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: active-workers drill-down)</t>
+          <t>Automated: test_olp_list_behaviour (Active workers count cell)</t>
         </is>
       </c>
     </row>
@@ -34021,11 +34073,15 @@
           <t>- User should be able to land on delivery tab and view the pending approvals</t>
         </is>
       </c>
-      <c r="E27" s="69" t="n"/>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F27" s="73" t="n"/>
       <c r="G27" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: total-deliveries drill-down)</t>
+          <t>Automated: test_olp_list_behaviour (Total Deliveries drill-down)</t>
         </is>
       </c>
     </row>
@@ -34052,11 +34108,15 @@
           <t xml:space="preserve">- User should be able to land on delivery tab </t>
         </is>
       </c>
-      <c r="E28" s="69" t="n"/>
+      <c r="E28" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F28" s="73" t="n"/>
       <c r="G28" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: verified-deliveries drill-down)</t>
+          <t>Automated: test_olp_list_behaviour (Verified Deliveries drill-down)</t>
         </is>
       </c>
     </row>
@@ -34083,11 +34143,15 @@
           <t xml:space="preserve">- User should be able to land on the payments tab </t>
         </is>
       </c>
-      <c r="E29" s="69" t="n"/>
+      <c r="E29" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F29" s="73" t="n"/>
       <c r="G29" s="73" t="inlineStr">
         <is>
-          <t>Pending (Tier 3: worker-earnings drill-down)</t>
+          <t>Automated: test_olp_list_behaviour (Worker Earnings drill-down)</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -33177,7 +33177,7 @@
       <c r="F3" s="73" t="n"/>
       <c r="G3" s="73" t="inlineStr">
         <is>
-          <t>Not automated - stale (no Add New button on current list page)</t>
+          <t>Manual - only create path is program-scoped ManagedOpportunityInit; clean 403 needs a real program slug the NM org lacks on staging (bogus slug 500s)</t>
         </is>
       </c>
     </row>
@@ -33941,7 +33941,7 @@
       <c r="F23" s="73" t="n"/>
       <c r="G23" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (Pending Invites count cell present)</t>
+          <t>Automated: test_olp_list_page NM (skips when NM org has no opportunities - unverified on staging)</t>
         </is>
       </c>
     </row>
@@ -33976,7 +33976,7 @@
       <c r="F24" s="73" t="n"/>
       <c r="G24" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (Inactive workers drill-down)</t>
+          <t>Automated: test_olp_list_page NM (skips when NM org has no opportunities - unverified on staging)</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34011,7 @@
       <c r="F25" s="73" t="n"/>
       <c r="G25" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (Payments Due drill-down)</t>
+          <t>Automated: test_olp_list_page NM (skips when NM org has no opportunities - unverified on staging)</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -33173,11 +33173,15 @@
           <t>-User is not able to create an opportunity as NM user</t>
         </is>
       </c>
-      <c r="E3" s="69" t="n"/>
+      <c r="E3" s="69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F3" s="73" t="n"/>
       <c r="G3" s="73" t="inlineStr">
         <is>
-          <t>Manual - only create path is program-scoped ManagedOpportunityInit; clean 403 needs a real program slug the NM org lacks on staging (bogus slug 500s)</t>
+          <t>Automated: test_olp_list_page NM (managed opportunity-init returns 403 for NM; uses seeded program_id)</t>
         </is>
       </c>
     </row>
@@ -33941,7 +33945,7 @@
       <c r="F23" s="73" t="n"/>
       <c r="G23" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (skips when NM org has no opportunities - unverified on staging)</t>
+          <t>Automated: test_olp_list_page NM (Pending Invites count cell) - runs only when NM list has rows</t>
         </is>
       </c>
     </row>
@@ -33976,7 +33980,7 @@
       <c r="F24" s="73" t="n"/>
       <c r="G24" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (skips when NM org has no opportunities - unverified on staging)</t>
+          <t>Automated: test_olp_list_page NM (Inactive workers drill-down) - runs only when NM list has rows</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34015,7 @@
       <c r="F25" s="73" t="n"/>
       <c r="G25" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (skips when NM org has no opportunities - unverified on staging)</t>
+          <t>Automated: test_olp_list_page NM (Payments Due drill-down) - runs only when NM list has rows</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -33945,7 +33945,7 @@
       <c r="F23" s="73" t="n"/>
       <c r="G23" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (Pending Invites count cell) - runs only when NM list has rows</t>
+          <t>Automated: test_olp_list_page NM (Pending Invites count cell) - verified with seeded OLP_Test_Opp</t>
         </is>
       </c>
     </row>
@@ -33980,7 +33980,7 @@
       <c r="F24" s="73" t="n"/>
       <c r="G24" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (Inactive workers drill-down) - runs only when NM list has rows</t>
+          <t>Automated: test_olp_list_page NM (Inactive workers drill-down) - verified with seeded OLP_Test_Opp</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       <c r="F25" s="73" t="n"/>
       <c r="G25" s="73" t="inlineStr">
         <is>
-          <t>Automated: test_olp_list_page NM (Payments Due drill-down) - runs only when NM list has rows</t>
+          <t>Automated: test_olp_list_page NM (Payments Due drill-down) - verified with seeded OLP_Test_Opp</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -186,8 +186,12 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -316,8 +320,13 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border/>
     <border>
       <left style="thin">
@@ -445,11 +454,17 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -950,6 +965,12 @@
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,7 +1628,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="41.5" customWidth="1" style="148" min="2" max="2"/>
@@ -2320,6 +2341,864 @@
       <c r="G21" s="123" t="n"/>
       <c r="H21" s="123" t="n"/>
       <c r="I21" s="123" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="188" t="inlineStr">
+        <is>
+          <t>OD_20</t>
+        </is>
+      </c>
+      <c r="B22" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the hamburger menu differs by role (PM vs Network Manager)</t>
+        </is>
+      </c>
+      <c r="C22" s="189" t="inlineStr">
+        <is>
+          <t>1. Login as a Program Manager (PM_Automation_01)
+2. Open an opportunity dashboard
+3. Open the hamburger menu and note options
+4. Repeat as a Network Manager on the same opportunity</t>
+        </is>
+      </c>
+      <c r="D22" s="189" t="inlineStr">
+        <is>
+          <t>PM sees the full set incl. Edit Opportunity, Add Payment Unit, Verification Rules, Configure Task Types.
+Network Manager sees only the non-PM subset (View Invoices, Catchment Areas, Add Budget, Send Message, and Add Connect Workers when not ended).</t>
+        </is>
+      </c>
+      <c r="E22" s="188" t="inlineStr"/>
+      <c r="F22" s="188" t="inlineStr"/>
+      <c r="G22" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:13-65 (is_opportunity_pm gating).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="188" t="inlineStr">
+        <is>
+          <t>OD_21</t>
+        </is>
+      </c>
+      <c r="B23" s="189" t="inlineStr">
+        <is>
+          <t>Confirm a Viewer has read-only access to the dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="189" t="inlineStr">
+        <is>
+          <t>1. Login as a user with the VIEWER org role
+2. Open an opportunity dashboard
+3. Try to open the hamburger menu
+4. Inspect worker-tab action buttons</t>
+        </is>
+      </c>
+      <c r="D23" s="189" t="inlineStr">
+        <is>
+          <t>Dashboard and all stat panels load for the viewer.
+The hamburger icon is non-interactive (menu cannot be opened).
+Action controls (Add Worker, Resend Invite, Delete, Exports/Imports) are disabled.</t>
+        </is>
+      </c>
+      <c r="E23" s="188" t="inlineStr"/>
+      <c r="F23" s="188" t="inlineStr"/>
+      <c r="G23" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:33-40 (viewer icon has no @click); workers.html action gating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="188" t="inlineStr">
+        <is>
+          <t>OD_22</t>
+        </is>
+      </c>
+      <c r="B24" s="189" t="inlineStr">
+        <is>
+          <t>Confirm a standalone (non-program-managed) opportunity hides PM-only menu items</t>
+        </is>
+      </c>
+      <c r="C24" s="189" t="inlineStr">
+        <is>
+          <t>1. Open a standalone opportunity (not owned by a program-manager org)
+2. Open the hamburger menu</t>
+        </is>
+      </c>
+      <c r="D24" s="189" t="inlineStr">
+        <is>
+          <t>PM-only items (Edit Opportunity, Add Payment Unit, Verification Rules, Configure Task Types) are not shown because is_opportunity_pm is False for standalone opps.</t>
+        </is>
+      </c>
+      <c r="E24" s="188" t="inlineStr"/>
+      <c r="F24" s="188" t="inlineStr"/>
+      <c r="G24" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: program/utils.py:5-19; users/middleware.py:36-52.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="188" t="inlineStr">
+        <is>
+          <t>OD_23</t>
+        </is>
+      </c>
+      <c r="B25" s="189" t="inlineStr">
+        <is>
+          <t>Confirm an opportunity with incomplete setup redirects to Add Payment Units</t>
+        </is>
+      </c>
+      <c r="C25" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity whose setup is not complete (no payment units)
+2. Navigate to its dashboard URL</t>
+        </is>
+      </c>
+      <c r="D25" s="189" t="inlineStr">
+        <is>
+          <t>Instead of the dashboard, the user is redirected to the Add Payment Units page with a warning message.</t>
+        </is>
+      </c>
+      <c r="E25" s="188" t="inlineStr"/>
+      <c r="F25" s="188" t="inlineStr"/>
+      <c r="G25" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:455-459 (is_setup_complete guard).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="188" t="inlineStr">
+        <is>
+          <t>OD_24</t>
+        </is>
+      </c>
+      <c r="B26" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the status badge is correct for Active / Ended / Inactive opportunities</t>
+        </is>
+      </c>
+      <c r="C26" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an Active opportunity and read the status badge
+2. Repeat for an ended opportunity (past end date) and an inactive one</t>
+        </is>
+      </c>
+      <c r="D26" s="189" t="inlineStr">
+        <is>
+          <t>Badge reads Active (positive), Ended (warning) or Inactive (negative) matching the opportunity state.</t>
+        </is>
+      </c>
+      <c r="E26" s="188" t="inlineStr"/>
+      <c r="F26" s="188" t="inlineStr">
+        <is>
+          <t>Potential product risk</t>
+        </is>
+      </c>
+      <c r="G26" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. NOTE: 'Ended' branch reads raw object.active while 'Active' reads is_active property - verify an ended-but-active opp badges as intended. Src: dashboard.html:94-100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="188" t="inlineStr">
+        <is>
+          <t>OD_25</t>
+        </is>
+      </c>
+      <c r="B27" s="189" t="inlineStr">
+        <is>
+          <t>Confirm an empty opportunity (0 workers/deliveries/payments) renders without errors</t>
+        </is>
+      </c>
+      <c r="C27" s="189" t="inlineStr">
+        <is>
+          <t>1. Open a newly-created opportunity with no invited workers, deliveries or payments
+2. Review all dashboard cards, progress bars and timestamps</t>
+        </is>
+      </c>
+      <c r="D27" s="189" t="inlineStr">
+        <is>
+          <t>Counts render as 0, progress bars show 0% (no divide-by-zero), and 'Last Delivery'/'Last Payment' show '--'; no errors or blank panels.</t>
+        </is>
+      </c>
+      <c r="E27" s="188" t="inlineStr"/>
+      <c r="F27" s="188" t="inlineStr"/>
+      <c r="G27" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:3051-3053 safe_percent; 3207-3213 fallbacks; 470-475 safe_display.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="188" t="inlineStr">
+        <is>
+          <t>OD_26</t>
+        </is>
+      </c>
+      <c r="B28" s="189" t="inlineStr">
+        <is>
+          <t>Confirm a Test opportunity (is_test) renders the Test badge and test theme</t>
+        </is>
+      </c>
+      <c r="C28" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity flagged as a test opportunity
+2. Observe the header badge and card styling</t>
+        </is>
+      </c>
+      <c r="D28" s="189" t="inlineStr">
+        <is>
+          <t>A 'Test' badge is shown and the dashboard uses the test visual theme (distinct card colours/separators).</t>
+        </is>
+      </c>
+      <c r="E28" s="188" t="inlineStr"/>
+      <c r="F28" s="188" t="inlineStr"/>
+      <c r="G28" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:5,27,32,90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="188" t="inlineStr">
+        <is>
+          <t>OD_27</t>
+        </is>
+      </c>
+      <c r="B29" s="189" t="inlineStr">
+        <is>
+          <t>Confirm currency values are formatted correctly across the dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity with a currency set
+2. Compare Max Budget (basic details), the Worker Payments panel title, and the worker-progress earned/paid values</t>
+        </is>
+      </c>
+      <c r="D29" s="189" t="inlineStr">
+        <is>
+          <t>All monetary values show the correct currency code and thousands separators consistently across the three surfaces.</t>
+        </is>
+      </c>
+      <c r="E29" s="188" t="inlineStr"/>
+      <c r="F29" s="188" t="inlineStr"/>
+      <c r="G29" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:525, 3060-3061, 3211 (three currency-format paths).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="188" t="inlineStr">
+        <is>
+          <t>OD_28</t>
+        </is>
+      </c>
+      <c r="B30" s="189" t="inlineStr">
+        <is>
+          <t>Confirm MICROPLANNING flag controls the Work Areas tab and Progress Map</t>
+        </is>
+      </c>
+      <c r="C30" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity with the MICROPLANNING flag ON: check the worker Work Areas tab and 'View Progress Map'
+2. Repeat with the flag OFF, and also request the work-areas URL directly</t>
+        </is>
+      </c>
+      <c r="D30" s="189" t="inlineStr">
+        <is>
+          <t>Flag ON: Work Areas tab is present and View Progress Map opens microplanning.
+Flag OFF: the Work Areas tab is absent and the direct work-areas URL returns 404.</t>
+        </is>
+      </c>
+      <c r="E30" s="188" t="inlineStr"/>
+      <c r="F30" s="188" t="inlineStr"/>
+      <c r="G30" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2646-2653, 2849-2852 (WorkerWorkAreaView 404).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="188" t="inlineStr">
+        <is>
+          <t>OD_29</t>
+        </is>
+      </c>
+      <c r="B31" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the View Progress Map / Audit Opportunity / Tasks Assigned panels navigate correctly</t>
+        </is>
+      </c>
+      <c r="C31" s="189" t="inlineStr">
+        <is>
+          <t>1. On the dashboard, click 'View Progress Map', 'Audit Opportunity' and 'Tasks Assigned to Connect Workers' panels in turn</t>
+        </is>
+      </c>
+      <c r="D31" s="189" t="inlineStr">
+        <is>
+          <t>Each opens its target page (microplanning home, audit report list, assigned task list) and enforces access control (no unhandled error/403).</t>
+        </is>
+      </c>
+      <c r="E31" s="188" t="inlineStr"/>
+      <c r="F31" s="188" t="inlineStr">
+        <is>
+          <t>Potential product risk</t>
+        </is>
+      </c>
+      <c r="G31" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. NOTE: these links render on every opportunity with no MICROPLANNING guard - verify they don't 404/deny on non-microplanning opps. Src: views.py:3152-3201.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="188" t="inlineStr">
+        <is>
+          <t>OD_30</t>
+        </is>
+      </c>
+      <c r="B32" s="189" t="inlineStr">
+        <is>
+          <t>Confirm 24h increment badges appear only on Services Delivered and Payments Earned</t>
+        </is>
+      </c>
+      <c r="C32" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity with deliveries/payments in the last 24h
+2. Inspect each stat panel for the increment badge</t>
+        </is>
+      </c>
+      <c r="D32" s="189" t="inlineStr">
+        <is>
+          <t>An increment 'up-arrow' badge (with a 'last 24 hours' tooltip) shows on the Services Delivered and Payments Earned panels only; other panels show no increment.</t>
+        </is>
+      </c>
+      <c r="E32" s="188" t="inlineStr"/>
+      <c r="F32" s="188" t="inlineStr"/>
+      <c r="G32" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_delivery_stat.html:56-62; views.py:3150, 3223.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="188" t="inlineStr">
+        <is>
+          <t>OD_31</t>
+        </is>
+      </c>
+      <c r="B33" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the Worker Progress Funnel shows all 7 stages with correct counts and tooltips</t>
+        </is>
+      </c>
+      <c r="C33" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity dashboard
+2. Read each funnel stage count and hover its tooltip</t>
+        </is>
+      </c>
+      <c r="D33" s="189" t="inlineStr">
+        <is>
+          <t>Seven stages render - Invited, Accepted, Started Learning, Completed Learning, Completed Assessment, Claimed Job, Started Delivery - with correct counts (Accepted = Invited - pending) and tooltips.</t>
+        </is>
+      </c>
+      <c r="E33" s="188" t="inlineStr"/>
+      <c r="F33" s="188" t="inlineStr"/>
+      <c r="G33" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2989-3037.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="188" t="inlineStr">
+        <is>
+          <t>OD_32</t>
+        </is>
+      </c>
+      <c r="B34" s="189" t="inlineStr">
+        <is>
+          <t>Confirm worker-progress bars show Approved/Rejected and Earned/Paid percentages with tooltips</t>
+        </is>
+      </c>
+      <c r="C34" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an opportunity with deliveries and payments
+2. Inspect the worker-progress section bars and tooltips</t>
+        </is>
+      </c>
+      <c r="D34" s="189" t="inlineStr">
+        <is>
+          <t>Bars show Approved/Rejected as % of total deliveries and Earned/Paid as % of budget/accrued, each with the correct percentage, badge and tooltip.</t>
+        </is>
+      </c>
+      <c r="E34" s="188" t="inlineStr"/>
+      <c r="F34" s="188" t="inlineStr"/>
+      <c r="G34" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:3055-3116.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="188" t="inlineStr">
+        <is>
+          <t>OD_33</t>
+        </is>
+      </c>
+      <c r="B35" s="189" t="inlineStr">
+        <is>
+          <t>Confirm resource cards show live counts and open the modal on the correct tab</t>
+        </is>
+      </c>
+      <c r="C35" s="189" t="inlineStr">
+        <is>
+          <t>1. On the dashboard, note the counts on the Learn App / Deliver App / Payment Units cards
+2. Click each card</t>
+        </is>
+      </c>
+      <c r="D35" s="189" t="inlineStr">
+        <is>
+          <t>Each card shows the live count and opens the resource modal pre-selected to the matching tab (Learn App / Deliver App / Payment Units).</t>
+        </is>
+      </c>
+      <c r="E35" s="188" t="inlineStr"/>
+      <c r="F35" s="188" t="inlineStr"/>
+      <c r="G35" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:466-489; dashboard.html:58-69.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="188" t="inlineStr">
+        <is>
+          <t>OD_34</t>
+        </is>
+      </c>
+      <c r="B36" s="189" t="inlineStr">
+        <is>
+          <t>Confirm Edit Opportunity, Add Payment Unit and Configure Task Types open (PM)</t>
+        </is>
+      </c>
+      <c r="C36" s="189" t="inlineStr">
+        <is>
+          <t>1. As PM, open the hamburger menu
+2. Click Edit Opportunity, then Add Payment Unit, then Configure Task Types</t>
+        </is>
+      </c>
+      <c r="D36" s="189" t="inlineStr">
+        <is>
+          <t>Each option opens its respective PM configuration page.</t>
+        </is>
+      </c>
+      <c r="E36" s="188" t="inlineStr"/>
+      <c r="F36" s="188" t="inlineStr"/>
+      <c r="G36" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:15,19,62.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="188" t="inlineStr">
+        <is>
+          <t>OD_35</t>
+        </is>
+      </c>
+      <c r="B37" s="189" t="inlineStr">
+        <is>
+          <t>Confirm View Invoices opens the invoice list for all roles</t>
+        </is>
+      </c>
+      <c r="C37" s="189" t="inlineStr">
+        <is>
+          <t>1. Open the hamburger menu (any role)
+2. Click View Invoices</t>
+        </is>
+      </c>
+      <c r="D37" s="189" t="inlineStr">
+        <is>
+          <t>The invoice list page opens for PM and non-PM members; PM additionally sees the invoice-ticket link.</t>
+        </is>
+      </c>
+      <c r="E37" s="188" t="inlineStr"/>
+      <c r="F37" s="188" t="inlineStr"/>
+      <c r="G37" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:24; views.py:1789.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="188" t="inlineStr">
+        <is>
+          <t>OD_36</t>
+        </is>
+      </c>
+      <c r="B38" s="189" t="inlineStr">
+        <is>
+          <t>Confirm Catchment Areas import validates columns and export downloads a file</t>
+        </is>
+      </c>
+      <c r="C38" s="189" t="inlineStr">
+        <is>
+          <t>1. Open hamburger &gt;&gt; Catchment Areas &gt;&gt; Import; upload a file missing required columns
+2. Then use Export</t>
+        </is>
+      </c>
+      <c r="D38" s="189" t="inlineStr">
+        <is>
+          <t>Import rejects/validates against required columns (Area Name, Active, Latitude, Longitude, Site code, Radius); Export downloads the catchment file.</t>
+        </is>
+      </c>
+      <c r="E38" s="188" t="inlineStr"/>
+      <c r="F38" s="188" t="inlineStr"/>
+      <c r="G38" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:27-39; dashboard.html:111-114.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="188" t="inlineStr">
+        <is>
+          <t>OD_37</t>
+        </is>
+      </c>
+      <c r="B39" s="189" t="inlineStr">
+        <is>
+          <t>Confirm Add Connect Workers is hidden when the opportunity has ended</t>
+        </is>
+      </c>
+      <c r="C39" s="189" t="inlineStr">
+        <is>
+          <t>1. Open an ended opportunity's hamburger menu</t>
+        </is>
+      </c>
+      <c r="D39" s="189" t="inlineStr">
+        <is>
+          <t>The 'Add Connect Workers' option is not shown for an ended opportunity.</t>
+        </is>
+      </c>
+      <c r="E39" s="188" t="inlineStr"/>
+      <c r="F39" s="188" t="inlineStr"/>
+      <c r="G39" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:40 (has_ended).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="188" t="inlineStr">
+        <is>
+          <t>OD_38</t>
+        </is>
+      </c>
+      <c r="B40" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the Learn tab shows learn columns and per-worker learn progress</t>
+        </is>
+      </c>
+      <c r="C40" s="189" t="inlineStr">
+        <is>
+          <t>1. Open the opportunity &gt;&gt; Connect Workers &gt;&gt; Learn tab</t>
+        </is>
+      </c>
+      <c r="D40" s="189" t="inlineStr">
+        <is>
+          <t>The Learn tab lists workers with learn columns (Started/Completed Learning, modules completed, assessment, attempts, learning hours) and per-worker learn history.</t>
+        </is>
+      </c>
+      <c r="E40" s="188" t="inlineStr"/>
+      <c r="F40" s="188" t="inlineStr"/>
+      <c r="G40" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2590-2596; tables.py:1366.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="188" t="inlineStr">
+        <is>
+          <t>OD_39</t>
+        </is>
+      </c>
+      <c r="B41" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the Tasks tab shows task columns and its filters</t>
+        </is>
+      </c>
+      <c r="C41" s="189" t="inlineStr">
+        <is>
+          <t>1. Open the opportunity &gt;&gt; Tasks tab
+2. Apply the worker-name, task-status, task-type and date-range filters</t>
+        </is>
+      </c>
+      <c r="D41" s="189" t="inlineStr">
+        <is>
+          <t>The Tasks tab lists tasks with the correct columns and each filter narrows the results as expected.</t>
+        </is>
+      </c>
+      <c r="E41" s="188" t="inlineStr"/>
+      <c r="F41" s="188" t="inlineStr"/>
+      <c r="G41" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2590-2596; filters.py:166-200; tables.py:1333.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="188" t="inlineStr">
+        <is>
+          <t>OD_40</t>
+        </is>
+      </c>
+      <c r="B42" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the Connect Workers tab count and the worker search</t>
+        </is>
+      </c>
+      <c r="C42" s="189" t="inlineStr">
+        <is>
+          <t>1. Open the Connect Workers tab and note the '(N)' count in the tab label
+2. Search by name/phone in the search box and use the clear button</t>
+        </is>
+      </c>
+      <c r="D42" s="189" t="inlineStr">
+        <is>
+          <t>The tab label shows the live worker count; search filters the table, shows a 'Displaying X of Y' line, and the clear button restores the full list.</t>
+        </is>
+      </c>
+      <c r="E42" s="188" t="inlineStr"/>
+      <c r="F42" s="188" t="inlineStr"/>
+      <c r="G42" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2640-2641, 2707-2723; workers.html:10-33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="188" t="inlineStr">
+        <is>
+          <t>OD_41</t>
+        </is>
+      </c>
+      <c r="B43" s="189" t="inlineStr">
+        <is>
+          <t>Confirm per-tab filters persist across tab navigation</t>
+        </is>
+      </c>
+      <c r="C43" s="189" t="inlineStr">
+        <is>
+          <t>1. Apply a filter on the Deliver tab
+2. Switch to another tab and back
+3. Then re-enter the workers area from elsewhere</t>
+        </is>
+      </c>
+      <c r="D43" s="189" t="inlineStr">
+        <is>
+          <t>The applied filter is retained per tab while navigating between tabs, and is cleared when the workers area is entered from an external page.</t>
+        </is>
+      </c>
+      <c r="E43" s="188" t="inlineStr"/>
+      <c r="F43" s="188" t="inlineStr"/>
+      <c r="G43" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2598-2637 (session/referer-based filter persistence).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="188" t="inlineStr">
+        <is>
+          <t>OD_42</t>
+        </is>
+      </c>
+      <c r="B44" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the Deliver tab filters behave correctly</t>
+        </is>
+      </c>
+      <c r="C44" s="189" t="inlineStr">
+        <is>
+          <t>1. Open the Deliver tab
+2. Apply each filter: last_active (1/3/7 days), has_duplicates, has_flags, has_overlimit, review_pending</t>
+        </is>
+      </c>
+      <c r="D44" s="189" t="inlineStr">
+        <is>
+          <t>Each filter narrows the delivery list according to its criterion.</t>
+        </is>
+      </c>
+      <c r="E44" s="188" t="inlineStr"/>
+      <c r="F44" s="188" t="inlineStr"/>
+      <c r="G44" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: filters.py:104-137.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="188" t="inlineStr">
+        <is>
+          <t>OD_43</t>
+        </is>
+      </c>
+      <c r="B45" s="189" t="inlineStr">
+        <is>
+          <t>Confirm auto-verification changes the Deliver tab filters and columns</t>
+        </is>
+      </c>
+      <c r="C45" s="189" t="inlineStr">
+        <is>
+          <t>1. Open the Deliver tab of an opportunity with automatic_visit_verification = True</t>
+        </is>
+      </c>
+      <c r="D45" s="189" t="inlineStr">
+        <is>
+          <t>The review_pending and has_duplicates filters are not offered, and the 'Pending' column is absent from the delivery table.</t>
+        </is>
+      </c>
+      <c r="E45" s="188" t="inlineStr"/>
+      <c r="F45" s="188" t="inlineStr"/>
+      <c r="G45" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: filters.py:135-137; views.py:2787-2788.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="188" t="inlineStr">
+        <is>
+          <t>OD_44</t>
+        </is>
+      </c>
+      <c r="B46" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the Deliver tab export offers NM vs PM sheets and completes the download flow</t>
+        </is>
+      </c>
+      <c r="C46" s="189" t="inlineStr">
+        <is>
+          <t>1. On the Deliver tab, open the export modal
+2. Choose 'User Visits Sheet' (NM) then 'PM Review Sheet' (PM) and export
+3. Follow the export-status spinner to download</t>
+        </is>
+      </c>
+      <c r="D46" s="189" t="inlineStr">
+        <is>
+          <t>The radio switches between the NM Visits Sheet and PM Review Sheet exports; the export queues, the status banner shows progress, and the file downloads. PM-review options are hidden when auto-verification is on.</t>
+        </is>
+      </c>
+      <c r="E46" s="188" t="inlineStr"/>
+      <c r="F46" s="188" t="inlineStr"/>
+      <c r="G46" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2753-2774, 536-602; deliver.html:36-84.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="188" t="inlineStr">
+        <is>
+          <t>OD_45</t>
+        </is>
+      </c>
+      <c r="B47" s="189" t="inlineStr">
+        <is>
+          <t>Confirm export/download enforces opportunity ownership (security)</t>
+        </is>
+      </c>
+      <c r="C47" s="189" t="inlineStr">
+        <is>
+          <t>1. Start an export in opportunity A to obtain an export_task_id
+2. Request export_status/download_export for opportunity B using A's task id</t>
+        </is>
+      </c>
+      <c r="D47" s="189" t="inlineStr">
+        <is>
+          <t>The cross-opportunity request is rejected (404); a user cannot download another opportunity's export via its task id.</t>
+        </is>
+      </c>
+      <c r="E47" s="188" t="inlineStr"/>
+      <c r="F47" s="188" t="inlineStr">
+        <is>
+          <t>Potential product risk</t>
+        </is>
+      </c>
+      <c r="G47" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:536-602 (get_opportunity_or_404 on the task args).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="188" t="inlineStr">
+        <is>
+          <t>OD_46</t>
+        </is>
+      </c>
+      <c r="B48" s="189" t="inlineStr">
+        <is>
+          <t>Confirm visit and payment imports validate file type and columns</t>
+        </is>
+      </c>
+      <c r="C48" s="189" t="inlineStr">
+        <is>
+          <t>1. On the Deliver tab, import a non-csv/xlsx file
+2. On the Payments tab, import a file missing the required columns</t>
+        </is>
+      </c>
+      <c r="D48" s="189" t="inlineStr">
+        <is>
+          <t>Non-csv/xlsx uploads are rejected; the payment import requires Username/Amount/Payment Date columns and reports errors otherwise. Import titles differ ('Import PM Review Sheet' vs 'Import Verified Visits').</t>
+        </is>
+      </c>
+      <c r="E48" s="188" t="inlineStr"/>
+      <c r="F48" s="188" t="inlineStr"/>
+      <c r="G48" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:614-615; payments.html:18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="188" t="inlineStr">
+        <is>
+          <t>OD_47</t>
+        </is>
+      </c>
+      <c r="B49" s="189" t="inlineStr">
+        <is>
+          <t>Confirm the dashboard stat HTMX endpoints load independently and are viewer-accessible</t>
+        </is>
+      </c>
+      <c r="C49" s="189" t="inlineStr">
+        <is>
+          <t>1. Load the dashboard and observe delivery_stats, worker_progress_stats and funnel_progress_stats loading
+2. Request each endpoint directly, including as a viewer</t>
+        </is>
+      </c>
+      <c r="D49" s="189" t="inlineStr">
+        <is>
+          <t>Each stat section loads via its own HTMX request on page load and each endpoint responds successfully, including for the VIEWER role.</t>
+        </is>
+      </c>
+      <c r="E49" s="188" t="inlineStr"/>
+      <c r="F49" s="188" t="inlineStr"/>
+      <c r="G49" s="189" t="inlineStr">
+        <is>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: urls.py:164-173; @org_viewer_required.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E21">

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -1959,7 +1959,11 @@
       </c>
       <c r="E9" s="66" t="n"/>
       <c r="F9" s="123" t="n"/>
-      <c r="G9" s="123" t="n"/>
+      <c r="G9" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Web part automated (Send Message page reachable) - PR #38, tests/test_opd_budget.py::test_opd_08_send_message_page. MOBILE HALF NOT AUTOMATED (push notification on device + notification history) - out of web/Playwright scope; needs a Maestro mobile hybrid test (device signs in as the enrolled worker after the web send, like TASKING_HYBRID / test_e2e_relearn_lifecycle). Prereqs: enrolled mobile worker on the opp, BrowserStack/Appium, a new Maestro flow; runs @on_demand.</t>
+        </is>
+      </c>
       <c r="H9" s="123" t="n"/>
       <c r="I9" s="123" t="n"/>
     </row>
@@ -1991,7 +1995,11 @@
       </c>
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="123" t="n"/>
-      <c r="G10" s="123" t="n"/>
+      <c r="G10" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget.py::test_opd_09_add_connect_workers_redirect (redirects to user_invite; #id_users present).</t>
+        </is>
+      </c>
       <c r="H10" s="123" t="n"/>
       <c r="I10" s="123" t="n"/>
     </row>
@@ -2023,7 +2031,11 @@
       </c>
       <c r="E11" s="66" t="n"/>
       <c r="F11" s="123" t="n"/>
-      <c r="G11" s="123" t="n"/>
+      <c r="G11" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget_mutations.py::test_opd_10 (increase visits; Max Visits reflects; mutate-then-revert on the dedicated staging Add Budget opp; net-zero).</t>
+        </is>
+      </c>
       <c r="H11" s="123" t="n"/>
       <c r="I11" s="123" t="n"/>
     </row>
@@ -2055,7 +2067,11 @@
       </c>
       <c r="E12" s="66" t="n"/>
       <c r="F12" s="123" t="n"/>
-      <c r="G12" s="123" t="n"/>
+      <c r="G12" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget_mutations.py::test_opd_11_increase_visits_proportional (delta = N x payment units; net-zero).</t>
+        </is>
+      </c>
       <c r="H12" s="123" t="n"/>
       <c r="I12" s="123" t="n"/>
     </row>
@@ -2087,7 +2103,11 @@
       </c>
       <c r="E13" s="66" t="n"/>
       <c r="F13" s="123" t="n"/>
-      <c r="G13" s="123" t="n"/>
+      <c r="G13" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget_mutations.py::test_opd_12_decrease_visits_proportional (net-zero increase-then-decrease).</t>
+        </is>
+      </c>
       <c r="H13" s="123" t="n"/>
       <c r="I13" s="123" t="n"/>
     </row>
@@ -2119,7 +2139,11 @@
       </c>
       <c r="E14" s="66" t="n"/>
       <c r="F14" s="123" t="n"/>
-      <c r="G14" s="123" t="n"/>
+      <c r="G14" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget.py::test_opd_13_negative_visits_validation (number_of_visits min=1 via browser ValidityState).</t>
+        </is>
+      </c>
       <c r="H14" s="123" t="n"/>
       <c r="I14" s="123" t="n"/>
     </row>
@@ -2149,7 +2173,11 @@
       </c>
       <c r="E15" s="66" t="n"/>
       <c r="F15" s="123" t="n"/>
-      <c r="G15" s="123" t="n"/>
+      <c r="G15" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget_mutations.py::test_opd_14 (decrease below completed/zero rejected with 'Cannot decrease...' error; no change). Exercised via a below-zero decrease (same validation/message); the exact below-COMPLETED path additionally needs a worker with completed visits.</t>
+        </is>
+      </c>
       <c r="H15" s="123" t="n"/>
       <c r="I15" s="123" t="n"/>
     </row>
@@ -2178,7 +2206,11 @@
       </c>
       <c r="E16" s="66" t="n"/>
       <c r="F16" s="123" t="n"/>
-      <c r="G16" s="123" t="n"/>
+      <c r="G16" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Web reflection automated (Connect Workers/Deliver max-visit denominators) - PR #38, test_opd_budget_mutations.py::test_opd_15_change_reflected_on_connect_workers. MOBILE REFLECTION NOT AUTOMATED (updated visit count on the device) - out of web scope; needs the same Maestro mobile hybrid follow-up as OD_8.</t>
+        </is>
+      </c>
       <c r="H16" s="123" t="n"/>
       <c r="I16" s="123" t="n"/>
     </row>
@@ -2208,7 +2240,11 @@
       </c>
       <c r="E17" s="66" t="n"/>
       <c r="F17" s="123" t="n"/>
-      <c r="G17" s="123" t="n"/>
+      <c r="G17" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget.py::test_opd_16_confirm_modal_shows_computed_visits (totalVisits shown in the confirm modal; no submit).</t>
+        </is>
+      </c>
       <c r="H17" s="123" t="n"/>
       <c r="I17" s="123" t="n"/>
     </row>
@@ -2240,7 +2276,11 @@
       </c>
       <c r="E18" s="66" t="n"/>
       <c r="F18" s="123" t="n"/>
-      <c r="G18" s="123" t="n"/>
+      <c r="G18" s="123" t="inlineStr">
+        <is>
+          <t>AUTOMATION: Automated - PR #38, test_opd_budget.py::test_opd_17_new_workers_autocalc_total_budget (total_budget auto-updates with the new-worker count).</t>
+        </is>
+      </c>
       <c r="H18" s="123" t="n"/>
       <c r="I18" s="123" t="n"/>
     </row>
@@ -2863,7 +2903,7 @@
       <c r="F38" s="188" t="inlineStr"/>
       <c r="G38" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:27-39; dashboard.html:111-114.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:27-39; dashboard.html:111-114. | AUTOMATION: Automated - PR #38, tests/test_opd_exports.py (catchment Export queues a background task; Import with missing columns rejected). Non-mutating.</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3142,7 @@
       <c r="F46" s="188" t="inlineStr"/>
       <c r="G46" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2753-2774, 536-602; deliver.html:36-84.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2753-2774, 536-602; deliver.html:36-84. | AUTOMATION: Partially automated - PR #38, test_opd_exports.py::test_opd_44_deliver_export_flow. NM 'User Visits Sheet' option + export form verified; the background export queue is best-effort (required-heavy HTMX form). PM 'PM Review Sheet' is hidden when automatic_visit_verification is ON - both current staging opps (Demo Opportunity, Add Budget Opp) are auto-verify, verified 2026-09-02 - so the PM path can't run live yet. BLOCKED: needs a manual-verification (auto-verify OFF) staging opp.</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3206,7 @@
       <c r="F48" s="188" t="inlineStr"/>
       <c r="G48" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:614-615; payments.html:18.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:614-615; payments.html:18. | AUTOMATION: Partially automated - PR #38, tests/test_opd_exports.py. Payments import rejects non-csv/xlsx ('File format not supported') - automated. Visit-status import is hidden under automatic_visit_verification (skips on current auto-verify staging opps). BLOCKED: needs a manual-verification staging opp.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -3142,7 +3142,7 @@
       <c r="F46" s="188" t="inlineStr"/>
       <c r="G46" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2753-2774, 536-602; deliver.html:36-84. | AUTOMATION: Partially automated - PR #38, test_opd_exports.py::test_opd_44_deliver_export_flow. NM 'User Visits Sheet' option + export form verified; the background export queue is best-effort (required-heavy HTMX form). PM 'PM Review Sheet' is hidden when automatic_visit_verification is ON - both current staging opps (Demo Opportunity, Add Budget Opp) are auto-verify, verified 2026-09-02 - so the PM path can't run live yet. BLOCKED: needs a manual-verification (auto-verify OFF) staging opp.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. | AUTOMATION: Automated - PR #38, tests/test_opd_exports.py::test_opd_44_deliver_export_flow. Runs on the manual-verification opp 'Manual approval opp' (org pm_automation_02, staging) and asserts BOTH the NM 'User Visits Sheet' and PM 'PM Review Sheet' export options; the background export queue is best-effort (required-heavy HTMX form). Staging only (manual-flow opp does not exist on prod).</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       <c r="F48" s="188" t="inlineStr"/>
       <c r="G48" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:614-615; payments.html:18. | AUTOMATION: Partially automated - PR #38, tests/test_opd_exports.py. Payments import rejects non-csv/xlsx ('File format not supported') - automated. Visit-status import is hidden under automatic_visit_verification (skips on current auto-verify staging opps). BLOCKED: needs a manual-verification staging opp.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. | AUTOMATION: Automated - PR #38, tests/test_opd_exports.py. Payments import rejects non-csv/xlsx ('File format not supported'). Visit-status import runs on the manual-verification opp (pm_automation_02, staging) and rejects a non-csv/xlsx file. Staging only for the visit import (hidden under auto-verification).</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -2411,7 +2411,7 @@
       <c r="F22" s="188" t="inlineStr"/>
       <c r="G22" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:13-65 (is_opportunity_pm gating).</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:13-65 (is_opportunity_pm gating). | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_20 (NM view of the manual opp via nm_automation; PM-only menu items absent).</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       <c r="F23" s="188" t="inlineStr"/>
       <c r="G23" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:33-40 (viewer icon has no @click); workers.html action gating.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:33-40 (viewer icon has no @click); workers.html action gating. | AUTOMATION: Pending - needs a VIEWER-role account (not yet provided).</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       <c r="F24" s="188" t="inlineStr"/>
       <c r="G24" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: program/utils.py:5-19; users/middleware.py:36-52.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: program/utils.py:5-19; users/middleware.py:36-52. | AUTOMATION: DEPRECATED - no standalone (non-program) opps exist; migrated to legacy program (Anshu 2026-09-04, pending Nitin confirm). Test skips.</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       <c r="F25" s="188" t="inlineStr"/>
       <c r="G25" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:455-459 (is_setup_complete guard).</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:455-459 (is_setup_complete guard). | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_23 (setup-incomplete opp redirects to Add Payment Units).</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       <c r="F28" s="188" t="inlineStr"/>
       <c r="G28" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:5,27,32,90.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:5,27,32,90. | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_26 (Test badge on an is_test opp; OLP Test opp).</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       <c r="F30" s="188" t="inlineStr"/>
       <c r="G30" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2646-2653, 2849-2852 (WorkerWorkAreaView 404).</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: views.py:2646-2653, 2849-2852 (WorkerWorkAreaView 404). | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_28 (MICROPLANNING opp: Work Area Assignments tab + work-areas URL 200; OLP Test opp).</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       <c r="F32" s="188" t="inlineStr"/>
       <c r="G32" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_delivery_stat.html:56-62; views.py:3150, 3223.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_delivery_stat.html:56-62; views.py:3150, 3223. | AUTOMATION: Pending/optional - needs deliveries+payments in last 24h; likely descoped (hard to keep fresh for automation).</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       <c r="F39" s="188" t="inlineStr"/>
       <c r="G39" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:40 (has_ended).</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_menu.html:40 (has_ended). | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_37 (Add Connect Workers hidden when Ended). Self-skips until the fixture opp's end date passes.</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       <c r="F45" s="188" t="inlineStr"/>
       <c r="G45" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: filters.py:135-137; views.py:2787-2788.</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: filters.py:135-137; views.py:2787-2788. | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_43 (auto-verify deliver-filter divergence; Demo Opp).</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -2723,7 +2723,7 @@
       <c r="F32" s="188" t="inlineStr"/>
       <c r="G32" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_delivery_stat.html:56-62; views.py:3150, 3223. | AUTOMATION: Pending/optional - needs deliveries+payments in last 24h; likely descoped (hard to keep fresh for automation).</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: opportunity_delivery_stat.html:56-62; views.py:3150, 3223. | AUTOMATION: DESCOPED (Anshu+Akanksha 2026-09-04) - the '24h increment' badge needs deliveries/payments submitted in the last 24h; no standalone web test can keep that fresh and no daily cadence exists. Proper home is inside the delivery-submitting E2E test (test_e2e_relearn_lifecycle): assert the badge right after it submits a visit. Fold in if prioritised.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -2445,7 +2445,7 @@
       <c r="F23" s="188" t="inlineStr"/>
       <c r="G23" s="189" t="inlineStr">
         <is>
-          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:33-40 (viewer icon has no @click); workers.html action gating. | AUTOMATION: Pending - needs a VIEWER-role account (not yet provided).</t>
+          <t>Added from source-derived gap analysis (2026-08-26), beyond documented OD_1-OD_19. Src: dashboard.html:33-40 (viewer icon has no @click); workers.html action gating. | AUTOMATION: Automated - PR #38, test_opd_gaps.py::test_opd_21 (VIEWER via direct Connect login - email/password, no HQ; loads a dashboard but cannot open the hamburger menu). Viewer creds in gitignored settings.cfg [viewer]; skips if absent.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -16479,7 +16479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="148" min="1" max="1"/>
@@ -19309,6 +19309,708 @@
       <c r="L52" s="171" t="inlineStr">
         <is>
           <t>Dev: add unit test</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-40</t>
+        </is>
+      </c>
+      <c r="B53" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C53" s="171" t="inlineStr">
+        <is>
+          <t>Verification tab-set is a function of mode x role: auto+PM=[All]; auto+NM=[Approved,Rejected,All]; manual+PM=[Pending PM Review,Disagree,Agree,All]; manual+NM=[Pending NM Review,Pending PM Review,Disagree,Agree,Rejected,All]. Tab labels are role-sensitive (agree='Agree'(PM)/'Approved'(NM); disagree='Disagree'(PM)/'Revalidate'(NM)). Src: VisitVerificationTableView.tabs + get_tab_display (views.py ~2355-2384).</t>
+        </is>
+      </c>
+      <c r="D53" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E53" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (WVV assumes a single tab set). Largest role/mode fork on the visit page.</t>
+        </is>
+      </c>
+      <c r="F53" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G53" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H53" s="171" t="inlineStr"/>
+      <c r="I53" s="171" t="inlineStr"/>
+      <c r="J53" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K53" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L53" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-41</t>
+        </is>
+      </c>
+      <c r="B54" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C54" s="171" t="inlineStr">
+        <is>
+          <t>WORKER_VISITS_TASKS waffle switch changes the whole visit table: ON -&gt; plain WorkerVisitTable (no review tabs, no bulk actions); OFF -&gt; tabbed VisitVerificationTable. Also gates the Visits/Tasks sub-tab bar on the worker profile. Src: visit_verification_table_view (~2436-2441); UserVisitVerificationView show_worker_tasks_tabs (~2190).</t>
+        </is>
+      </c>
+      <c r="D54" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E54" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP; a happy-path plan silently mismatches when the switch flips.</t>
+        </is>
+      </c>
+      <c r="F54" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G54" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H54" s="171" t="inlineStr"/>
+      <c r="I54" s="171" t="inlineStr"/>
+      <c r="J54" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K54" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L54" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-42</t>
+        </is>
+      </c>
+      <c r="B55" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C55" s="171" t="inlineStr">
+        <is>
+          <t>In-UI bulk Approve/Reject rules: max 100 visits per bulk op (400 'Maximum 100 visits allowed'); justification mandatory for flagged visits; reject requires a reason; disagree-&gt;pending; payment accrued recomputed. Src: approve_visits (~1062-1109) / reject_visits (~1116-1136).</t>
+        </is>
+      </c>
+      <c r="D55" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E55" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs SRC-W-24 (that covers the CSV import path, not the in-UI bulk limits/justification).</t>
+        </is>
+      </c>
+      <c r="F55" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G55" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H55" s="171" t="inlineStr"/>
+      <c r="I55" s="171" t="inlineStr"/>
+      <c r="J55" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K55" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L55" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-43</t>
+        </is>
+      </c>
+      <c r="B56" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C56" s="171" t="inlineStr">
+        <is>
+          <t>Bulk select + Approve All/Reject All controls are hidden for PM, for viewer, and under auto-verify; only a non-viewer NM on a manual-review opp sees them. The select checkbox column is invisible for PM. Src: user_visit_verification_table.html bulk button guards; UserVisitVerificationTable.__init__ select column (~915-917).</t>
+        </is>
+      </c>
+      <c r="D56" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E56" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP; role/mode gating of bulk actions.</t>
+        </is>
+      </c>
+      <c r="F56" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G56" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H56" s="171" t="inlineStr"/>
+      <c r="I56" s="171" t="inlineStr"/>
+      <c r="J56" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K56" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L56" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-44</t>
+        </is>
+      </c>
+      <c r="B57" s="171" t="inlineStr">
+        <is>
+          <t>Visit verification page</t>
+        </is>
+      </c>
+      <c r="C57" s="171" t="inlineStr">
+        <is>
+          <t>Individual visit-review action bar is role/mode gated: hidden entirely under auto-verify; PM sees Agree/Disagree (Disagree only when review pending; Agree disabled when already agree); NM sees Approve/Reject with enable/disable by status; all disabled for viewer. Src: user_visit_details.html action bar (~292-320); user_visit_review (~1547-1557).</t>
+        </is>
+      </c>
+      <c r="D57" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E57" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (WVV covers approve/reject happy path, not PM agree/disagree or gating).</t>
+        </is>
+      </c>
+      <c r="F57" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G57" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H57" s="171" t="inlineStr"/>
+      <c r="I57" s="171" t="inlineStr"/>
+      <c r="J57" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K57" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L57" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-45</t>
+        </is>
+      </c>
+      <c r="B58" s="171" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C58" s="171" t="inlineStr">
+        <is>
+          <t>Manual-verification endpoints (approve/reject/review/import-review/export-review) return HTTP 403 + HX-Trigger reload_table when the opportunity is auto-verify. Src: @require_manual_visit_verification (decorators.py ~6-27).</t>
+        </is>
+      </c>
+      <c r="D58" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E58" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP; mode-gating at endpoint level (negative test).</t>
+        </is>
+      </c>
+      <c r="F58" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G58" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H58" s="171" t="inlineStr"/>
+      <c r="I58" s="171" t="inlineStr"/>
+      <c r="J58" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K58" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L58" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-46</t>
+        </is>
+      </c>
+      <c r="B59" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C59" s="171" t="inlineStr">
+        <is>
+          <t>Worker profile KPI header: Total Visits, Pending Tasks (links to filtered tasks), Rejected Visits with per-flag rejection popup, Accrued Amount, Paid Amount with last-payment popup (only when a payment exists). Src: get_worker_kpi_context (~2125-2167) + worker_profile_kpi.html.</t>
+        </is>
+      </c>
+      <c r="D59" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E59" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (worker profile page KPIs not covered).</t>
+        </is>
+      </c>
+      <c r="F59" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G59" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H59" s="171" t="inlineStr"/>
+      <c r="I59" s="171" t="inlineStr"/>
+      <c r="J59" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K59" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L59" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-47</t>
+        </is>
+      </c>
+      <c r="B60" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C60" s="171" t="inlineStr">
+        <is>
+          <t>Viewer read-only + has_ended gating across worker tabs: Add Worker, Resend Invites, Delete Invites and Export buttons are disabled for viewers and when opportunity.has_ended; opportunity_user_invite redirects with an error when has_ended. Src: workers.html (~36-78); opportunity_user_invite (~1527-1530).</t>
+        </is>
+      </c>
+      <c r="D60" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E60" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (no viewer/role or has_ended gating cases).</t>
+        </is>
+      </c>
+      <c r="F60" s="171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G60" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H60" s="171" t="inlineStr"/>
+      <c r="I60" s="171" t="inlineStr"/>
+      <c r="J60" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K60" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L60" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-48</t>
+        </is>
+      </c>
+      <c r="B61" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C61" s="171" t="inlineStr">
+        <is>
+          <t>Suspend modal + edge cases: modal shows a reason textarea plus pending_completed_work_count / payment_accrued / pending_payment warnings; re-suspending an already-suspended worker is idempotent; the suspended-users list page renders a Revoke column only for PM. Src: user_status_card.html (~43-94); suspend_user (~1441-1443); suspended_users_list (~1470-1493).</t>
+        </is>
+      </c>
+      <c r="D61" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E61" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Connect_worker_07 (status only); modal content, re-suspend, suspended-list + PM-gated revoke not covered.</t>
+        </is>
+      </c>
+      <c r="F61" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G61" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H61" s="171" t="inlineStr"/>
+      <c r="I61" s="171" t="inlineStr"/>
+      <c r="J61" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K61" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L61" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-49</t>
+        </is>
+      </c>
+      <c r="B62" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C62" s="171" t="inlineStr">
+        <is>
+          <t>Work Area Assignments tab appears only under the MICROPLANNING flag; the 6th worker tab is absent when the flag is off and the direct /workers/work-areas/ URL 404s. Src: BaseWorkerListView.get() tab append (~2646-2653); WorkerWorkAreaView.dispatch 404 (~2849-2852).</t>
+        </is>
+      </c>
+      <c r="D62" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E62" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP (worker-tab gating by MICROPLANNING; distinct from MP import cases SRC-W-31..33).</t>
+        </is>
+      </c>
+      <c r="F62" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G62" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H62" s="171" t="inlineStr"/>
+      <c r="I62" s="171" t="inlineStr"/>
+      <c r="J62" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K62" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L62" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-50</t>
+        </is>
+      </c>
+      <c r="B63" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C63" s="171" t="inlineStr">
+        <is>
+          <t>Cross-tab filter persistence: filters set on a worker sub-tab are saved to session and re-applied when navigating between worker tabs, but cleared when the page is entered from an unrelated page (referer check). Src: BaseWorkerListView.get_tabs / _is_navigating_between_tabs (~2598-2642).</t>
+        </is>
+      </c>
+      <c r="D63" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E63" s="171" t="inlineStr">
+        <is>
+          <t>MISSING from MTP; easy-miss stateful behaviour.</t>
+        </is>
+      </c>
+      <c r="F63" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G63" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H63" s="171" t="inlineStr"/>
+      <c r="I63" s="171" t="inlineStr"/>
+      <c r="J63" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K63" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L63" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-51</t>
+        </is>
+      </c>
+      <c r="B64" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C64" s="171" t="inlineStr">
+        <is>
+          <t>Deliver-tab count-breakdown popups are lazy hx-get to worker_flag_counts (status/payment_unit_id/access_id); the endpoint adds a 'Duplicate' bucket when saved_completed_count&gt;1; the column-footer popup (no access_id) shows whole-opportunity totals; empty state 'No flagged visits'. Src: _render_flag_counts (~1610-1636); worker_flag_counts (~2910-2942); TotalFlagCountsColumn (~1456-1495).</t>
+        </is>
+      </c>
+      <c r="D64" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E64" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Delivery_tab_03/05/09 (per-worker breakdown only; footer/whole-opp popup + duplicate bucket + empty state not covered).</t>
+        </is>
+      </c>
+      <c r="F64" s="171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G64" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H64" s="171" t="inlineStr"/>
+      <c r="I64" s="171" t="inlineStr"/>
+      <c r="J64" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K64" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L64" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP + Automate (confirm w/ eng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="171" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-52</t>
+        </is>
+      </c>
+      <c r="B65" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C65" s="171" t="inlineStr">
+        <is>
+          <t>Payments tab specifics: only rows with payment_accrued&gt;=0 and accepted=True, ordered -payment_accrued; Accrued/Total Paid/Confirm headers are currency-code-suffixed and blank when no rows; footers sum accrued and total paid; last-paid history is a lazy popup ('--' when never paid); payment import is CSV/XLSX-only and cache-locked against concurrent imports. Src: WorkerPaymentsView (~2794-2820); WorkerPaymentsTable (~1173-1229); payment_import (~784-802).</t>
+        </is>
+      </c>
+      <c r="D65" s="171" t="inlineStr">
+        <is>
+          <t>🟡 Automatable - not yet done</t>
+        </is>
+      </c>
+      <c r="E65" s="171" t="inlineStr">
+        <is>
+          <t>PARTIAL vs Payment Processing_1-4 (info/pay/history/rollback happy path).</t>
+        </is>
+      </c>
+      <c r="F65" s="171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G65" s="171" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H65" s="171" t="inlineStr"/>
+      <c r="I65" s="171" t="inlineStr"/>
+      <c r="J65" s="171" t="inlineStr">
+        <is>
+          <t>Web pass 7: workers-page views/tables/filters/templates deep-dive (feature/workers-web-automation)</t>
+        </is>
+      </c>
+      <c r="K65" s="171" t="inlineStr">
+        <is>
+          <t>Eng-covered (logic) - QA e2e only if critical journey</t>
+        </is>
+      </c>
+      <c r="L65" s="171" t="inlineStr">
+        <is>
+          <t>Add to MTP only (eng-covered)</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G317"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -31763,6 +31763,265 @@
       <c r="G317" s="171" t="inlineStr">
         <is>
           <t>QA-owned (UI/e2e - eng cannot cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_17</t>
+        </is>
+      </c>
+      <c r="B318" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C318" s="171" t="inlineStr">
+        <is>
+          <t>Verify user can sort the workers list by clicking the header columns</t>
+        </is>
+      </c>
+      <c r="D318" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E318" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_list_view.py::test_connect_worker_17_sort_list_by_header</t>
+        </is>
+      </c>
+      <c r="F318" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G318" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="171" t="inlineStr">
+        <is>
+          <t>Delivery_tab_10</t>
+        </is>
+      </c>
+      <c r="B319" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C319" s="171" t="inlineStr">
+        <is>
+          <t>Verify Filters pop up modal is displayed by clicking the filters icon on the delivery tab</t>
+        </is>
+      </c>
+      <c r="D319" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E319" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_deliver_filters.py::test_delivery_tab_10_filter_modal_opens</t>
+        </is>
+      </c>
+      <c r="F319" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G319" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="171" t="inlineStr">
+        <is>
+          <t>Delivery_tab_11</t>
+        </is>
+      </c>
+      <c r="B320" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C320" s="171" t="inlineStr">
+        <is>
+          <t>Verify Last active filter dropdown contains the expected options (Any time / 1 / 3 / 7 days ago)</t>
+        </is>
+      </c>
+      <c r="D320" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E320" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_deliver_filters.py::test_delivery_tab_11_last_active_options</t>
+        </is>
+      </c>
+      <c r="F320" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G320" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="171" t="inlineStr">
+        <is>
+          <t>Delivery_tab_13</t>
+        </is>
+      </c>
+      <c r="B321" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C321" s="171" t="inlineStr">
+        <is>
+          <t>Verify Deliveries-with-flags filter dropdown contains the expected options (---------/Yes/No)</t>
+        </is>
+      </c>
+      <c r="D321" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E321" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_deliver_filters.py::test_delivery_tab_13_deliveries_with_flags_options</t>
+        </is>
+      </c>
+      <c r="F321" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G321" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="171" t="inlineStr">
+        <is>
+          <t>Delivery_tab_14</t>
+        </is>
+      </c>
+      <c r="B322" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C322" s="171" t="inlineStr">
+        <is>
+          <t>Verify Has-overlimit-deliveries filter dropdown contains the expected options (---------/Yes/No)</t>
+        </is>
+      </c>
+      <c r="D322" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E322" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_deliver_filters.py::test_delivery_tab_14_has_overlimit_options</t>
+        </is>
+      </c>
+      <c r="F322" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G322" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="171" t="inlineStr">
+        <is>
+          <t>Delivery_tab_16</t>
+        </is>
+      </c>
+      <c r="B323" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C323" s="171" t="inlineStr">
+        <is>
+          <t>Ensure all filter combinations are applied simultaneously and function correctly (badge counts them)</t>
+        </is>
+      </c>
+      <c r="D323" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E323" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_deliver_filters.py::test_delivery_tab_16_filter_combination_applies</t>
+        </is>
+      </c>
+      <c r="F323" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G323" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="171" t="inlineStr">
+        <is>
+          <t>Payment Processing_2</t>
+        </is>
+      </c>
+      <c r="B324" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C324" s="171" t="inlineStr">
+        <is>
+          <t>Confirm user sees a message when a payment is made (covered via the import-confirmation path; confirm "Pay button" wording w/ product)</t>
+        </is>
+      </c>
+      <c r="D324" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E324" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_payments.py::test_payment_processing_01_02_03_04</t>
+        </is>
+      </c>
+      <c r="F324" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch A/B (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G324" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:G325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32020,6 +32020,43 @@
         </is>
       </c>
       <c r="G324" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="171" t="inlineStr">
+        <is>
+          <t>Learn_tab_04</t>
+        </is>
+      </c>
+      <c r="B325" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C325" s="171" t="inlineStr">
+        <is>
+          <t>Verify Assessment status is shown as Passed when a worker passes the assessment (100% modules, attempts + completed learning present)</t>
+        </is>
+      </c>
+      <c r="D325" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E325" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_list_view.py::test_learn_tab_04_assessment_passed</t>
+        </is>
+      </c>
+      <c r="F325" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch D probe (feature/workers-web-automation, 2026-09-09)</t>
+        </is>
+      </c>
+      <c r="G325" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G325"/>
+  <dimension ref="A1:G327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32057,6 +32057,80 @@
         </is>
       </c>
       <c r="G325" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_02</t>
+        </is>
+      </c>
+      <c r="B326" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C326" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is able to see the status as invite pending until the invitation is accepted</t>
+        </is>
+      </c>
+      <c r="D326" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E326" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_invites.py::test_connect_worker_02_pending_invite_status</t>
+        </is>
+      </c>
+      <c r="F326" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C phase 1 (feature/workers-web-automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G326" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_03</t>
+        </is>
+      </c>
+      <c r="B327" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C327" s="171" t="inlineStr">
+        <is>
+          <t>Verify resend/delete invite buttons are enabled only when the user selects the invites</t>
+        </is>
+      </c>
+      <c r="D327" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E327" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_invites.py::test_connect_worker_03_resend_delete_gated_by_selection</t>
+        </is>
+      </c>
+      <c r="F327" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C phase 1 (feature/workers-web-automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G327" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G327"/>
+  <dimension ref="A1:G330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32131,6 +32131,117 @@
         </is>
       </c>
       <c r="G327" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_05</t>
+        </is>
+      </c>
+      <c r="B328" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C328" s="171" t="inlineStr">
+        <is>
+          <t>Verify we are able to pre-invite a worker that is not registered for Personal ID yet</t>
+        </is>
+      </c>
+      <c r="D328" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E328" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_invites.py::test_connect_worker_05_12_08_invite_resend_delete</t>
+        </is>
+      </c>
+      <c r="F328" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C phase 2 (feature/workers-web-automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G328" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_08</t>
+        </is>
+      </c>
+      <c r="B329" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C329" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is able to delete the pending invites</t>
+        </is>
+      </c>
+      <c r="D329" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E329" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_invites.py::test_connect_worker_05_12_08_invite_resend_delete</t>
+        </is>
+      </c>
+      <c r="F329" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C phase 2 (feature/workers-web-automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G329" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_12</t>
+        </is>
+      </c>
+      <c r="B330" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C330" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is not able to resend the invite for not-found (unregistered) users (skipped with a naming message)</t>
+        </is>
+      </c>
+      <c r="D330" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E330" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_invites.py::test_connect_worker_05_12_08_invite_resend_delete</t>
+        </is>
+      </c>
+      <c r="F330" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C phase 2 (feature/workers-web-automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G330" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G330"/>
+  <dimension ref="A1:G332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32242,6 +32242,80 @@
         </is>
       </c>
       <c r="G330" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_04</t>
+        </is>
+      </c>
+      <c r="B331" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C331" s="171" t="inlineStr">
+        <is>
+          <t>Verify worker status is updated to invite accepted when the invitation is accepted</t>
+        </is>
+      </c>
+      <c r="D331" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E331" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_04_accepted_status</t>
+        </is>
+      </c>
+      <c r="F331" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C seeded data (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G331" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="171" t="inlineStr">
+        <is>
+          <t>Learn_tab_03</t>
+        </is>
+      </c>
+      <c r="B332" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C332" s="171" t="inlineStr">
+        <is>
+          <t>Verify Assessment status is shown as Failed when the worker fails the assessment</t>
+        </is>
+      </c>
+      <c r="D332" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E332" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_learn_tab_03_assessment_failed</t>
+        </is>
+      </c>
+      <c r="F332" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C seeded data (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G332" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G332"/>
+  <dimension ref="A1:G335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32316,6 +32316,117 @@
         </is>
       </c>
       <c r="G332" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_10</t>
+        </is>
+      </c>
+      <c r="B333" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C333" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is able to resend the invite for invite-pending workers (Successfully resent)</t>
+        </is>
+      </c>
+      <c r="D333" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E333" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_10_resend_allowed_for_pending</t>
+        </is>
+      </c>
+      <c r="F333" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C seeded data (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G333" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_11</t>
+        </is>
+      </c>
+      <c r="B334" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C334" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is not able to resend the invite for accepted workers (skipped - already accepted)</t>
+        </is>
+      </c>
+      <c r="D334" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E334" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_11_resend_skipped_for_accepted</t>
+        </is>
+      </c>
+      <c r="F334" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C seeded data (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G334" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_14</t>
+        </is>
+      </c>
+      <c r="B335" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C335" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is not able to resend the invite for suspended users (skipped)</t>
+        </is>
+      </c>
+      <c r="D335" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E335" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_14_resend_skipped_for_suspended</t>
+        </is>
+      </c>
+      <c r="F335" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C seeded data (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G335" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -20025,7 +20025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G335"/>
+  <dimension ref="A1:G336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32427,6 +32427,43 @@
         </is>
       </c>
       <c r="G335" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_15</t>
+        </is>
+      </c>
+      <c r="B336" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C336" s="171" t="inlineStr">
+        <is>
+          <t>Verify appropriate messages are displayed when the user bulk-resends invites to a mix of worker types (accepted/suspended skipped, pending resent)</t>
+        </is>
+      </c>
+      <c r="D336" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E336" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_15_bulk_resend_messages</t>
+        </is>
+      </c>
+      <c r="F336" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C seeded data (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G336" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -464,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -971,6 +971,9 @@
     <xf numFmtId="0" fontId="31" fillId="23" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3364,7 +3367,11 @@
       </c>
       <c r="E3" s="66" t="n"/>
       <c r="F3" s="80" t="n"/>
-      <c r="G3" s="80" t="n"/>
+      <c r="G3" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_01_02_03 (migration)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="73" t="n"/>
@@ -3408,7 +3415,11 @@
       </c>
       <c r="E5" s="66" t="n"/>
       <c r="F5" s="85" t="n"/>
-      <c r="G5" s="85" t="n"/>
+      <c r="G5" s="88" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_invites.py::test_connect_worker_02_pending_invite_status</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="73" t="inlineStr">
@@ -3436,7 +3447,11 @@
       </c>
       <c r="E6" s="66" t="n"/>
       <c r="F6" s="80" t="n"/>
-      <c r="G6" s="80" t="n"/>
+      <c r="G6" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_invites.py::test_connect_worker_03_resend_delete_gated_by_selection</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="73" t="inlineStr">
@@ -3457,7 +3472,11 @@
       </c>
       <c r="E7" s="66" t="n"/>
       <c r="F7" s="104" t="n"/>
-      <c r="G7" s="104" t="n"/>
+      <c r="G7" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_connect_worker_04_accepted_status (Worker_Lifecycle_Automation)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="73" t="inlineStr">
@@ -3487,7 +3506,11 @@
       </c>
       <c r="E8" s="66" t="n"/>
       <c r="F8" s="104" t="n"/>
-      <c r="G8" s="80" t="n"/>
+      <c r="G8" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_invites.py::test_connect_worker_05_12_08_invite_resend_delete</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="73" t="inlineStr">
@@ -3517,7 +3540,11 @@
       </c>
       <c r="E9" s="66" t="n"/>
       <c r="F9" s="104" t="n"/>
-      <c r="G9" s="80" t="n"/>
+      <c r="G9" s="68" t="inlineStr">
+        <is>
+          <t>⏳ Not automated - not-found "mobile under Name" resolves asynchronously (SMS delivery callback); a freshly-invited number shows "—". Needs a resolved not-found worker seeded (requested from data setup).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="73" t="inlineStr">
@@ -3546,7 +3573,11 @@
       </c>
       <c r="E10" s="66" t="n"/>
       <c r="F10" s="85" t="n"/>
-      <c r="G10" s="85" t="n"/>
+      <c r="G10" s="88" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_connect_worker_07_suspended_status (+ suspend/revoke action in test_worker_visit_verification.py)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="73" t="inlineStr">
@@ -3576,7 +3607,11 @@
       </c>
       <c r="E11" s="66" t="n"/>
       <c r="F11" s="85" t="n"/>
-      <c r="G11" s="85" t="n"/>
+      <c r="G11" s="88" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_invites.py::test_connect_worker_05_12_08_invite_resend_delete</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
@@ -3605,7 +3640,11 @@
       </c>
       <c r="E12" s="66" t="n"/>
       <c r="F12" s="85" t="n"/>
-      <c r="G12" s="85" t="n"/>
+      <c r="G12" s="88" t="inlineStr">
+        <is>
+          <t>🔴 Manual only - demo/reserved numbers do NOT enforce the 24h resend cooldown (per data setup); needs a real number to verify.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="73" t="inlineStr">
@@ -3634,7 +3673,11 @@
       </c>
       <c r="E13" s="66" t="n"/>
       <c r="F13" s="80" t="n"/>
-      <c r="G13" s="85" t="n"/>
+      <c r="G13" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_connect_worker_10_resend_allowed_for_pending</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="73" t="inlineStr">
@@ -3664,7 +3707,11 @@
       </c>
       <c r="E14" s="66" t="n"/>
       <c r="F14" s="85" t="n"/>
-      <c r="G14" s="85" t="n"/>
+      <c r="G14" s="88" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_connect_worker_11_resend_skipped_for_accepted</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
@@ -3693,7 +3740,11 @@
       </c>
       <c r="E15" s="66" t="n"/>
       <c r="F15" s="85" t="n"/>
-      <c r="G15" s="85" t="n"/>
+      <c r="G15" s="88" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_invites.py::test_connect_worker_05_12_08_invite_resend_delete</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="73" t="inlineStr">
@@ -3722,7 +3773,11 @@
       </c>
       <c r="E16" s="66" t="n"/>
       <c r="F16" s="85" t="n"/>
-      <c r="G16" s="85" t="n"/>
+      <c r="G16" s="88" t="inlineStr">
+        <is>
+          <t>⏳ Not automated - delete not-found shares the async not-found dependency as _06; needs a resolved not-found worker seeded.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="73" t="inlineStr">
@@ -3752,7 +3807,11 @@
       </c>
       <c r="E17" s="66" t="n"/>
       <c r="F17" s="85" t="n"/>
-      <c r="G17" s="85" t="n"/>
+      <c r="G17" s="88" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_connect_worker_14_resend_skipped_for_suspended</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="73" t="inlineStr">
@@ -3785,7 +3844,11 @@
       </c>
       <c r="E18" s="66" t="n"/>
       <c r="F18" s="104" t="n"/>
-      <c r="G18" s="104" t="n"/>
+      <c r="G18" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_connect_worker_15_bulk_resend_messages</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="73" t="inlineStr">
@@ -3816,7 +3879,11 @@
       </c>
       <c r="E19" s="66" t="n"/>
       <c r="F19" s="104" t="n"/>
-      <c r="G19" s="104" t="n"/>
+      <c r="G19" s="118" t="inlineStr">
+        <is>
+          <t>⏸ Deferred - bulk delete across all types would delete the seeded pending/accepted workers (destructive). Not automated to protect the seed.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="73" t="inlineStr">
@@ -3849,7 +3916,11 @@
       </c>
       <c r="E20" s="66" t="n"/>
       <c r="F20" s="80" t="n"/>
-      <c r="G20" s="80" t="n"/>
+      <c r="G20" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_connect_worker_17_sort_list_by_header</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="12.75" customHeight="1" s="148">
       <c r="A21" s="76" t="n"/>
@@ -3896,7 +3967,11 @@
       </c>
       <c r="E22" s="66" t="n"/>
       <c r="F22" s="80" t="n"/>
-      <c r="G22" s="80" t="n"/>
+      <c r="G22" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_01_02_03 (migration)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="73" t="inlineStr">
@@ -3924,7 +3999,11 @@
       </c>
       <c r="E23" s="66" t="n"/>
       <c r="F23" s="80" t="n"/>
-      <c r="G23" s="80" t="n"/>
+      <c r="G23" s="68" t="inlineStr">
+        <is>
+          <t>🔴 Not automated (web) - requires a mobile learn-app submission during the test; web-only cannot drive it.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="73" t="inlineStr">
@@ -3952,7 +4031,11 @@
       </c>
       <c r="E24" s="66" t="n"/>
       <c r="F24" s="80" t="n"/>
-      <c r="G24" s="80" t="n"/>
+      <c r="G24" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_lifecycle.py::test_learn_tab_03_assessment_failed (Map_09)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="73" t="inlineStr">
@@ -3980,7 +4063,11 @@
       </c>
       <c r="E25" s="66" t="n"/>
       <c r="F25" s="80" t="n"/>
-      <c r="G25" s="80" t="n"/>
+      <c r="G25" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_learn_tab_04_assessment_passed</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="12.75" customHeight="1" s="148">
       <c r="A26" s="76" t="n"/>
@@ -4021,7 +4108,11 @@
       </c>
       <c r="E27" s="66" t="n"/>
       <c r="F27" s="80" t="n"/>
-      <c r="G27" s="80" t="n"/>
+      <c r="G27" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_01_02_03 (Deliver tab, migration)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="73" t="inlineStr">
@@ -4051,7 +4142,11 @@
       </c>
       <c r="E28" s="66" t="n"/>
       <c r="F28" s="80" t="n"/>
-      <c r="G28" s="80" t="n"/>
+      <c r="G28" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_01_02_03 (deliver headers)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="73" t="inlineStr">
@@ -4083,7 +4178,11 @@
       </c>
       <c r="E29" s="66" t="n"/>
       <c r="F29" s="80" t="n"/>
-      <c r="G29" s="80" t="n"/>
+      <c r="G29" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_04_worker_status_count_breakdown (Delivered)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="73" t="inlineStr">
@@ -4112,7 +4211,11 @@
       </c>
       <c r="E30" s="66" t="n"/>
       <c r="F30" s="80" t="n"/>
-      <c r="G30" s="80" t="n"/>
+      <c r="G30" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_04/05 (Approved breakdown)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="73" t="inlineStr">
@@ -4141,7 +4244,11 @@
       </c>
       <c r="E31" s="66" t="n"/>
       <c r="F31" s="80" t="n"/>
-      <c r="G31" s="80" t="n"/>
+      <c r="G31" s="190" t="inlineStr">
+        <is>
+          <t>⏸ Deferred - delivery-completion logic (1 visit per payment unit); eng-covered, needs controlled visit data.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
@@ -4170,7 +4277,11 @@
       </c>
       <c r="E32" s="66" t="n"/>
       <c r="F32" s="80" t="n"/>
-      <c r="G32" s="80" t="n"/>
+      <c r="G32" s="68" t="inlineStr">
+        <is>
+          <t>⏸ Deferred - delivery-completion rule (required + optional approved); eng-covered, needs controlled visit data.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="73" t="inlineStr">
@@ -4204,7 +4315,11 @@
       </c>
       <c r="E33" s="66" t="n"/>
       <c r="F33" s="80" t="n"/>
-      <c r="G33" s="80" t="n"/>
+      <c r="G33" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_list_view.py::test_wlv_04/05 (Rejected breakdown)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="73" t="inlineStr">
@@ -4241,7 +4356,11 @@
       </c>
       <c r="E34" s="66" t="n"/>
       <c r="F34" s="104" t="n"/>
-      <c r="G34" s="80" t="n"/>
+      <c r="G34" s="68" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_deliver_filters.py::test_delivery_tab_10_filter_modal_opens</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="73" t="inlineStr">
@@ -4278,7 +4397,11 @@
       </c>
       <c r="E35" s="66" t="n"/>
       <c r="F35" s="104" t="n"/>
-      <c r="G35" s="104" t="n"/>
+      <c r="G35" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_deliver_filters.py::test_delivery_tab_11_last_active_options</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="73" t="inlineStr">
@@ -4311,7 +4434,11 @@
       </c>
       <c r="E36" s="66" t="n"/>
       <c r="F36" s="104" t="n"/>
-      <c r="G36" s="104" t="n"/>
+      <c r="G36" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_deliver_filters.py::test_delivery_tab_13_deliveries_with_flags_options</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="73" t="inlineStr">
@@ -4344,7 +4471,11 @@
       </c>
       <c r="E37" s="66" t="n"/>
       <c r="F37" s="104" t="n"/>
-      <c r="G37" s="104" t="n"/>
+      <c r="G37" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_deliver_filters.py::test_delivery_tab_14_has_overlimit_options</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="73" t="inlineStr">
@@ -4374,7 +4505,11 @@
       </c>
       <c r="E38" s="66" t="n"/>
       <c r="F38" s="104" t="n"/>
-      <c r="G38" s="104" t="n"/>
+      <c r="G38" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_deliver_filters.py::test_delivery_tab_16_filter_combination_applies</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="12.75" customHeight="1" s="148">
       <c r="A39" s="76" t="n"/>
@@ -4419,6 +4554,11 @@
         </is>
       </c>
       <c r="E40" s="66" t="n"/>
+      <c r="G40" s="83" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_payments.py::test_payment_processing_01_02_03_04</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="82" t="inlineStr">
@@ -4438,6 +4578,11 @@
         </is>
       </c>
       <c r="E41" s="66" t="n"/>
+      <c r="G41" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_payments.py (import-confirmation path)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="82" t="inlineStr">
@@ -4469,6 +4614,11 @@
         </is>
       </c>
       <c r="E42" s="66" t="n"/>
+      <c r="G42" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_payments.py (last-paid history popup)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="82" t="inlineStr">
@@ -4498,6 +4648,11 @@
         </is>
       </c>
       <c r="E43" s="66" t="n"/>
+      <c r="G43" s="118" t="inlineStr">
+        <is>
+          <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_payments.py (rollback)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -464,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -974,6 +974,9 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3273,7 +3276,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="23.63" customWidth="1" style="148" min="1" max="1"/>
@@ -4651,6 +4654,153 @@
       <c r="G43" s="118" t="inlineStr">
         <is>
           <t>✅ Automated (Playwright, feature/workers-web-automation): test_worker_payments.py (rollback)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-46</t>
+        </is>
+      </c>
+      <c r="B44" s="118" t="inlineStr">
+        <is>
+          <t>Worker profile KPI header: Total Visits, Pending Tasks (links to filtered tasks), Rejected Visits with per-flag rejection popup, Accrued Amount, Paid Amount with last-payment popup (only when a payment exists). Src: get_worker_kpi_context (~2125-2167) + worker_profile_kpi.html.</t>
+        </is>
+      </c>
+      <c r="C44" s="118" t="inlineStr"/>
+      <c r="D44" s="118" t="inlineStr"/>
+      <c r="E44" s="66" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-46.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-47</t>
+        </is>
+      </c>
+      <c r="B45" s="118" t="inlineStr">
+        <is>
+          <t>Viewer read-only + has_ended gating across worker tabs: Add Worker, Resend Invites, Delete Invites and Export buttons are disabled for viewers and when opportunity.has_ended; opportunity_user_invite redirects with an error when has_ended. Src: workers.html (~36-78); opportunity_user_invite (~1527-1530).</t>
+        </is>
+      </c>
+      <c r="C45" s="118" t="inlineStr"/>
+      <c r="D45" s="118" t="inlineStr"/>
+      <c r="E45" s="66" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-47.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-48</t>
+        </is>
+      </c>
+      <c r="B46" s="118" t="inlineStr">
+        <is>
+          <t>Suspend modal + edge cases: modal shows a reason textarea plus pending_completed_work_count / payment_accrued / pending_payment warnings; re-suspending an already-suspended worker is idempotent; the suspended-users list page renders a Revoke column only for PM. Src: user_status_card.html (~43-94); suspend_user (~1441-1443); suspended_users_list (~1470-1493).</t>
+        </is>
+      </c>
+      <c r="C46" s="118" t="inlineStr"/>
+      <c r="D46" s="118" t="inlineStr"/>
+      <c r="E46" s="66" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-48.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-49</t>
+        </is>
+      </c>
+      <c r="B47" s="118" t="inlineStr">
+        <is>
+          <t>Work Area Assignments tab appears only under the MICROPLANNING flag; the 6th worker tab is absent when the flag is off and the direct /workers/work-areas/ URL 404s. Src: BaseWorkerListView.get() tab append (~2646-2653); WorkerWorkAreaView.dispatch 404 (~2849-2852).</t>
+        </is>
+      </c>
+      <c r="C47" s="118" t="inlineStr"/>
+      <c r="D47" s="118" t="inlineStr"/>
+      <c r="E47" s="66" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-49.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-50</t>
+        </is>
+      </c>
+      <c r="B48" s="118" t="inlineStr">
+        <is>
+          <t>Cross-tab filter persistence: filters set on a worker sub-tab are saved to session and re-applied when navigating between worker tabs, but cleared when the page is entered from an unrelated page (referer check). Src: BaseWorkerListView.get_tabs / _is_navigating_between_tabs (~2598-2642).</t>
+        </is>
+      </c>
+      <c r="C48" s="118" t="inlineStr"/>
+      <c r="D48" s="118" t="inlineStr"/>
+      <c r="E48" s="66" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-51</t>
+        </is>
+      </c>
+      <c r="B49" s="118" t="inlineStr">
+        <is>
+          <t>Deliver-tab count-breakdown popups are lazy hx-get to worker_flag_counts (status/payment_unit_id/access_id); the endpoint adds a 'Duplicate' bucket when saved_completed_count&gt;1; the column-footer popup (no access_id) shows whole-opportunity totals; empty state 'No flagged visits'. Src: _render_flag_counts (~1610-1636); worker_flag_counts (~2910-2942); TotalFlagCountsColumn (~1456-1495).</t>
+        </is>
+      </c>
+      <c r="C49" s="118" t="inlineStr"/>
+      <c r="D49" s="118" t="inlineStr"/>
+      <c r="E49" s="66" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-51.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="82" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-52</t>
+        </is>
+      </c>
+      <c r="B50" s="118" t="inlineStr">
+        <is>
+          <t>Payments tab specifics: only rows with payment_accrued&gt;=0 and accepted=True, ordered -payment_accrued; Accrued/Total Paid/Confirm headers are currency-code-suffixed and blank when no rows; footers sum accrued and total paid; last-paid history is a lazy popup ('--' when never paid); payment import is CSV/XLSX-only and cache-locked against concurrent imports. Src: WorkerPaymentsView (~2794-2820); WorkerPaymentsTable (~1173-1229); payment_import (~784-802).</t>
+        </is>
+      </c>
+      <c r="C50" s="118" t="inlineStr"/>
+      <c r="D50" s="118" t="inlineStr"/>
+      <c r="E50" s="66" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" s="118" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Low. Action: Add to MTP only (eng-covered). Source: Gap Analysis GAP-SRC-W-52.</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4841,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.25" customWidth="1" style="148" min="1" max="1"/>
@@ -6054,13 +6204,130 @@
       <c r="G46" s="73" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="58" t="n"/>
-      <c r="B47" s="88" t="n"/>
-      <c r="C47" s="88" t="n"/>
-      <c r="D47" s="68" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="89" t="n"/>
-      <c r="G47" s="89" t="n"/>
+      <c r="A47" s="58" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-40</t>
+        </is>
+      </c>
+      <c r="B47" s="104" t="inlineStr">
+        <is>
+          <t>Verification tab-set is a function of mode x role: auto+PM=[All]; auto+NM=[Approved,Rejected,All]; manual+PM=[Pending PM Review,Disagree,Agree,All]; manual+NM=[Pending NM Review,Pending PM Review,Disagree,Agree,Rejected,All]. Tab labels are role-sensitive (agree='Agree'(PM)/'Approved'(NM); disagree='Disagree'(PM)/'Revalidate'(NM)). Src: VisitVerificationTableView.tabs + get_tab_display (views.py ~2355-2384).</t>
+        </is>
+      </c>
+      <c r="C47" s="104" t="inlineStr"/>
+      <c r="D47" s="80" t="inlineStr"/>
+      <c r="E47" s="66" t="inlineStr"/>
+      <c r="F47" s="73" t="inlineStr"/>
+      <c r="G47" s="73" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="191" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-41</t>
+        </is>
+      </c>
+      <c r="B48" s="104" t="inlineStr">
+        <is>
+          <t>WORKER_VISITS_TASKS waffle switch changes the whole visit table: ON -&gt; plain WorkerVisitTable (no review tabs, no bulk actions); OFF -&gt; tabbed VisitVerificationTable. Also gates the Visits/Tasks sub-tab bar on the worker profile. Src: visit_verification_table_view (~2436-2441); UserVisitVerificationView show_worker_tasks_tabs (~2190).</t>
+        </is>
+      </c>
+      <c r="C48" s="104" t="inlineStr"/>
+      <c r="D48" s="104" t="inlineStr"/>
+      <c r="E48" s="66" t="inlineStr"/>
+      <c r="F48" s="73" t="inlineStr"/>
+      <c r="G48" s="73" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-41.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="191" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-42</t>
+        </is>
+      </c>
+      <c r="B49" s="104" t="inlineStr">
+        <is>
+          <t>In-UI bulk Approve/Reject rules: max 100 visits per bulk op (400 'Maximum 100 visits allowed'); justification mandatory for flagged visits; reject requires a reason; disagree-&gt;pending; payment accrued recomputed. Src: approve_visits (~1062-1109) / reject_visits (~1116-1136).</t>
+        </is>
+      </c>
+      <c r="C49" s="104" t="inlineStr"/>
+      <c r="D49" s="104" t="inlineStr"/>
+      <c r="E49" s="66" t="inlineStr"/>
+      <c r="F49" s="73" t="inlineStr"/>
+      <c r="G49" s="73" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-42.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="191" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-43</t>
+        </is>
+      </c>
+      <c r="B50" s="104" t="inlineStr">
+        <is>
+          <t>Bulk select + Approve All/Reject All controls are hidden for PM, for viewer, and under auto-verify; only a non-viewer NM on a manual-review opp sees them. The select checkbox column is invisible for PM. Src: user_visit_verification_table.html bulk button guards; UserVisitVerificationTable.__init__ select column (~915-917).</t>
+        </is>
+      </c>
+      <c r="C50" s="104" t="inlineStr"/>
+      <c r="D50" s="104" t="inlineStr"/>
+      <c r="E50" s="66" t="inlineStr"/>
+      <c r="F50" s="73" t="inlineStr"/>
+      <c r="G50" s="73" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-43.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="191" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-44</t>
+        </is>
+      </c>
+      <c r="B51" s="104" t="inlineStr">
+        <is>
+          <t>Individual visit-review action bar is role/mode gated: hidden entirely under auto-verify; PM sees Agree/Disagree (Disagree only when review pending; Agree disabled when already agree); NM sees Approve/Reject with enable/disable by status; all disabled for viewer. Src: user_visit_details.html action bar (~292-320); user_visit_review (~1547-1557).</t>
+        </is>
+      </c>
+      <c r="C51" s="104" t="inlineStr"/>
+      <c r="D51" s="104" t="inlineStr"/>
+      <c r="E51" s="66" t="inlineStr"/>
+      <c r="F51" s="73" t="inlineStr"/>
+      <c r="G51" s="73" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-44.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="191" t="inlineStr">
+        <is>
+          <t>GAP-SRC-W-45</t>
+        </is>
+      </c>
+      <c r="B52" s="104" t="inlineStr">
+        <is>
+          <t>Manual-verification endpoints (approve/reject/review/import-review/export-review) return HTTP 403 + HX-Trigger reload_table when the opportunity is auto-verify. Src: @require_manual_visit_verification (decorators.py ~6-27).</t>
+        </is>
+      </c>
+      <c r="C52" s="104" t="inlineStr"/>
+      <c r="D52" s="104" t="inlineStr"/>
+      <c r="E52" s="66" t="inlineStr"/>
+      <c r="F52" s="73" t="inlineStr"/>
+      <c r="G52" s="73" t="inlineStr">
+        <is>
+          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-45.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -4671,10 +4671,10 @@
       <c r="C44" s="118" t="inlineStr"/>
       <c r="D44" s="118" t="inlineStr"/>
       <c r="E44" s="66" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" s="0" t="inlineStr"/>
       <c r="G44" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-46.</t>
+          <t>✅ Automated (Playwright): test_worker_gaps.py::test_src_w_46_worker_profile_kpis</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       <c r="C45" s="118" t="inlineStr"/>
       <c r="D45" s="118" t="inlineStr"/>
       <c r="E45" s="66" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" s="0" t="inlineStr"/>
       <c r="G45" s="118" t="inlineStr">
         <is>
           <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-47.</t>
@@ -4713,7 +4713,7 @@
       <c r="C46" s="118" t="inlineStr"/>
       <c r="D46" s="118" t="inlineStr"/>
       <c r="E46" s="66" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" s="0" t="inlineStr"/>
       <c r="G46" s="118" t="inlineStr">
         <is>
           <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-48.</t>
@@ -4734,10 +4734,10 @@
       <c r="C47" s="118" t="inlineStr"/>
       <c r="D47" s="118" t="inlineStr"/>
       <c r="E47" s="66" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" s="0" t="inlineStr"/>
       <c r="G47" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-49.</t>
+          <t>✅ Automated (positive - tab present + reachable under MICROPLANNING): test_worker_gaps.py::test_src_w_49_work_area_tab_present. Off-state (absent + 404) needs a non-microplanning opp.</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       <c r="C48" s="118" t="inlineStr"/>
       <c r="D48" s="118" t="inlineStr"/>
       <c r="E48" s="66" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" s="0" t="inlineStr"/>
       <c r="G48" s="118" t="inlineStr">
         <is>
           <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-50.</t>
@@ -4776,7 +4776,7 @@
       <c r="C49" s="118" t="inlineStr"/>
       <c r="D49" s="118" t="inlineStr"/>
       <c r="E49" s="66" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" s="0" t="inlineStr"/>
       <c r="G49" s="118" t="inlineStr">
         <is>
           <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-51.</t>
@@ -4797,10 +4797,10 @@
       <c r="C50" s="118" t="inlineStr"/>
       <c r="D50" s="118" t="inlineStr"/>
       <c r="E50" s="66" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" s="0" t="inlineStr"/>
       <c r="G50" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Low. Action: Add to MTP only (eng-covered). Source: Gap Analysis GAP-SRC-W-52.</t>
+          <t>✅ Automated (partial - currency-suffixed headers): test_worker_gaps.py::test_src_w_52_payments_currency_headers. Footer sums / import cache-lock eng-covered.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -4758,7 +4758,7 @@
       <c r="F48" s="0" t="inlineStr"/>
       <c r="G48" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-50.</t>
+          <t>✅ Automated (Playwright): test_worker_gaps.py::test_src_w_50_cross_tab_filter_persistence</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -4695,7 +4695,7 @@
       <c r="F45" s="0" t="inlineStr"/>
       <c r="G45" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: High. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-47.</t>
+          <t>✅ Automated (viewer half - Add Worker gated for a viewer): test_worker_gaps.py::test_src_w_47_viewer_read_only_gating. has_ended half needs an ended opp.</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       <c r="F46" s="0" t="inlineStr"/>
       <c r="G46" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-48.</t>
+          <t>✅ Automated (suspended-users list Revoke column + listing): test_worker_gaps.py::test_src_w_48_suspended_users_list. Suspend-modal content + re-suspend idempotency deferred (modal path).</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       <c r="F49" s="0" t="inlineStr"/>
       <c r="G49" s="118" t="inlineStr">
         <is>
-          <t>Not automated (proposed, gap-derived). Priority: Medium. Action: Add to MTP + Automate (confirm w/ eng). Source: Gap Analysis GAP-SRC-W-51.</t>
+          <t>✅ Covered by WLV_4/WLV_5 count-breakdown popups (test_worker_list_view.py per-worker + Total/footer). Duplicate bucket + "No flagged visits" empty state need specific data - deferred.</t>
         </is>
       </c>
     </row>

--- a/test_plans/CCC_Web_Platform_MTP.xlsx
+++ b/test_plans/CCC_Web_Platform_MTP.xlsx
@@ -3545,7 +3545,7 @@
       <c r="F9" s="104" t="n"/>
       <c r="G9" s="68" t="inlineStr">
         <is>
-          <t>⏳ Not automated - not-found "mobile under Name" resolves asynchronously (SMS delivery callback); a freshly-invited number shows "—". Needs a resolved not-found worker seeded (requested from data setup).</t>
+          <t>✅ Automated (Playwright): test_worker_lifecycle.py::test_connect_worker_06_not_found_display (seeded not-found +74261291230, status "User not found", "—" under Name).</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       <c r="F12" s="85" t="n"/>
       <c r="G12" s="88" t="inlineStr">
         <is>
-          <t>🔴 Manual only - demo/reserved numbers do NOT enforce the 24h resend cooldown (per data setup); needs a real number to verify.</t>
+          <t>✅ Automated (Playwright): test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown (real number +919000696488 -&gt; "sent in the last 24 hours"). NOTE: relies on the invite staying &lt;24h old; refresh if it flips.</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       <c r="F16" s="85" t="n"/>
       <c r="G16" s="88" t="inlineStr">
         <is>
-          <t>⏳ Not automated - delete not-found shares the async not-found dependency as _06; needs a resolved not-found worker seeded.</t>
+          <t>✅ Automated (Playwright): test_worker_lifecycle.py::test_connect_worker_13_not_found_deletable (Delete affordance on the seeded not-found user; not executed to preserve the seed).</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G336"/>
+  <dimension ref="A1:G339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="148" min="1" max="1"/>
@@ -32886,6 +32886,117 @@
         </is>
       </c>
       <c r="G336" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_06</t>
+        </is>
+      </c>
+      <c r="B337" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C337" s="171" t="inlineStr">
+        <is>
+          <t>Verify a not-found (unregistered) user shows "User not found" with no name - only the mobile number</t>
+        </is>
+      </c>
+      <c r="D337" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E337" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_06_not_found_display</t>
+        </is>
+      </c>
+      <c r="F337" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C - Anshu data 2 (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G337" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_09</t>
+        </is>
+      </c>
+      <c r="B338" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C338" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is not able to resend the invite within 24h (cooldown) - real number</t>
+        </is>
+      </c>
+      <c r="D338" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E338" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_09_resend_cooldown</t>
+        </is>
+      </c>
+      <c r="F338" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C - Anshu data 2 (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G338" s="171" t="inlineStr">
+        <is>
+          <t>Already automated (n/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="171" t="inlineStr">
+        <is>
+          <t>Connect_worker_13</t>
+        </is>
+      </c>
+      <c r="B339" s="171" t="inlineStr">
+        <is>
+          <t>Connect workers page</t>
+        </is>
+      </c>
+      <c r="C339" s="171" t="inlineStr">
+        <is>
+          <t>Verify user is able to delete not-found users (Delete affordance; not executed to preserve seed)</t>
+        </is>
+      </c>
+      <c r="D339" s="171" t="inlineStr">
+        <is>
+          <t>🟢 Already automated</t>
+        </is>
+      </c>
+      <c r="E339" s="171" t="inlineStr">
+        <is>
+          <t>test_worker_lifecycle.py::test_connect_worker_13_not_found_deletable</t>
+        </is>
+      </c>
+      <c r="F339" s="171" t="inlineStr">
+        <is>
+          <t>Connect Workers Batch C - Anshu data 2 (Worker_Lifecycle_Automation, 2026-09-10)</t>
+        </is>
+      </c>
+      <c r="G339" s="171" t="inlineStr">
         <is>
           <t>Already automated (n/a)</t>
         </is>
